--- a/Data Analysis/1_Data/economic_MF_final.xlsx
+++ b/Data Analysis/1_Data/economic_MF_final.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y79"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -452,30 +452,20 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dCVdSR</t>
+          <t>SOC_costs_mid</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>SOC_costs_lo</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>SOC_costs_mid</t>
+          <t>SOC_costs_hi</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>SOC_costs_lo</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>SOC_costs_hi</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>costs_total_mid</t>
         </is>
@@ -491,16 +481,16 @@
         <v>4.405795634920635</v>
       </c>
       <c r="C2">
-        <v>453.3312142227535</v>
+        <v>454.1734339950201</v>
       </c>
       <c r="D2">
-        <v>0.3863271230937151</v>
+        <v>0.39345572806922</v>
       </c>
       <c r="E2">
-        <v>417.0299279952928</v>
+        <v>416.5968581011657</v>
       </c>
       <c r="F2">
-        <v>36.30128622746071</v>
+        <v>37.57657589385445</v>
       </c>
       <c r="G2">
         <v>16</v>
@@ -535,31 +525,25 @@
         <v>-10.47532815937312</v>
       </c>
       <c r="Q2">
-        <v>-23.52758704595202</v>
+        <v>-30.37845166218204</v>
       </c>
       <c r="R2">
-        <v>-41.90131263749247</v>
+        <v>-50.28157516499095</v>
       </c>
       <c r="S2">
         <v>11.83333333333333</v>
       </c>
       <c r="T2">
-        <v>0.03134540163025619</v>
+        <v>776.0019362477558</v>
       </c>
       <c r="U2">
-        <v>-0.501526426084099</v>
+        <v>194.0004840619389</v>
       </c>
       <c r="V2">
-        <v>821.6491089682121</v>
+        <v>2069.338496660682</v>
       </c>
       <c r="W2">
-        <v>205.412277242053</v>
-      </c>
-      <c r="X2">
-        <v>2191.064290581899</v>
-      </c>
-      <c r="Y2">
-        <v>1251.452736145014</v>
+        <v>1199.796918580594</v>
       </c>
     </row>
     <row r="3">
@@ -572,16 +556,16 @@
         <v>3.340894047619048</v>
       </c>
       <c r="C3">
-        <v>361.7746334690266</v>
+        <v>362.4139693049078</v>
       </c>
       <c r="D3">
-        <v>0.3641539720102155</v>
+        <v>0.4168268958916156</v>
       </c>
       <c r="E3">
-        <v>335.7301238987416</v>
+        <v>329.2007010263908</v>
       </c>
       <c r="F3">
-        <v>26.04450957028496</v>
+        <v>33.21326827851698</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -616,31 +600,25 @@
         <v>-13.07296535913886</v>
       </c>
       <c r="Q3">
-        <v>-29.36188019662587</v>
+        <v>-37.91159954150268</v>
       </c>
       <c r="R3">
-        <v>-52.29186143655542</v>
+        <v>-62.7502337238665</v>
       </c>
       <c r="S3">
         <v>5.728813559322034</v>
       </c>
       <c r="T3">
-        <v>-0.03797628596756679</v>
+        <v>7.583391783192281</v>
       </c>
       <c r="U3">
-        <v>0.3038102877405343</v>
+        <v>1.89584794579807</v>
       </c>
       <c r="V3">
-        <v>8.029473652791827</v>
+        <v>20.22237808851275</v>
       </c>
       <c r="W3">
-        <v>2.007368413197957</v>
-      </c>
-      <c r="X3">
-        <v>21.41192974077821</v>
-      </c>
-      <c r="Y3">
-        <v>340.4422269251925</v>
+        <v>332.0857615465974</v>
       </c>
     </row>
     <row r="4">
@@ -653,16 +631,16 @@
         <v>3.206009523809524</v>
       </c>
       <c r="C4">
-        <v>277.2926839321931</v>
+        <v>308.6344959557815</v>
       </c>
       <c r="D4">
-        <v>0.7520044840041459</v>
+        <v>0.6592796869815137</v>
       </c>
       <c r="E4">
-        <v>211.9067446606369</v>
+        <v>248.540370395803</v>
       </c>
       <c r="F4">
-        <v>65.38593927155617</v>
+        <v>60.09412555997855</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -697,31 +675,25 @@
         <v>-39.37303388097506</v>
       </c>
       <c r="Q4">
-        <v>-88.43183409666999</v>
+        <v>-114.1817982548277</v>
       </c>
       <c r="R4">
-        <v>-157.4921355239002</v>
+        <v>-188.9905626286803</v>
       </c>
       <c r="S4">
         <v>6.186440677966102</v>
       </c>
       <c r="T4">
-        <v>-0.03797628596756679</v>
+        <v>74.56707340401853</v>
       </c>
       <c r="U4">
-        <v>0.3038102877405343</v>
+        <v>18.64176835100463</v>
       </c>
       <c r="V4">
-        <v>78.95337183954904</v>
+        <v>198.8455290773827</v>
       </c>
       <c r="W4">
-        <v>19.73834295988726</v>
-      </c>
-      <c r="X4">
-        <v>210.5423249054641</v>
-      </c>
-      <c r="Y4">
-        <v>267.8142216750721</v>
+        <v>269.0197711049724</v>
       </c>
     </row>
     <row r="5">
@@ -734,16 +706,16 @@
         <v>4.394603174603175</v>
       </c>
       <c r="C5">
-        <v>346.5858584228995</v>
+        <v>435.2538959729509</v>
       </c>
       <c r="D5">
-        <v>0.7236711137263443</v>
+        <v>0.6277465946716212</v>
       </c>
       <c r="E5">
-        <v>269.19759665971</v>
+        <v>356.5929114777018</v>
       </c>
       <c r="F5">
-        <v>77.38826176318952</v>
+        <v>78.66098449524912</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -778,31 +750,25 @@
         <v>-33.81296508887635</v>
       </c>
       <c r="Q5">
-        <v>-75.9439195896163</v>
+        <v>-98.05759875774143</v>
       </c>
       <c r="R5">
-        <v>-135.2518603555054</v>
+        <v>-162.3022324266065</v>
       </c>
       <c r="S5">
         <v>3.35</v>
       </c>
       <c r="T5">
-        <v>-0.07263712976647828</v>
+        <v>-381.4278283481973</v>
       </c>
       <c r="U5">
-        <v>0.2905485190659131</v>
+        <v>-95.35695708704932</v>
       </c>
       <c r="V5">
-        <v>-403.864759427503</v>
+        <v>-1017.140875595193</v>
       </c>
       <c r="W5">
-        <v>-100.9661898568758</v>
-      </c>
-      <c r="X5">
-        <v>-1076.972691806675</v>
-      </c>
-      <c r="Y5">
-        <v>-133.2228205942199</v>
+        <v>-44.23153113298775</v>
       </c>
     </row>
     <row r="6">
@@ -815,16 +781,16 @@
         <v>4.464246825396826</v>
       </c>
       <c r="C6">
-        <v>271.2646369070449</v>
+        <v>394.3106866112535</v>
       </c>
       <c r="D6">
-        <v>1.152708310768079</v>
+        <v>1.023510985183034</v>
       </c>
       <c r="E6">
-        <v>163.3506912605039</v>
+        <v>256.5043236285</v>
       </c>
       <c r="F6">
-        <v>107.913945646541</v>
+        <v>137.8063629827535</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -859,31 +825,25 @@
         <v>-27.26269086603715</v>
       </c>
       <c r="Q6">
-        <v>-61.23200368511945</v>
+        <v>-79.06180351150775</v>
       </c>
       <c r="R6">
-        <v>-109.0507634641486</v>
+        <v>-130.8609161569784</v>
       </c>
       <c r="S6">
         <v>1.864406779661017</v>
       </c>
       <c r="T6">
-        <v>-0.08996755166593402</v>
+        <v>-405.2626142571454</v>
       </c>
       <c r="U6">
-        <v>0.179935103331868</v>
+        <v>-101.3156535642864</v>
       </c>
       <c r="V6">
-        <v>-429.1015915663892</v>
+        <v>-1080.700304685721</v>
       </c>
       <c r="W6">
-        <v>-107.2753978915973</v>
-      </c>
-      <c r="X6">
-        <v>-1144.270910843705</v>
-      </c>
-      <c r="Y6">
-        <v>-219.0689583444637</v>
+        <v>-90.0137311573996</v>
       </c>
     </row>
     <row r="7">
@@ -896,16 +856,16 @@
         <v>3.109760079365079</v>
       </c>
       <c r="C7">
-        <v>298.0172404748202</v>
+        <v>324.9483390849962</v>
       </c>
       <c r="D7">
-        <v>0.5514338268886007</v>
+        <v>0.4815114334563739</v>
       </c>
       <c r="E7">
-        <v>254.1317898036486</v>
+        <v>286.7338295428325</v>
       </c>
       <c r="F7">
-        <v>43.88545067117164</v>
+        <v>38.21450954216374</v>
       </c>
       <c r="G7">
         <v>16</v>
@@ -940,31 +900,25 @@
         <v>-6.331647797361014</v>
       </c>
       <c r="Q7">
-        <v>-14.22088095287284</v>
+        <v>-18.36177861234694</v>
       </c>
       <c r="R7">
-        <v>-25.32659118944406</v>
+        <v>-30.39190942733287</v>
       </c>
       <c r="S7">
         <v>12.89830508474576</v>
       </c>
       <c r="T7">
-        <v>0.03134540163025619</v>
+        <v>212.5784837509758</v>
       </c>
       <c r="U7">
-        <v>-0.501526426084099</v>
+        <v>53.14462093774394</v>
       </c>
       <c r="V7">
-        <v>225.0831004422096</v>
+        <v>566.8759566692687</v>
       </c>
       <c r="W7">
-        <v>56.27077511055241</v>
-      </c>
-      <c r="X7">
-        <v>600.2216011792257</v>
-      </c>
-      <c r="Y7">
-        <v>508.879459964157</v>
+        <v>519.165044223625</v>
       </c>
     </row>
     <row r="8">
@@ -977,16 +931,16 @@
         <v>1.978450634920635</v>
       </c>
       <c r="C8">
-        <v>200.6668101600493</v>
+        <v>189.681000553283</v>
       </c>
       <c r="D8">
-        <v>0.8516592508034231</v>
+        <v>0.7615213407886234</v>
       </c>
       <c r="E8">
-        <v>144.6615877910172</v>
+        <v>144.1596234494615</v>
       </c>
       <c r="F8">
-        <v>56.00522236903203</v>
+        <v>45.52137710382149</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1021,31 +975,25 @@
         <v>-29.17091187774911</v>
       </c>
       <c r="Q8">
-        <v>-65.5178680774245</v>
+        <v>-84.5956444454724</v>
       </c>
       <c r="R8">
-        <v>-116.6836475109964</v>
+        <v>-140.0203770131957</v>
       </c>
       <c r="S8">
         <v>2</v>
       </c>
       <c r="T8">
-        <v>-0.08996755166593402</v>
+        <v>-373.4422893248743</v>
       </c>
       <c r="U8">
-        <v>0.179935103331868</v>
+        <v>-93.36057233121856</v>
       </c>
       <c r="V8">
-        <v>-395.4094828145728</v>
+        <v>-995.8461048663313</v>
       </c>
       <c r="W8">
-        <v>-98.85237070364319</v>
-      </c>
-      <c r="X8">
-        <v>-1054.425287505527</v>
-      </c>
-      <c r="Y8">
-        <v>-260.260540731948</v>
+        <v>-268.3569332170637</v>
       </c>
     </row>
     <row r="9">
@@ -1058,16 +1006,16 @@
         <v>3.525586507936508</v>
       </c>
       <c r="C9">
-        <v>308.3830296472063</v>
+        <v>382.7767824268525</v>
       </c>
       <c r="D9">
-        <v>0.6586741284191985</v>
+        <v>0.6679587706777543</v>
       </c>
       <c r="E9">
-        <v>248.4207944023855</v>
+        <v>306.7709091073825</v>
       </c>
       <c r="F9">
-        <v>59.96223524482076</v>
+        <v>76.00587331946997</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1102,31 +1050,25 @@
         <v>-47.77855710353627</v>
       </c>
       <c r="Q9">
-        <v>-107.3106392545425</v>
+        <v>-138.5578156002552</v>
       </c>
       <c r="R9">
-        <v>-191.1142284141451</v>
+        <v>-229.3370740969741</v>
       </c>
       <c r="S9">
         <v>1</v>
       </c>
       <c r="T9">
-        <v>-0.0986327626156619</v>
+        <v>-356.7084314993093</v>
       </c>
       <c r="U9">
-        <v>0.0986327626156619</v>
+        <v>-89.17710787482731</v>
       </c>
       <c r="V9">
-        <v>-377.6912804110333</v>
+        <v>-951.2224839981581</v>
       </c>
       <c r="W9">
-        <v>-94.42282010275834</v>
-      </c>
-      <c r="X9">
-        <v>-1007.176747762756</v>
-      </c>
-      <c r="Y9">
-        <v>-176.6188900183695</v>
+        <v>-112.489464672712</v>
       </c>
     </row>
     <row r="10">
@@ -1139,16 +1081,16 @@
         <v>0.8964404761904762</v>
       </c>
       <c r="C10">
-        <v>37.17377170845272</v>
+        <v>76.61009767213613</v>
       </c>
       <c r="D10">
-        <v>0.9097008866777399</v>
+        <v>1.087336851145372</v>
       </c>
       <c r="E10">
-        <v>25.88893909096406</v>
+        <v>47.96640542908309</v>
       </c>
       <c r="F10">
-        <v>11.28483261748866</v>
+        <v>28.64369224305305</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1183,31 +1125,25 @@
         <v>-22.22402034233572</v>
       </c>
       <c r="Q10">
-        <v>-49.91514968888603</v>
+        <v>-64.44965899277359</v>
       </c>
       <c r="R10">
-        <v>-88.89608136934288</v>
+        <v>-106.6752976432115</v>
       </c>
       <c r="S10">
         <v>0.9523809523809523</v>
       </c>
       <c r="T10">
-        <v>-0.0986327626156619</v>
+        <v>-453.0081391389492</v>
       </c>
       <c r="U10">
-        <v>0.0986327626156619</v>
+        <v>-113.2520347847373</v>
       </c>
       <c r="V10">
-        <v>-479.6556767353579</v>
+        <v>-1208.021704370531</v>
       </c>
       <c r="W10">
-        <v>-119.9139191838395</v>
-      </c>
-      <c r="X10">
-        <v>-1279.081804627621</v>
-      </c>
-      <c r="Y10">
-        <v>-492.3970547157912</v>
+        <v>-440.8477004595866</v>
       </c>
     </row>
     <row r="11">
@@ -1220,16 +1156,16 @@
         <v>3.324372142857143</v>
       </c>
       <c r="C11">
-        <v>320.4325778753254</v>
+        <v>351.2190186346197</v>
       </c>
       <c r="D11">
-        <v>0.5488687498261735</v>
+        <v>0.4566204374199388</v>
       </c>
       <c r="E11">
-        <v>273.6017277433339</v>
+        <v>313.4942306184083</v>
       </c>
       <c r="F11">
-        <v>46.8308501319915</v>
+        <v>37.72478801621145</v>
       </c>
       <c r="G11">
         <v>16</v>
@@ -1264,31 +1200,25 @@
         <v>-11.62772251125077</v>
       </c>
       <c r="Q11">
-        <v>-26.11586476026923</v>
+        <v>-33.72039528262723</v>
       </c>
       <c r="R11">
-        <v>-46.51089004500307</v>
+        <v>-55.81306805400369</v>
       </c>
       <c r="S11">
         <v>11.03333333333333</v>
       </c>
       <c r="T11">
-        <v>0.03134540163025619</v>
+        <v>1022.72996477033</v>
       </c>
       <c r="U11">
-        <v>-0.501526426084099</v>
+        <v>255.6824911925825</v>
       </c>
       <c r="V11">
-        <v>1082.89055093329</v>
+        <v>2727.279906054213</v>
       </c>
       <c r="W11">
-        <v>270.7226377333226</v>
-      </c>
-      <c r="X11">
-        <v>2887.708135822108</v>
-      </c>
-      <c r="Y11">
-        <v>1377.207264048347</v>
+        <v>1340.228588122322</v>
       </c>
     </row>
     <row r="12">
@@ -1301,16 +1231,16 @@
         <v>4.736521507936508</v>
       </c>
       <c r="C12">
-        <v>446.5502780110959</v>
+        <v>493.5619191353025</v>
       </c>
       <c r="D12">
-        <v>0.5961619175694598</v>
+        <v>0.5448753392177107</v>
       </c>
       <c r="E12">
-        <v>372.0729853755073</v>
+        <v>422.2794362261802</v>
       </c>
       <c r="F12">
-        <v>74.47729263558858</v>
+        <v>71.28248290912234</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -1345,31 +1275,25 @@
         <v>-33.847964515706</v>
       </c>
       <c r="Q12">
-        <v>-76.02252830227569</v>
+        <v>-98.15909709554741</v>
       </c>
       <c r="R12">
-        <v>-135.391858062824</v>
+        <v>-162.4702296753888</v>
       </c>
       <c r="S12">
         <v>5.3</v>
       </c>
       <c r="T12">
-        <v>-0.03797628596756679</v>
+        <v>-370.1816630423123</v>
       </c>
       <c r="U12">
-        <v>0.3038102877405343</v>
+        <v>-92.54541576057808</v>
       </c>
       <c r="V12">
-        <v>-391.9570549859777</v>
+        <v>-987.1511014461662</v>
       </c>
       <c r="W12">
-        <v>-97.98926374649443</v>
-      </c>
-      <c r="X12">
-        <v>-1045.218813295941</v>
-      </c>
-      <c r="Y12">
-        <v>-21.42930527715754</v>
+        <v>25.22115899744279</v>
       </c>
     </row>
     <row r="13">
@@ -1382,16 +1306,16 @@
         <v>4.663600793650794</v>
       </c>
       <c r="C13">
-        <v>418.9017897742518</v>
+        <v>474.1843273460485</v>
       </c>
       <c r="D13">
-        <v>0.6923045603860244</v>
+        <v>0.6498474301972058</v>
       </c>
       <c r="E13">
-        <v>331.1928842816537</v>
+        <v>383.8417064536477</v>
       </c>
       <c r="F13">
-        <v>87.70890549259809</v>
+        <v>90.34262089240082</v>
       </c>
       <c r="G13">
         <v>4</v>
@@ -1426,31 +1350,25 @@
         <v>-31.01088590349041</v>
       </c>
       <c r="Q13">
-        <v>-69.65044973923948</v>
+        <v>-89.93156912012221</v>
       </c>
       <c r="R13">
-        <v>-124.0435436139617</v>
+        <v>-148.852252336754</v>
       </c>
       <c r="S13">
         <v>3.2</v>
       </c>
       <c r="T13">
-        <v>-0.07263712976647828</v>
+        <v>-168.5018317652187</v>
       </c>
       <c r="U13">
-        <v>0.2905485190659131</v>
+        <v>-42.12545794130468</v>
       </c>
       <c r="V13">
-        <v>-178.4137042219963</v>
+        <v>-449.3382180405833</v>
       </c>
       <c r="W13">
-        <v>-44.60342605549907</v>
-      </c>
-      <c r="X13">
-        <v>-475.7698779253234</v>
-      </c>
-      <c r="Y13">
-        <v>170.837635813016</v>
+        <v>215.7509264607076</v>
       </c>
     </row>
     <row r="14">
@@ -1463,16 +1381,16 @@
         <v>2.559590873015873</v>
       </c>
       <c r="C14">
-        <v>236.0013860586845</v>
+        <v>256.9109856449426</v>
       </c>
       <c r="D14">
-        <v>0.6569215218853575</v>
+        <v>0.5280969391028871</v>
       </c>
       <c r="E14">
-        <v>190.2967581059404</v>
+        <v>221.6580450526751</v>
       </c>
       <c r="F14">
-        <v>45.70462795274409</v>
+        <v>35.25294059226744</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -1507,31 +1425,25 @@
         <v>-8.496045057041325</v>
       </c>
       <c r="Q14">
-        <v>-19.08211719811482</v>
+        <v>-24.63853066541984</v>
       </c>
       <c r="R14">
-        <v>-33.9841802281653</v>
+        <v>-40.78101627379836</v>
       </c>
       <c r="S14">
         <v>6.559322033898305</v>
       </c>
       <c r="T14">
-        <v>-0.03797628596756679</v>
+        <v>433.4735654111012</v>
       </c>
       <c r="U14">
-        <v>0.3038102877405343</v>
+        <v>108.3683913527753</v>
       </c>
       <c r="V14">
-        <v>458.9720104352836</v>
+        <v>1155.929507762937</v>
       </c>
       <c r="W14">
-        <v>114.7430026088209</v>
-      </c>
-      <c r="X14">
-        <v>1223.925361160756</v>
-      </c>
-      <c r="Y14">
-        <v>675.8912792958532</v>
+        <v>665.7460203906239</v>
       </c>
     </row>
     <row r="15">
@@ -1544,16 +1456,16 @@
         <v>1.051080952380952</v>
       </c>
       <c r="C15">
-        <v>15.59614096183473</v>
+        <v>96.0014550060751</v>
       </c>
       <c r="D15">
-        <v>1.965212575320455</v>
+        <v>2.059899075105867</v>
       </c>
       <c r="E15">
-        <v>6.038442545738572</v>
+        <v>35.52390877429637</v>
       </c>
       <c r="F15">
-        <v>9.557698416096162</v>
+        <v>60.47754623177874</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1588,31 +1500,25 @@
         <v>-19.26984409302531</v>
       </c>
       <c r="Q15">
-        <v>-43.28006983293484</v>
+        <v>-55.88254786977339</v>
       </c>
       <c r="R15">
-        <v>-77.07937637210124</v>
+        <v>-92.49525164652148</v>
       </c>
       <c r="S15">
         <v>0.95</v>
       </c>
       <c r="T15">
-        <v>-0.0986327626156619</v>
+        <v>-607.3755880406841</v>
       </c>
       <c r="U15">
-        <v>0.0986327626156619</v>
+        <v>-151.843897010171</v>
       </c>
       <c r="V15">
-        <v>-643.1035638077832</v>
+        <v>-1619.668234775158</v>
       </c>
       <c r="W15">
-        <v>-160.7758909519458</v>
-      </c>
-      <c r="X15">
-        <v>-1714.942836820755</v>
-      </c>
-      <c r="Y15">
-        <v>-670.7874926788833</v>
+        <v>-567.2566809043824</v>
       </c>
     </row>
     <row r="16">
@@ -1625,16 +1531,16 @@
         <v>1.690539285714286</v>
       </c>
       <c r="C16">
-        <v>147.2994055308986</v>
+        <v>175.7049704187549</v>
       </c>
       <c r="D16">
-        <v>0.6921566561654485</v>
+        <v>0.7187828851276133</v>
       </c>
       <c r="E16">
-        <v>116.4677935492791</v>
+        <v>136.8525914046039</v>
       </c>
       <c r="F16">
-        <v>30.83161198161949</v>
+        <v>38.85237901415098</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1669,31 +1575,25 @@
         <v>-5.682655945739832</v>
       </c>
       <c r="Q16">
-        <v>-12.76324525413166</v>
+        <v>-16.47970224264551</v>
       </c>
       <c r="R16">
-        <v>-22.73062378295933</v>
+        <v>-27.27674853955119</v>
       </c>
       <c r="S16">
         <v>1.983050847457627</v>
       </c>
       <c r="T16">
-        <v>-0.08996755166593402</v>
+        <v>-637.9332337409667</v>
       </c>
       <c r="U16">
-        <v>0.179935103331868</v>
+        <v>-159.4833084352417</v>
       </c>
       <c r="V16">
-        <v>-675.4587180786706</v>
+        <v>-1701.155289975911</v>
       </c>
       <c r="W16">
-        <v>-168.8646795196676</v>
-      </c>
-      <c r="X16">
-        <v>-1801.223248209788</v>
-      </c>
-      <c r="Y16">
-        <v>-540.9225578019037</v>
+        <v>-478.7079655648573</v>
       </c>
     </row>
     <row r="17">
@@ -1706,16 +1606,16 @@
         <v>2.063876587301587</v>
       </c>
       <c r="C17">
-        <v>177.0907335107914</v>
+        <v>205.0190027778368</v>
       </c>
       <c r="D17">
-        <v>0.7491995787986518</v>
+        <v>0.6582366787324752</v>
       </c>
       <c r="E17">
-        <v>135.5514037686816</v>
+        <v>165.1947746486002</v>
       </c>
       <c r="F17">
-        <v>41.5393297421098</v>
+        <v>39.82422812923664</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1750,31 +1650,25 @@
         <v>-14.46110214439125</v>
       </c>
       <c r="Q17">
-        <v>-32.47963541630276</v>
+        <v>-41.93719621873464</v>
       </c>
       <c r="R17">
-        <v>-57.84440857756502</v>
+        <v>-69.41329029307803</v>
       </c>
       <c r="S17">
         <v>2</v>
       </c>
       <c r="T17">
-        <v>-0.08996755166593402</v>
+        <v>-998.2419574417249</v>
       </c>
       <c r="U17">
-        <v>0.179935103331868</v>
+        <v>-249.5604893604312</v>
       </c>
       <c r="V17">
-        <v>-1056.962072585356</v>
+        <v>-2661.978553177933</v>
       </c>
       <c r="W17">
-        <v>-264.240518146339</v>
-      </c>
-      <c r="X17">
-        <v>-2818.565526894282</v>
-      </c>
-      <c r="Y17">
-        <v>-912.3509744908672</v>
+        <v>-835.1601508826228</v>
       </c>
     </row>
     <row r="18">
@@ -1787,16 +1681,16 @@
         <v>0.6598722222222222</v>
       </c>
       <c r="C18">
-        <v>43.27300399466804</v>
+        <v>68.65963846850231</v>
       </c>
       <c r="D18">
-        <v>0.9998600503185773</v>
+        <v>0.9174449964737151</v>
       </c>
       <c r="E18">
-        <v>28.55193294662387</v>
+        <v>47.59588718965632</v>
       </c>
       <c r="F18">
-        <v>14.72107104804418</v>
+        <v>21.06375127884599</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1831,31 +1725,25 @@
         <v>-10.86887627414816</v>
       </c>
       <c r="Q18">
-        <v>-24.41149611173678</v>
+        <v>-31.51974119502968</v>
       </c>
       <c r="R18">
-        <v>-43.47550509659266</v>
+        <v>-52.17060611591119</v>
       </c>
       <c r="S18">
         <v>1</v>
       </c>
       <c r="T18">
-        <v>-0.0986327626156619</v>
+        <v>-757.7101452362072</v>
       </c>
       <c r="U18">
-        <v>0.0986327626156619</v>
+        <v>-189.4275363090518</v>
       </c>
       <c r="V18">
-        <v>-802.2813302501017</v>
+        <v>-2020.560387296552</v>
       </c>
       <c r="W18">
-        <v>-200.5703325625254</v>
-      </c>
-      <c r="X18">
-        <v>-2139.416880666938</v>
-      </c>
-      <c r="Y18">
-        <v>-783.4198223671706</v>
+        <v>-720.5702479627346</v>
       </c>
     </row>
     <row r="19">
@@ -1868,16 +1756,16 @@
         <v>2.689576587301588</v>
       </c>
       <c r="C19">
-        <v>246.80134723912</v>
+        <v>275.5734261908571</v>
       </c>
       <c r="D19">
-        <v>0.7082164730955326</v>
+        <v>0.6161318233197487</v>
       </c>
       <c r="E19">
-        <v>193.3837942463713</v>
+        <v>227.1861985099758</v>
       </c>
       <c r="F19">
-        <v>53.41755299274871</v>
+        <v>48.3872276808813</v>
       </c>
       <c r="G19">
         <v>4</v>
@@ -1912,31 +1800,25 @@
         <v>-10.92994534158543</v>
       </c>
       <c r="Q19">
-        <v>-24.54865723720087</v>
+        <v>-31.69684149059774</v>
       </c>
       <c r="R19">
-        <v>-43.71978136634172</v>
+        <v>-52.46373763961006</v>
       </c>
       <c r="S19">
         <v>3.559322033898305</v>
       </c>
       <c r="T19">
-        <v>-0.07263712976647828</v>
+        <v>-744.369023474728</v>
       </c>
       <c r="U19">
-        <v>0.2905485190659131</v>
+        <v>-186.092255868682</v>
       </c>
       <c r="V19">
-        <v>-788.1554366203003</v>
+        <v>-1984.984062599275</v>
       </c>
       <c r="W19">
-        <v>-197.0388591550751</v>
-      </c>
-      <c r="X19">
-        <v>-2101.747830987467</v>
-      </c>
-      <c r="Y19">
-        <v>-565.9027466183812</v>
+        <v>-500.4924387744687</v>
       </c>
     </row>
     <row r="20">
@@ -1949,16 +1831,16 @@
         <v>5.965528968253969</v>
       </c>
       <c r="C20">
-        <v>596.6949576228966</v>
+        <v>624.4237670625664</v>
       </c>
       <c r="D20">
-        <v>0.3332924713492372</v>
+        <v>0.3206156334207687</v>
       </c>
       <c r="E20">
-        <v>560.1498987509879</v>
+        <v>588.8201959106296</v>
       </c>
       <c r="F20">
-        <v>36.54505887190874</v>
+        <v>35.60357115193676</v>
       </c>
       <c r="G20">
         <v>16</v>
@@ -1993,31 +1875,25 @@
         <v>-16.78413690809824</v>
       </c>
       <c r="Q20">
-        <v>-37.69717149558866</v>
+        <v>-48.6739970334849</v>
       </c>
       <c r="R20">
-        <v>-67.13654763239296</v>
+        <v>-80.56385715887156</v>
       </c>
       <c r="S20">
         <v>12.15254237288136</v>
       </c>
       <c r="T20">
-        <v>0.03134540163025619</v>
+        <v>-156.5795148059204</v>
       </c>
       <c r="U20">
-        <v>-0.501526426084099</v>
+        <v>-39.14487870148009</v>
       </c>
       <c r="V20">
-        <v>-165.7900745003863</v>
+        <v>-417.5453728157876</v>
       </c>
       <c r="W20">
-        <v>-41.44751862509656</v>
-      </c>
-      <c r="X20">
-        <v>-442.1068653343634</v>
-      </c>
-      <c r="Y20">
-        <v>393.2077116269217</v>
+        <v>419.1702552231611</v>
       </c>
     </row>
     <row r="21">
@@ -2030,16 +1906,16 @@
         <v>1.625247619047619</v>
       </c>
       <c r="C21">
-        <v>114.701253971223</v>
+        <v>163.617689553654</v>
       </c>
       <c r="D21">
-        <v>1.145671606508711</v>
+        <v>1.012011213505238</v>
       </c>
       <c r="E21">
-        <v>69.36046143284703</v>
+        <v>107.1722850759626</v>
       </c>
       <c r="F21">
-        <v>45.34079253837598</v>
+        <v>56.44540447769138</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -2074,31 +1950,25 @@
         <v>-4.995341446251246</v>
       </c>
       <c r="Q21">
-        <v>-11.2195368882803</v>
+        <v>-14.48649019412861</v>
       </c>
       <c r="R21">
-        <v>-19.98136578500498</v>
+        <v>-23.97763894200598</v>
       </c>
       <c r="S21">
         <v>3.694915254237288</v>
       </c>
       <c r="T21">
-        <v>-0.07263712976647828</v>
+        <v>72.5154982273032</v>
       </c>
       <c r="U21">
-        <v>0.2905485190659131</v>
+        <v>18.1288745568258</v>
       </c>
       <c r="V21">
-        <v>76.78111577008573</v>
+        <v>193.3746619394752</v>
       </c>
       <c r="W21">
-        <v>19.19527894252143</v>
-      </c>
-      <c r="X21">
-        <v>204.749642053562</v>
-      </c>
-      <c r="Y21">
-        <v>180.2628328530284</v>
+        <v>221.6466975868286</v>
       </c>
     </row>
     <row r="22">
@@ -2111,16 +1981,16 @@
         <v>4.653543650793651</v>
       </c>
       <c r="C22">
-        <v>479.5245089496918</v>
+        <v>490.5675059831864</v>
       </c>
       <c r="D22">
-        <v>0.3771079139456976</v>
+        <v>0.3551811417396349</v>
       </c>
       <c r="E22">
-        <v>442.7546673183969</v>
+        <v>456.8148258797681</v>
       </c>
       <c r="F22">
-        <v>36.76984163129498</v>
+        <v>33.75268010341836</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -2155,31 +2025,25 @@
         <v>-9.391559245869148</v>
       </c>
       <c r="Q22">
-        <v>-21.09344206622211</v>
+        <v>-27.23552181302053</v>
       </c>
       <c r="R22">
-        <v>-37.56623698347659</v>
+        <v>-45.07948438017191</v>
       </c>
       <c r="S22">
         <v>3.6</v>
       </c>
       <c r="T22">
-        <v>-0.07263712976647828</v>
+        <v>822.0031998972684</v>
       </c>
       <c r="U22">
-        <v>0.2905485190659131</v>
+        <v>205.5007999743171</v>
       </c>
       <c r="V22">
-        <v>870.35632930299</v>
+        <v>2192.008533059382</v>
       </c>
       <c r="W22">
-        <v>217.5890823257475</v>
-      </c>
-      <c r="X22">
-        <v>2320.95021147464</v>
-      </c>
-      <c r="Y22">
-        <v>1328.78739618646</v>
+        <v>1285.335184067434</v>
       </c>
     </row>
     <row r="23">
@@ -2192,16 +2056,16 @@
         <v>2.115553174603175</v>
       </c>
       <c r="C23">
-        <v>182.4974102223082</v>
+        <v>204.625456822857</v>
       </c>
       <c r="D23">
-        <v>0.8112147303905599</v>
+        <v>0.7130422182029099</v>
       </c>
       <c r="E23">
-        <v>134.7395500868845</v>
+        <v>159.8986152219455</v>
       </c>
       <c r="F23">
-        <v>47.7578601354237</v>
+        <v>44.72684160091154</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2236,31 +2100,25 @@
         <v>-3.704487971959333</v>
       </c>
       <c r="Q23">
-        <v>-8.320279985020663</v>
+        <v>-10.74301511868207</v>
       </c>
       <c r="R23">
-        <v>-14.81795188783733</v>
+        <v>-17.7815422654048</v>
       </c>
       <c r="S23">
         <v>1.983050847457627</v>
       </c>
       <c r="T23">
-        <v>-0.08996755166593402</v>
+        <v>-50.02277013860132</v>
       </c>
       <c r="U23">
-        <v>0.179935103331868</v>
+        <v>-12.50569253465033</v>
       </c>
       <c r="V23">
-        <v>-52.96528602910728</v>
+        <v>-133.3940537029368</v>
       </c>
       <c r="W23">
-        <v>-13.24132150727682</v>
-      </c>
-      <c r="X23">
-        <v>-141.2407627442861</v>
-      </c>
-      <c r="Y23">
-        <v>121.2118442081803</v>
+        <v>143.8596715655736</v>
       </c>
     </row>
     <row r="24">
@@ -2273,16 +2131,16 @@
         <v>1.449059523809524</v>
       </c>
       <c r="C24">
-        <v>112.7775117945326</v>
+        <v>152.2000485997734</v>
       </c>
       <c r="D24">
-        <v>0.7909640609586905</v>
+        <v>0.8559765251674778</v>
       </c>
       <c r="E24">
-        <v>84.25785983022837</v>
+        <v>109.44133844812</v>
       </c>
       <c r="F24">
-        <v>28.51965196430424</v>
+        <v>42.75871015165337</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2317,31 +2175,25 @@
         <v>-25.17162819222155</v>
       </c>
       <c r="Q24">
-        <v>-56.5354769197296</v>
+        <v>-72.99772175744249</v>
       </c>
       <c r="R24">
-        <v>-100.6865127688862</v>
+        <v>-120.8238153226634</v>
       </c>
       <c r="S24">
         <v>1</v>
       </c>
       <c r="T24">
-        <v>-0.0986327626156619</v>
+        <v>-216.7298338907898</v>
       </c>
       <c r="U24">
-        <v>0.0986327626156619</v>
+        <v>-54.18245847269746</v>
       </c>
       <c r="V24">
-        <v>-229.4786476490716</v>
+        <v>-577.9462237087729</v>
       </c>
       <c r="W24">
-        <v>-57.3696619122679</v>
-      </c>
-      <c r="X24">
-        <v>-611.9430603975243</v>
-      </c>
-      <c r="Y24">
-        <v>-173.2366127742686</v>
+        <v>-137.527507048459</v>
       </c>
     </row>
     <row r="25">
@@ -2354,16 +2206,16 @@
         <v>1.815904761904762</v>
       </c>
       <c r="C25">
-        <v>100.5743262345679</v>
+        <v>169.6616993817148</v>
       </c>
       <c r="D25">
-        <v>1.332232262728016</v>
+        <v>1.339552482385653</v>
       </c>
       <c r="E25">
-        <v>54.51852543292651</v>
+        <v>91.5820982705574</v>
       </c>
       <c r="F25">
-        <v>46.0558008016414</v>
+        <v>78.07960111115742</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2398,31 +2250,25 @@
         <v>-9.519688028999356</v>
       </c>
       <c r="Q25">
-        <v>-21.38121931313255</v>
+        <v>-27.60709528409813</v>
       </c>
       <c r="R25">
-        <v>-38.07875211599742</v>
+        <v>-45.6945025391969</v>
       </c>
       <c r="S25">
         <v>0.9833333333333333</v>
       </c>
       <c r="T25">
-        <v>-0.0986327626156619</v>
+        <v>-70.16476144728868</v>
       </c>
       <c r="U25">
-        <v>0.0986327626156619</v>
+        <v>-17.54119036182217</v>
       </c>
       <c r="V25">
-        <v>-74.29210035595273</v>
+        <v>-187.1060305261032</v>
       </c>
       <c r="W25">
-        <v>-18.57302508898818</v>
-      </c>
-      <c r="X25">
-        <v>-198.1122676158739</v>
-      </c>
-      <c r="Y25">
-        <v>4.901006565482618</v>
+        <v>71.88984265032799</v>
       </c>
     </row>
     <row r="26">
@@ -2435,16 +2281,16 @@
         <v>3.270512301587301</v>
       </c>
       <c r="C26">
-        <v>346.3252054309166</v>
+        <v>319.9500321010954</v>
       </c>
       <c r="D26">
-        <v>0.6144300145254673</v>
+        <v>0.3709690988846847</v>
       </c>
       <c r="E26">
-        <v>285.7752083918498</v>
+        <v>296.1312695228585</v>
       </c>
       <c r="F26">
-        <v>60.5499970390668</v>
+        <v>23.81876257823694</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -2479,31 +2325,25 @@
         <v>-12.47330286656029</v>
       </c>
       <c r="Q26">
-        <v>-28.0150382382944</v>
+        <v>-36.17257831302483</v>
       </c>
       <c r="R26">
-        <v>-49.89321146624114</v>
+        <v>-59.87185375948937</v>
       </c>
       <c r="S26">
         <v>3.677966101694915</v>
       </c>
       <c r="T26">
-        <v>-0.07263712976647828</v>
+        <v>458.1313522679775</v>
       </c>
       <c r="U26">
-        <v>0.2905485190659131</v>
+        <v>114.5328380669944</v>
       </c>
       <c r="V26">
-        <v>485.0802553425644</v>
+        <v>1221.68360604794</v>
       </c>
       <c r="W26">
-        <v>121.2700638356411</v>
-      </c>
-      <c r="X26">
-        <v>1293.547347580172</v>
-      </c>
-      <c r="Y26">
-        <v>803.3904225351866</v>
+        <v>741.9088060560481</v>
       </c>
     </row>
     <row r="27">
@@ -2516,16 +2356,16 @@
         <v>1.457390396825397</v>
       </c>
       <c r="C27">
-        <v>132.8224990911576</v>
+        <v>153.1027994695602</v>
       </c>
       <c r="D27">
-        <v>0.723306360420332</v>
+        <v>0.7943447411242142</v>
       </c>
       <c r="E27">
-        <v>103.1863530260593</v>
+        <v>114.1598476401484</v>
       </c>
       <c r="F27">
-        <v>29.63614606509832</v>
+        <v>38.94295182941181</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -2560,31 +2400,25 @@
         <v>-10.06655659182699</v>
       </c>
       <c r="Q27">
-        <v>-22.60948610524342</v>
+        <v>-29.19301411629827</v>
       </c>
       <c r="R27">
-        <v>-40.26622636730796</v>
+        <v>-48.31947164076955</v>
       </c>
       <c r="S27">
         <v>1.627118644067797</v>
       </c>
       <c r="T27">
-        <v>-0.08996755166593402</v>
+        <v>-417.5614356405866</v>
       </c>
       <c r="U27">
-        <v>0.179935103331868</v>
+        <v>-104.3903589101467</v>
       </c>
       <c r="V27">
-        <v>-442.1238730312094</v>
+        <v>-1113.497161708231</v>
       </c>
       <c r="W27">
-        <v>-110.5309682578023</v>
-      </c>
-      <c r="X27">
-        <v>-1178.996994749892</v>
-      </c>
-      <c r="Y27">
-        <v>-331.9108600452952</v>
+        <v>-293.6516502873247</v>
       </c>
     </row>
     <row r="28">
@@ -2597,16 +2431,16 @@
         <v>1.943852380952381</v>
       </c>
       <c r="C28">
-        <v>198.7374646505075</v>
+        <v>207.3402822573734</v>
       </c>
       <c r="D28">
-        <v>0.6441807369611584</v>
+        <v>0.6482604441170002</v>
       </c>
       <c r="E28">
-        <v>161.3732786759508</v>
+        <v>167.9833922714159</v>
       </c>
       <c r="F28">
-        <v>37.36418597455676</v>
+        <v>39.35688998595751</v>
       </c>
       <c r="G28">
         <v>4</v>
@@ -2641,31 +2475,25 @@
         <v>-4.996636621111337</v>
       </c>
       <c r="Q28">
-        <v>-11.22244585101606</v>
+        <v>-14.49024620122288</v>
       </c>
       <c r="R28">
-        <v>-19.98654648444535</v>
+        <v>-23.98385578133442</v>
       </c>
       <c r="S28">
         <v>3.933333333333333</v>
       </c>
       <c r="T28">
-        <v>-0.07263712976647828</v>
+        <v>-152.817217983223</v>
       </c>
       <c r="U28">
-        <v>0.2905485190659131</v>
+        <v>-38.20430449580575</v>
       </c>
       <c r="V28">
-        <v>-161.8064660998832</v>
+        <v>-407.5125812885947</v>
       </c>
       <c r="W28">
-        <v>-40.4516165249708</v>
-      </c>
-      <c r="X28">
-        <v>-431.4839095996885</v>
-      </c>
-      <c r="Y28">
-        <v>25.70855269960828</v>
+        <v>40.03281807292754</v>
       </c>
     </row>
     <row r="29">
@@ -2678,16 +2506,16 @@
         <v>3.591167063492064</v>
       </c>
       <c r="C29">
-        <v>393.7107541392018</v>
+        <v>393.5415434968938</v>
       </c>
       <c r="D29">
-        <v>0.3880998118779651</v>
+        <v>0.4230253462140602</v>
       </c>
       <c r="E29">
-        <v>361.9243431727642</v>
+        <v>356.5276811339573</v>
       </c>
       <c r="F29">
-        <v>31.78641096643753</v>
+        <v>37.01386236293655</v>
       </c>
       <c r="G29">
         <v>16</v>
@@ -2722,31 +2550,25 @@
         <v>-5.4330114544019</v>
       </c>
       <c r="Q29">
-        <v>-12.20254372658667</v>
+        <v>-15.75573321776551</v>
       </c>
       <c r="R29">
-        <v>-21.7320458176076</v>
+        <v>-26.07845498112912</v>
       </c>
       <c r="S29">
         <v>12.86440677966102</v>
       </c>
       <c r="T29">
-        <v>0.03134540163025619</v>
+        <v>446.5867656201178</v>
       </c>
       <c r="U29">
-        <v>-0.501526426084099</v>
+        <v>111.6466914050294</v>
       </c>
       <c r="V29">
-        <v>472.8565753624776</v>
+        <v>1190.898041653647</v>
       </c>
       <c r="W29">
-        <v>118.2141438406194</v>
-      </c>
-      <c r="X29">
-        <v>1260.950867633274</v>
-      </c>
-      <c r="Y29">
-        <v>854.3647857750927</v>
+        <v>824.3725758992462</v>
       </c>
     </row>
     <row r="30">
@@ -2759,16 +2581,16 @@
         <v>3.536456507936508</v>
       </c>
       <c r="C30">
-        <v>379.6415670649172</v>
+        <v>383.8768173635491</v>
       </c>
       <c r="D30">
-        <v>0.4437108071033612</v>
+        <v>0.4629939334493692</v>
       </c>
       <c r="E30">
-        <v>340.8344996615859</v>
+        <v>341.6509932303018</v>
       </c>
       <c r="F30">
-        <v>38.80706740333136</v>
+        <v>42.22582413324727</v>
       </c>
       <c r="G30">
         <v>8</v>
@@ -2803,31 +2625,25 @@
         <v>-4.778417432193342</v>
       </c>
       <c r="Q30">
-        <v>-10.73232555270625</v>
+        <v>-13.85741055336069</v>
       </c>
       <c r="R30">
-        <v>-19.11366972877337</v>
+        <v>-22.93640367452804</v>
       </c>
       <c r="S30">
         <v>6.135593220338983</v>
       </c>
       <c r="T30">
-        <v>-0.03797628596756679</v>
+        <v>686.5262758335965</v>
       </c>
       <c r="U30">
-        <v>0.3038102877405343</v>
+        <v>171.6315689583991</v>
       </c>
       <c r="V30">
-        <v>726.9101744120434</v>
+        <v>1830.736735556257</v>
       </c>
       <c r="W30">
-        <v>181.7275436030108</v>
-      </c>
-      <c r="X30">
-        <v>1938.427131765449</v>
-      </c>
-      <c r="Y30">
-        <v>1095.819415924254</v>
+        <v>1056.545682643785</v>
       </c>
     </row>
     <row r="31">
@@ -2840,16 +2656,16 @@
         <v>1.038455555555556</v>
       </c>
       <c r="C31">
-        <v>102.2602342320714</v>
+        <v>110.8339909270243</v>
       </c>
       <c r="D31">
-        <v>0.572064348628554</v>
+        <v>0.561157748949866</v>
       </c>
       <c r="E31">
-        <v>86.28467089005638</v>
+        <v>94.04543703289646</v>
       </c>
       <c r="F31">
-        <v>15.97556334201505</v>
+        <v>16.78855389412787</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2884,31 +2700,25 @@
         <v>-27.58571026976554</v>
       </c>
       <c r="Q31">
-        <v>-61.95750526589341</v>
+        <v>-79.99855978232007</v>
       </c>
       <c r="R31">
-        <v>-110.3428410790622</v>
+        <v>-132.4114092948746</v>
       </c>
       <c r="S31">
         <v>1</v>
       </c>
       <c r="T31">
-        <v>-0.0986327626156619</v>
+        <v>-348.1786362533473</v>
       </c>
       <c r="U31">
-        <v>0.0986327626156619</v>
+        <v>-87.04465906333684</v>
       </c>
       <c r="V31">
-        <v>-368.6597325035443</v>
+        <v>-928.4763633422596</v>
       </c>
       <c r="W31">
-        <v>-92.16493312588607</v>
-      </c>
-      <c r="X31">
-        <v>-983.0926200094514</v>
-      </c>
-      <c r="Y31">
-        <v>-328.3570035373663</v>
+        <v>-317.3432051086431</v>
       </c>
     </row>
     <row r="32">
@@ -2921,16 +2731,16 @@
         <v>3.485672698412698</v>
       </c>
       <c r="C32">
-        <v>332.1206935376766</v>
+        <v>360.6229863295089</v>
       </c>
       <c r="D32">
-        <v>0.5319876142007162</v>
+        <v>0.4999571520091635</v>
       </c>
       <c r="E32">
-        <v>285.9945416373791</v>
+        <v>315.4396844215909</v>
       </c>
       <c r="F32">
-        <v>46.12615190029749</v>
+        <v>45.18330190791801</v>
       </c>
       <c r="G32">
         <v>8</v>
@@ -2965,31 +2775,25 @@
         <v>-6.828565003487666</v>
       </c>
       <c r="Q32">
-        <v>-15.3369569978333</v>
+        <v>-19.80283851011423</v>
       </c>
       <c r="R32">
-        <v>-27.31426001395067</v>
+        <v>-32.7771120167408</v>
       </c>
       <c r="S32">
         <v>6</v>
       </c>
       <c r="T32">
-        <v>-0.03797628596756679</v>
+        <v>285.0303606961218</v>
       </c>
       <c r="U32">
-        <v>0.3038102877405343</v>
+        <v>71.25759017403045</v>
       </c>
       <c r="V32">
-        <v>301.7968525017761</v>
+        <v>760.0809618563248</v>
       </c>
       <c r="W32">
-        <v>75.44921312544402</v>
-      </c>
-      <c r="X32">
-        <v>804.7916066714029</v>
-      </c>
-      <c r="Y32">
-        <v>618.5805890416193</v>
+        <v>625.8505085155165</v>
       </c>
     </row>
     <row r="33">
@@ -3002,16 +2806,16 @@
         <v>4.819488888888889</v>
       </c>
       <c r="C33">
-        <v>368.873792979351</v>
+        <v>454.7321642289736</v>
       </c>
       <c r="D33">
-        <v>0.9936406302552971</v>
+        <v>0.9771527159386635</v>
       </c>
       <c r="E33">
-        <v>244.2963038902572</v>
+        <v>304.1519598482253</v>
       </c>
       <c r="F33">
-        <v>124.5774890890939</v>
+        <v>150.5802043807483</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3046,31 +2850,25 @@
         <v>-20.69211210331341</v>
       </c>
       <c r="Q33">
-        <v>-46.47448378404192</v>
+        <v>-60.00712509960888</v>
       </c>
       <c r="R33">
-        <v>-82.76844841325364</v>
+        <v>-99.32213809590436</v>
       </c>
       <c r="S33">
         <v>0.7333333333333333</v>
       </c>
       <c r="T33">
-        <v>-0.0986327626156619</v>
+        <v>-245.2723622574324</v>
       </c>
       <c r="U33">
-        <v>0.0986327626156619</v>
+        <v>-61.31809056435809</v>
       </c>
       <c r="V33">
-        <v>-259.7001482725755</v>
+        <v>-654.0596326864863</v>
       </c>
       <c r="W33">
-        <v>-64.92503706814387</v>
-      </c>
-      <c r="X33">
-        <v>-692.5337287268679</v>
-      </c>
-      <c r="Y33">
-        <v>62.69916092273365</v>
+        <v>149.4526768719323</v>
       </c>
     </row>
     <row r="34">
@@ -3083,16 +2881,16 @@
         <v>4.904101825396825</v>
       </c>
       <c r="C34">
-        <v>494.4717901393054</v>
+        <v>541.4711777392212</v>
       </c>
       <c r="D34">
-        <v>0.3391426406398945</v>
+        <v>0.4227347236872109</v>
       </c>
       <c r="E34">
-        <v>463.2041650576957</v>
+        <v>490.6054258011374</v>
       </c>
       <c r="F34">
-        <v>31.26762508160971</v>
+        <v>50.86575193808375</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -3127,31 +2925,25 @@
         <v>-7.032031308109477</v>
       </c>
       <c r="Q34">
-        <v>-15.79394231801389</v>
+        <v>-20.39289079351748</v>
       </c>
       <c r="R34">
-        <v>-28.12812523243791</v>
+        <v>-33.75375027892549</v>
       </c>
       <c r="S34">
         <v>3.610169491525424</v>
       </c>
       <c r="T34">
-        <v>-0.07263712976647828</v>
+        <v>-71.83156791000187</v>
       </c>
       <c r="U34">
-        <v>0.2905485190659131</v>
+        <v>-17.95789197750047</v>
       </c>
       <c r="V34">
-        <v>-76.05695425764904</v>
+        <v>-191.550847760005</v>
       </c>
       <c r="W34">
-        <v>-19.01423856441226</v>
-      </c>
-      <c r="X34">
-        <v>-202.8185446870641</v>
-      </c>
-      <c r="Y34">
-        <v>402.6208935636424</v>
+        <v>449.2467190357018</v>
       </c>
     </row>
     <row r="35">
@@ -3164,16 +2956,16 @@
         <v>3.198464285714286</v>
       </c>
       <c r="C35">
-        <v>279.5618397311321</v>
+        <v>331.3133935817298</v>
       </c>
       <c r="D35">
-        <v>0.6151735730407675</v>
+        <v>0.5533812224418524</v>
       </c>
       <c r="E35">
-        <v>230.5926436610751</v>
+        <v>282.2455123677459</v>
       </c>
       <c r="F35">
-        <v>48.969196070057</v>
+        <v>49.06788121398392</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -3208,31 +3000,25 @@
         <v>-14.53458432783136</v>
       </c>
       <c r="Q35">
-        <v>-32.64467640030924</v>
+        <v>-42.15029455071094</v>
       </c>
       <c r="R35">
-        <v>-58.13833731132544</v>
+        <v>-69.76600477359052</v>
       </c>
       <c r="S35">
         <v>6.220338983050848</v>
       </c>
       <c r="T35">
-        <v>-0.03797628596756679</v>
+        <v>715.1119955715096</v>
       </c>
       <c r="U35">
-        <v>0.3038102877405343</v>
+        <v>178.7779988928774</v>
       </c>
       <c r="V35">
-        <v>757.177407075716</v>
+        <v>1906.965321524026</v>
       </c>
       <c r="W35">
-        <v>189.294351768929</v>
-      </c>
-      <c r="X35">
-        <v>2019.139752201909</v>
-      </c>
-      <c r="Y35">
-        <v>1004.094570406539</v>
+        <v>1004.275094602528</v>
       </c>
     </row>
     <row r="36">
@@ -3245,16 +3031,16 @@
         <v>3.859080158730159</v>
       </c>
       <c r="C36">
-        <v>400.9615174677251</v>
+        <v>403.0191364053323</v>
       </c>
       <c r="D36">
-        <v>0.456719147057954</v>
+        <v>0.4351810597028645</v>
       </c>
       <c r="E36">
-        <v>357.8778190480903</v>
+        <v>363.1890360414601</v>
       </c>
       <c r="F36">
-        <v>43.08369841963486</v>
+        <v>39.83010036387219</v>
       </c>
       <c r="G36">
         <v>16</v>
@@ -3289,31 +3075,25 @@
         <v>-5.672820576479848</v>
       </c>
       <c r="Q36">
-        <v>-12.74115501477374</v>
+        <v>-16.45117967179156</v>
       </c>
       <c r="R36">
-        <v>-22.69128230591939</v>
+        <v>-27.22953876710327</v>
       </c>
       <c r="S36">
         <v>11.2</v>
       </c>
       <c r="T36">
-        <v>0.03134540163025619</v>
+        <v>799.9688724580296</v>
       </c>
       <c r="U36">
-        <v>-0.501526426084099</v>
+        <v>199.9922181145074</v>
       </c>
       <c r="V36">
-        <v>847.0258649555608</v>
+        <v>2133.250326554746</v>
       </c>
       <c r="W36">
-        <v>211.7564662388902</v>
-      </c>
-      <c r="X36">
-        <v>2258.735639881495</v>
-      </c>
-      <c r="Y36">
-        <v>1235.246227408512</v>
+        <v>1186.53682919157</v>
       </c>
     </row>
     <row r="37">
@@ -3326,16 +3106,16 @@
         <v>1.715449206349206</v>
       </c>
       <c r="C37">
-        <v>191.2306144316038</v>
+        <v>179.0746807723573</v>
       </c>
       <c r="D37">
-        <v>0.460733756643706</v>
+        <v>0.4713941864434524</v>
       </c>
       <c r="E37">
-        <v>170.3713651048544</v>
+        <v>158.7618523761666</v>
       </c>
       <c r="F37">
-        <v>20.85924932674931</v>
+        <v>20.31282839619072</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -3370,31 +3150,25 @@
         <v>-3.871129013415148</v>
       </c>
       <c r="Q37">
-        <v>-8.694555764130424</v>
+        <v>-11.22627413890393</v>
       </c>
       <c r="R37">
-        <v>-15.48451605366059</v>
+        <v>-18.58141926439271</v>
       </c>
       <c r="S37">
         <v>2</v>
       </c>
       <c r="T37">
-        <v>-0.08996755166593402</v>
+        <v>115.1339448338881</v>
       </c>
       <c r="U37">
-        <v>0.179935103331868</v>
+        <v>28.78348620847201</v>
       </c>
       <c r="V37">
-        <v>121.9065298241168</v>
+        <v>307.0238528903681</v>
       </c>
       <c r="W37">
-        <v>30.47663245602919</v>
-      </c>
-      <c r="X37">
-        <v>325.084079530978</v>
-      </c>
-      <c r="Y37">
-        <v>304.4425884915901</v>
+        <v>282.9823514673414</v>
       </c>
     </row>
     <row r="38">
@@ -3407,16 +3181,16 @@
         <v>1.729815079365079</v>
       </c>
       <c r="C38">
-        <v>158.2217374347612</v>
+        <v>175.9401597250164</v>
       </c>
       <c r="D38">
-        <v>0.6550482214981007</v>
+        <v>0.5705049226071159</v>
       </c>
       <c r="E38">
-        <v>127.7117142107444</v>
+        <v>148.5736822371986</v>
       </c>
       <c r="F38">
-        <v>30.51002322401678</v>
+        <v>27.3664774878178</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -3451,31 +3225,25 @@
         <v>-12.02161941213857</v>
       </c>
       <c r="Q38">
-        <v>-27.00055719966322</v>
+        <v>-34.86269629520184</v>
       </c>
       <c r="R38">
-        <v>-48.08647764855426</v>
+        <v>-57.70377317826512</v>
       </c>
       <c r="S38">
         <v>1.88135593220339</v>
       </c>
       <c r="T38">
-        <v>-0.08996755166593402</v>
+        <v>-391.0246525627841</v>
       </c>
       <c r="U38">
-        <v>0.179935103331868</v>
+        <v>-97.75616314069602</v>
       </c>
       <c r="V38">
-        <v>-414.0261027135361</v>
+        <v>-1042.732406834091</v>
       </c>
       <c r="W38">
-        <v>-103.506525678384</v>
-      </c>
-      <c r="X38">
-        <v>-1104.069607236096</v>
-      </c>
-      <c r="Y38">
-        <v>-282.8049224784381</v>
+        <v>-249.9471891329695</v>
       </c>
     </row>
     <row r="39">
@@ -3488,16 +3256,16 @@
         <v>5.756326587301587</v>
       </c>
       <c r="C39">
-        <v>502.7152670605612</v>
+        <v>568.1531050216819</v>
       </c>
       <c r="D39">
-        <v>0.6149379817733531</v>
+        <v>0.4661272433346796</v>
       </c>
       <c r="E39">
-        <v>414.7099187922122</v>
+        <v>504.9312466879447</v>
       </c>
       <c r="F39">
-        <v>88.005348268349</v>
+        <v>63.22185833373715</v>
       </c>
       <c r="G39">
         <v>8</v>
@@ -3532,31 +3300,25 @@
         <v>-7.880898590939847</v>
       </c>
       <c r="Q39">
-        <v>-17.7004982352509</v>
+        <v>-22.85460591372556</v>
       </c>
       <c r="R39">
-        <v>-31.52359436375939</v>
+        <v>-37.82831323651127</v>
       </c>
       <c r="S39">
         <v>6.915254237288136</v>
       </c>
       <c r="T39">
-        <v>-0.03797628596756679</v>
+        <v>-273.0250565140611</v>
       </c>
       <c r="U39">
-        <v>0.3038102877405343</v>
+        <v>-68.25626412851528</v>
       </c>
       <c r="V39">
-        <v>-289.0853539560648</v>
+        <v>-728.0668173708297</v>
       </c>
       <c r="W39">
-        <v>-72.27133848901619</v>
-      </c>
-      <c r="X39">
-        <v>-770.8942772161727</v>
-      </c>
-      <c r="Y39">
-        <v>195.9294148692456</v>
+        <v>272.2734425938952</v>
       </c>
     </row>
     <row r="40">
@@ -3569,16 +3331,16 @@
         <v>5.802690873015873</v>
       </c>
       <c r="C40">
-        <v>581.6810957243231</v>
+        <v>575.5891306580762</v>
       </c>
       <c r="D40">
-        <v>0.565800186321505</v>
+        <v>0.4968011189958311</v>
       </c>
       <c r="E40">
-        <v>492.3965017997072</v>
+        <v>504.2340106443602</v>
       </c>
       <c r="F40">
-        <v>89.28459392461588</v>
+        <v>71.35512001371598</v>
       </c>
       <c r="G40">
         <v>16</v>
@@ -3613,31 +3375,25 @@
         <v>-18.39557484712715</v>
       </c>
       <c r="Q40">
-        <v>-41.31646110664759</v>
+        <v>-53.34716705666875</v>
       </c>
       <c r="R40">
-        <v>-73.58229938850862</v>
+        <v>-88.29875926621034</v>
       </c>
       <c r="S40">
         <v>11.22033898305085</v>
       </c>
       <c r="T40">
-        <v>0.03134540163025619</v>
+        <v>204.5507074525101</v>
       </c>
       <c r="U40">
-        <v>-0.501526426084099</v>
+        <v>51.13767686312753</v>
       </c>
       <c r="V40">
-        <v>216.5831020085401</v>
+        <v>545.4685532066936</v>
       </c>
       <c r="W40">
-        <v>54.14577550213503</v>
-      </c>
-      <c r="X40">
-        <v>577.5549386894403</v>
-      </c>
-      <c r="Y40">
-        <v>756.9477366262156</v>
+        <v>726.7926710539176</v>
       </c>
     </row>
     <row r="41">
@@ -3650,16 +3406,16 @@
         <v>2.498323015873016</v>
       </c>
       <c r="C41">
-        <v>239.337890179783</v>
+        <v>264.8724827998727</v>
       </c>
       <c r="D41">
-        <v>0.5701998270414992</v>
+        <v>0.5561755448508273</v>
       </c>
       <c r="E41">
-        <v>202.1421082038789</v>
+        <v>225.3238302146827</v>
       </c>
       <c r="F41">
-        <v>37.19578197590408</v>
+        <v>39.54865258518996</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -3694,31 +3450,25 @@
         <v>-6.666178833161541</v>
       </c>
       <c r="Q41">
-        <v>-14.97223765928082</v>
+        <v>-19.33191861616847</v>
       </c>
       <c r="R41">
-        <v>-26.66471533264616</v>
+        <v>-31.9976583991754</v>
       </c>
       <c r="S41">
         <v>1</v>
       </c>
       <c r="T41">
-        <v>-0.0986327626156619</v>
+        <v>-966.0429212020487</v>
       </c>
       <c r="U41">
-        <v>0.0986327626156619</v>
+        <v>-241.5107303005122</v>
       </c>
       <c r="V41">
-        <v>-1022.868975390405</v>
+        <v>-2576.114456538796</v>
       </c>
       <c r="W41">
-        <v>-255.7172438476011</v>
-      </c>
-      <c r="X41">
-        <v>-2727.650601041079</v>
-      </c>
-      <c r="Y41">
-        <v>-798.5033228699024</v>
+        <v>-720.5023570183444</v>
       </c>
     </row>
     <row r="42">
@@ -3731,16 +3481,16 @@
         <v>1.808678571428572</v>
       </c>
       <c r="C42">
-        <v>105.58836874449</v>
+        <v>176.8275957080737</v>
       </c>
       <c r="D42">
-        <v>1.251970038946499</v>
+        <v>1.200818368266199</v>
       </c>
       <c r="E42">
-        <v>59.96764821199471</v>
+        <v>103.4919112060029</v>
       </c>
       <c r="F42">
-        <v>45.62072053249533</v>
+        <v>73.33568450207086</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -3775,31 +3525,25 @@
         <v>-13.87698207466623</v>
       </c>
       <c r="Q42">
-        <v>-31.16770173970035</v>
+        <v>-40.24324801653206</v>
       </c>
       <c r="R42">
-        <v>-55.50792829866491</v>
+        <v>-66.6095139583979</v>
       </c>
       <c r="S42">
         <v>1.932203389830508</v>
       </c>
       <c r="T42">
-        <v>-0.08996755166593402</v>
+        <v>-1141.569156945336</v>
       </c>
       <c r="U42">
-        <v>0.179935103331868</v>
+        <v>-285.3922892363341</v>
       </c>
       <c r="V42">
-        <v>-1208.720283824474</v>
+        <v>-3044.184418520897</v>
       </c>
       <c r="W42">
-        <v>-302.1800709561184</v>
-      </c>
-      <c r="X42">
-        <v>-3223.254090198596</v>
-      </c>
-      <c r="Y42">
-        <v>-1134.299616819684</v>
+        <v>-1004.984809253795</v>
       </c>
     </row>
     <row r="43">
@@ -3812,16 +3556,16 @@
         <v>2.961619841269841</v>
       </c>
       <c r="C43">
-        <v>219.8755784460432</v>
+        <v>292.0116349438413</v>
       </c>
       <c r="D43">
-        <v>0.8426233742519338</v>
+        <v>0.8501191074525598</v>
       </c>
       <c r="E43">
-        <v>159.3592115714147</v>
+        <v>210.7045849345145</v>
       </c>
       <c r="F43">
-        <v>60.51636687462849</v>
+        <v>81.30705000932684</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -3856,31 +3600,25 @@
         <v>-9.07755840019988</v>
       </c>
       <c r="Q43">
-        <v>-20.38819616684893</v>
+        <v>-26.32491936057965</v>
       </c>
       <c r="R43">
-        <v>-36.31023360079952</v>
+        <v>-43.57228032095942</v>
       </c>
       <c r="S43">
         <v>3.491525423728814</v>
       </c>
       <c r="T43">
-        <v>-0.07263712976647828</v>
+        <v>-1624.929458919247</v>
       </c>
       <c r="U43">
-        <v>0.2905485190659131</v>
+        <v>-406.2323647298118</v>
       </c>
       <c r="V43">
-        <v>-1720.513544738026</v>
+        <v>-4333.14522378466</v>
       </c>
       <c r="W43">
-        <v>-430.1283861845066</v>
-      </c>
-      <c r="X43">
-        <v>-4588.036119301404</v>
-      </c>
-      <c r="Y43">
-        <v>-1521.026162458832</v>
+        <v>-1359.242743335986</v>
       </c>
     </row>
     <row r="44">
@@ -3893,16 +3631,16 @@
         <v>3.942361904761905</v>
       </c>
       <c r="C44">
-        <v>392.8992316022807</v>
+        <v>413.2346424527939</v>
       </c>
       <c r="D44">
-        <v>0.5197142258595433</v>
+        <v>0.4695421996711477</v>
       </c>
       <c r="E44">
-        <v>340.3908204690578</v>
+        <v>366.6743099508213</v>
       </c>
       <c r="F44">
-        <v>52.50841113322292</v>
+        <v>46.5603325019726</v>
       </c>
       <c r="G44">
         <v>8</v>
@@ -3937,31 +3675,25 @@
         <v>-4.916329742993625</v>
       </c>
       <c r="Q44">
-        <v>-11.04207660276368</v>
+        <v>-14.25735625468151</v>
       </c>
       <c r="R44">
-        <v>-19.6653189719745</v>
+        <v>-23.5983827663694</v>
       </c>
       <c r="S44">
         <v>6.35593220338983</v>
       </c>
       <c r="T44">
-        <v>-0.03797628596756679</v>
+        <v>-931.5429266587793</v>
       </c>
       <c r="U44">
-        <v>0.3038102877405343</v>
+        <v>-232.8857316646948</v>
       </c>
       <c r="V44">
-        <v>-986.3395694034133</v>
+        <v>-2484.114471090078</v>
       </c>
       <c r="W44">
-        <v>-246.5848923508533</v>
-      </c>
-      <c r="X44">
-        <v>-2630.238851742436</v>
-      </c>
-      <c r="Y44">
-        <v>-604.4824144038963</v>
+        <v>-532.5656404606669</v>
       </c>
     </row>
     <row r="45">
@@ -3974,16 +3706,16 @@
         <v>5.839504365079365</v>
       </c>
       <c r="C45">
-        <v>419.1321428583452</v>
+        <v>574.7102328907465</v>
       </c>
       <c r="D45">
-        <v>0.6815696083708351</v>
+        <v>0.4831526210202264</v>
       </c>
       <c r="E45">
-        <v>333.3732397249591</v>
+        <v>506.7326196642649</v>
       </c>
       <c r="F45">
-        <v>85.75890313338613</v>
+        <v>67.97761322648159</v>
       </c>
       <c r="G45">
         <v>8</v>
@@ -4018,31 +3750,25 @@
         <v>-7.346761773217376</v>
       </c>
       <c r="Q45">
-        <v>-16.50082694264623</v>
+        <v>-21.30560914233039</v>
       </c>
       <c r="R45">
-        <v>-29.3870470928695</v>
+        <v>-35.26445651144341</v>
       </c>
       <c r="S45">
         <v>5.491525423728813</v>
       </c>
       <c r="T45">
-        <v>-0.03797628596756679</v>
+        <v>-28.55696837950058</v>
       </c>
       <c r="U45">
-        <v>0.3038102877405343</v>
+        <v>-7.139242094875145</v>
       </c>
       <c r="V45">
-        <v>-30.23679004888297</v>
+        <v>-76.15191567866822</v>
       </c>
       <c r="W45">
-        <v>-7.559197512220742</v>
-      </c>
-      <c r="X45">
-        <v>-80.63144013035458</v>
-      </c>
-      <c r="Y45">
-        <v>372.394525866816</v>
+        <v>524.8476553689155</v>
       </c>
     </row>
     <row r="46">
@@ -4055,16 +3781,16 @@
         <v>2.838361904761905</v>
       </c>
       <c r="C46">
-        <v>243.2980284533024</v>
+        <v>279.4587091982777</v>
       </c>
       <c r="D46">
-        <v>0.7641403259561864</v>
+        <v>0.670426792632747</v>
       </c>
       <c r="E46">
-        <v>184.6291274424928</v>
+        <v>223.6617586294217</v>
       </c>
       <c r="F46">
-        <v>58.66890101080963</v>
+        <v>55.79695056885603</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -4099,31 +3825,25 @@
         <v>-3.615948969151304</v>
       </c>
       <c r="Q46">
-        <v>-8.121421384713829</v>
+        <v>-10.48625201053878</v>
       </c>
       <c r="R46">
-        <v>-14.46379587660521</v>
+        <v>-17.35655505192626</v>
       </c>
       <c r="S46">
         <v>1</v>
       </c>
       <c r="T46">
-        <v>-0.0986327626156619</v>
+        <v>-794.2045027091767</v>
       </c>
       <c r="U46">
-        <v>0.0986327626156619</v>
+        <v>-198.5511256772942</v>
       </c>
       <c r="V46">
-        <v>-840.922414633246</v>
+        <v>-2117.878673891138</v>
       </c>
       <c r="W46">
-        <v>-210.2306036583115</v>
-      </c>
-      <c r="X46">
-        <v>-2242.459772355323</v>
-      </c>
-      <c r="Y46">
-        <v>-605.7458075646574</v>
+        <v>-525.2320455214378</v>
       </c>
     </row>
     <row r="47">
@@ -4136,16 +3856,16 @@
         <v>6.073994444444445</v>
       </c>
       <c r="C47">
-        <v>520.956237778267</v>
+        <v>606.303395001484</v>
       </c>
       <c r="D47">
-        <v>0.6325035561438457</v>
+        <v>0.5410559028991293</v>
       </c>
       <c r="E47">
-        <v>425.7092770876124</v>
+        <v>519.736224828245</v>
       </c>
       <c r="F47">
-        <v>95.24696069065459</v>
+        <v>86.56717017323899</v>
       </c>
       <c r="G47">
         <v>8</v>
@@ -4180,31 +3900,25 @@
         <v>-6.179629133071668</v>
       </c>
       <c r="Q47">
-        <v>-13.87944703287897</v>
+        <v>-17.92092448590784</v>
       </c>
       <c r="R47">
-        <v>-24.71851653228667</v>
+        <v>-29.66221983874401</v>
       </c>
       <c r="S47">
         <v>6.203389830508475</v>
       </c>
       <c r="T47">
-        <v>-0.03797628596756679</v>
+        <v>-13.28549215938822</v>
       </c>
       <c r="U47">
-        <v>0.3038102877405343</v>
+        <v>-3.321373039847054</v>
       </c>
       <c r="V47">
-        <v>-14.06699169817576</v>
+        <v>-35.42797909170191</v>
       </c>
       <c r="W47">
-        <v>-3.516747924543939</v>
-      </c>
-      <c r="X47">
-        <v>-37.51197786180202</v>
-      </c>
-      <c r="Y47">
-        <v>493.0097990472123</v>
+        <v>575.0969783561879</v>
       </c>
     </row>
     <row r="48">
@@ -4217,16 +3931,16 @@
         <v>2.615027777777778</v>
       </c>
       <c r="C48">
-        <v>248.3554896342183</v>
+        <v>263.4350587249479</v>
       </c>
       <c r="D48">
-        <v>0.705076830229782</v>
+        <v>0.6955641178841452</v>
       </c>
       <c r="E48">
-        <v>194.9474126271545</v>
+        <v>207.8962680971215</v>
       </c>
       <c r="F48">
-        <v>53.40807700706381</v>
+        <v>55.53879062782633</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -4261,31 +3975,25 @@
         <v>-5.397599986973854</v>
       </c>
       <c r="Q48">
-        <v>-12.12300957074328</v>
+        <v>-15.65303996222418</v>
       </c>
       <c r="R48">
-        <v>-21.59039994789542</v>
+        <v>-25.9084799374745</v>
       </c>
       <c r="S48">
         <v>1.864406779661017</v>
       </c>
       <c r="T48">
-        <v>-0.08996755166593402</v>
+        <v>-907.9343167996072</v>
       </c>
       <c r="U48">
-        <v>0.179935103331868</v>
+        <v>-226.9835791999018</v>
       </c>
       <c r="V48">
-        <v>-961.3422177878194</v>
+        <v>-2421.158178132286</v>
       </c>
       <c r="W48">
-        <v>-240.3355544469549</v>
-      </c>
-      <c r="X48">
-        <v>-2563.579247434185</v>
-      </c>
-      <c r="Y48">
-        <v>-725.1097377243444</v>
+        <v>-660.1522980368836</v>
       </c>
     </row>
     <row r="49">
@@ -4298,16 +4006,16 @@
         <v>4.413233730158731</v>
       </c>
       <c r="C49">
-        <v>498.1933266502572</v>
+        <v>473.4943466114673</v>
       </c>
       <c r="D49">
-        <v>0.3094136792719699</v>
+        <v>0.3150807368421378</v>
       </c>
       <c r="E49">
-        <v>471.6003854329633</v>
+        <v>447.353439584931</v>
       </c>
       <c r="F49">
-        <v>26.59294121729391</v>
+        <v>26.1409070265363</v>
       </c>
       <c r="G49">
         <v>16</v>
@@ -4342,31 +4050,25 @@
         <v>-4.048880110779567</v>
       </c>
       <c r="Q49">
-        <v>-9.093784728810908</v>
+        <v>-11.74175232126074</v>
       </c>
       <c r="R49">
-        <v>-16.19552044311827</v>
+        <v>-19.43462453174192</v>
       </c>
       <c r="S49">
         <v>11.5</v>
       </c>
       <c r="T49">
-        <v>0.03134540163025619</v>
+        <v>-13.44608419750229</v>
       </c>
       <c r="U49">
-        <v>-0.501526426084099</v>
+        <v>-3.361521049375571</v>
       </c>
       <c r="V49">
-        <v>-14.23703032676713</v>
+        <v>-35.85622452667276</v>
       </c>
       <c r="W49">
-        <v>-3.559257581691782</v>
-      </c>
-      <c r="X49">
-        <v>-37.96541420471234</v>
-      </c>
-      <c r="Y49">
-        <v>474.8625115946792</v>
+        <v>448.3065100927043</v>
       </c>
     </row>
     <row r="50">
@@ -4379,16 +4081,16 @@
         <v>3.290001984126984</v>
       </c>
       <c r="C50">
-        <v>355.9231088201439</v>
+        <v>356.5055791546645</v>
       </c>
       <c r="D50">
-        <v>0.3263539200756922</v>
+        <v>0.3420029303696343</v>
       </c>
       <c r="E50">
-        <v>334.9528787435012</v>
+        <v>333.6125329626454</v>
       </c>
       <c r="F50">
-        <v>20.97023007664274</v>
+        <v>22.89304619201909</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -4423,31 +4125,25 @@
         <v>-5.836044713259972</v>
       </c>
       <c r="Q50">
-        <v>-13.1077564259819</v>
+        <v>-16.92452966845392</v>
       </c>
       <c r="R50">
-        <v>-23.34417885303989</v>
+        <v>-28.01301462364787</v>
       </c>
       <c r="S50">
         <v>3.254237288135593</v>
       </c>
       <c r="T50">
-        <v>-0.07263712976647828</v>
+        <v>38.77324499785593</v>
       </c>
       <c r="U50">
-        <v>0.2905485190659131</v>
+        <v>9.693311249463981</v>
       </c>
       <c r="V50">
-        <v>41.05402411537687</v>
+        <v>103.3953199942825</v>
       </c>
       <c r="W50">
-        <v>10.26350602884422</v>
-      </c>
-      <c r="X50">
-        <v>109.477397641005</v>
-      </c>
-      <c r="Y50">
-        <v>383.8693765095389</v>
+        <v>378.3542944840665</v>
       </c>
     </row>
     <row r="51">
@@ -4460,16 +4156,16 @@
         <v>1.466324603174603</v>
       </c>
       <c r="C51">
-        <v>100.6352978319743</v>
+        <v>137.4035013533133</v>
       </c>
       <c r="D51">
-        <v>0.9622102714149059</v>
+        <v>0.8889942869013838</v>
       </c>
       <c r="E51">
-        <v>67.91677415783586</v>
+        <v>96.88147330183328</v>
       </c>
       <c r="F51">
-        <v>32.71852367413847</v>
+        <v>40.52202805147998</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -4504,31 +4200,25 @@
         <v>-40.19009203302244</v>
       </c>
       <c r="Q51">
-        <v>-90.2669467061684</v>
+        <v>-116.5512668957651</v>
       </c>
       <c r="R51">
-        <v>-160.7603681320898</v>
+        <v>-192.9124417585077</v>
       </c>
       <c r="S51">
         <v>1</v>
       </c>
       <c r="T51">
-        <v>-0.0986327626156619</v>
+        <v>-459.991635634027</v>
       </c>
       <c r="U51">
-        <v>0.0986327626156619</v>
+        <v>-114.9979089085068</v>
       </c>
       <c r="V51">
-        <v>-487.049967141911</v>
+        <v>-1226.644361690739</v>
       </c>
       <c r="W51">
-        <v>-121.7624917854777</v>
-      </c>
-      <c r="X51">
-        <v>-1298.799912378429</v>
-      </c>
-      <c r="Y51">
-        <v>-476.6816160161051</v>
+        <v>-439.1394011764789</v>
       </c>
     </row>
     <row r="52">
@@ -4541,16 +4231,16 @@
         <v>3.722611111111111</v>
       </c>
       <c r="C52">
-        <v>384.1636853642574</v>
+        <v>399.5167381290545</v>
       </c>
       <c r="D52">
-        <v>0.3663527147989356</v>
+        <v>0.392666266310928</v>
       </c>
       <c r="E52">
-        <v>356.2043634783932</v>
+        <v>366.5804652467775</v>
       </c>
       <c r="F52">
-        <v>27.9593218858642</v>
+        <v>32.93627288227702</v>
       </c>
       <c r="G52">
         <v>4</v>
@@ -4585,31 +4275,25 @@
         <v>-5.727050558876873</v>
       </c>
       <c r="Q52">
-        <v>-12.86295555523746</v>
+        <v>-16.60844662074293</v>
       </c>
       <c r="R52">
-        <v>-22.90820223550749</v>
+        <v>-27.48984268260899</v>
       </c>
       <c r="S52">
         <v>3.033898305084746</v>
       </c>
       <c r="T52">
-        <v>-0.07263712976647828</v>
+        <v>-531.4328454065576</v>
       </c>
       <c r="U52">
-        <v>0.2905485190659131</v>
+        <v>-132.8582113516394</v>
       </c>
       <c r="V52">
-        <v>-562.6936010187081</v>
+        <v>-1417.154254417487</v>
       </c>
       <c r="W52">
-        <v>-140.673400254677</v>
-      </c>
-      <c r="X52">
-        <v>-1500.516269383222</v>
-      </c>
-      <c r="Y52">
-        <v>-191.3928712096882</v>
+        <v>-148.524553898246</v>
       </c>
     </row>
     <row r="53">
@@ -4622,16 +4306,16 @@
         <v>5.690806746031746</v>
       </c>
       <c r="C53">
-        <v>504.238268214851</v>
+        <v>599.2133628970912</v>
       </c>
       <c r="D53">
-        <v>0.5083215035773628</v>
+        <v>0.5184715306626632</v>
       </c>
       <c r="E53">
-        <v>439.2851194108846</v>
+        <v>519.4490710126141</v>
       </c>
       <c r="F53">
-        <v>64.95314880396637</v>
+        <v>79.76429188447707</v>
       </c>
       <c r="G53">
         <v>16</v>
@@ -4666,31 +4350,25 @@
         <v>-8.134438287936586</v>
       </c>
       <c r="Q53">
-        <v>-18.26994839470557</v>
+        <v>-23.5898710350161</v>
       </c>
       <c r="R53">
-        <v>-32.53775315174634</v>
+        <v>-39.04530378209561</v>
       </c>
       <c r="S53">
         <v>10.33898305084746</v>
       </c>
       <c r="T53">
-        <v>0.03134540163025619</v>
+        <v>-203.5334048808638</v>
       </c>
       <c r="U53">
-        <v>-0.501526426084099</v>
+        <v>-50.88335122021595</v>
       </c>
       <c r="V53">
-        <v>-215.5059581091499</v>
+        <v>-542.7557463489701</v>
       </c>
       <c r="W53">
-        <v>-53.87648952728748</v>
-      </c>
-      <c r="X53">
-        <v>-574.682554957733</v>
-      </c>
-      <c r="Y53">
-        <v>270.4623617109955</v>
+        <v>372.0900869812113</v>
       </c>
     </row>
     <row r="54">
@@ -4703,16 +4381,16 @@
         <v>0.7614388888888889</v>
       </c>
       <c r="C54">
-        <v>40.79085873113207</v>
+        <v>74.74924632269337</v>
       </c>
       <c r="D54">
-        <v>1.546211393826185</v>
+        <v>1.57066084700116</v>
       </c>
       <c r="E54">
-        <v>19.60576866682831</v>
+        <v>35.451641983204</v>
       </c>
       <c r="F54">
-        <v>21.18509006430376</v>
+        <v>39.29760433948937</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -4747,31 +4425,25 @@
         <v>-17.0237604403544</v>
       </c>
       <c r="Q54">
-        <v>-38.23536594903599</v>
+        <v>-49.36890527702777</v>
       </c>
       <c r="R54">
-        <v>-68.0950417614176</v>
+        <v>-81.71405011370113</v>
       </c>
       <c r="S54">
         <v>1</v>
       </c>
       <c r="T54">
-        <v>-0.0986327626156619</v>
+        <v>-513.3567931933326</v>
       </c>
       <c r="U54">
-        <v>0.0986327626156619</v>
+        <v>-128.3391982983331</v>
       </c>
       <c r="V54">
-        <v>-543.5542516164697</v>
+        <v>-1368.951448515553</v>
       </c>
       <c r="W54">
-        <v>-135.8885629041174</v>
-      </c>
-      <c r="X54">
-        <v>-1449.478004310586</v>
-      </c>
-      <c r="Y54">
-        <v>-540.9987588343737</v>
+        <v>-487.976452147667</v>
       </c>
     </row>
     <row r="55">
@@ -4784,16 +4456,16 @@
         <v>1.497456349206349</v>
       </c>
       <c r="C55">
-        <v>135.1974232060544</v>
+        <v>150.3578009567313</v>
       </c>
       <c r="D55">
-        <v>0.6031480800862945</v>
+        <v>0.550547410568094</v>
       </c>
       <c r="E55">
-        <v>112.2329479970225</v>
+        <v>128.2740563103069</v>
       </c>
       <c r="F55">
-        <v>22.96447520903182</v>
+        <v>22.08374464642444</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -4828,31 +4500,25 @@
         <v>-8.513612661198213</v>
       </c>
       <c r="Q55">
-        <v>-19.12157403705119</v>
+        <v>-24.68947671747482</v>
       </c>
       <c r="R55">
-        <v>-34.05445064479285</v>
+        <v>-40.86534077375143</v>
       </c>
       <c r="S55">
         <v>1.983050847457627</v>
       </c>
       <c r="T55">
-        <v>-0.08996755166593402</v>
+        <v>-847.4048581032467</v>
       </c>
       <c r="U55">
-        <v>0.179935103331868</v>
+        <v>-211.8512145258117</v>
       </c>
       <c r="V55">
-        <v>-897.2522026975554</v>
+        <v>-2259.746288275325</v>
       </c>
       <c r="W55">
-        <v>-224.3130506743888</v>
-      </c>
-      <c r="X55">
-        <v>-2392.672540526814</v>
-      </c>
-      <c r="Y55">
-        <v>-781.1763535285522</v>
+        <v>-721.7365338639902</v>
       </c>
     </row>
     <row r="56">
@@ -4865,16 +4531,16 @@
         <v>4.94229126984127</v>
       </c>
       <c r="C56">
-        <v>565.9330809234908</v>
+        <v>519.0974594836642</v>
       </c>
       <c r="D56">
-        <v>0.4412435084188968</v>
+        <v>0.4377367241241371</v>
       </c>
       <c r="E56">
-        <v>508.6401882712537</v>
+        <v>467.2697511388687</v>
       </c>
       <c r="F56">
-        <v>57.29289265223713</v>
+        <v>51.8277083447955</v>
       </c>
       <c r="G56">
         <v>8</v>
@@ -4909,31 +4575,25 @@
         <v>-17.60072454043722</v>
       </c>
       <c r="Q56">
-        <v>-39.531227317822</v>
+        <v>-51.04210116726794</v>
       </c>
       <c r="R56">
-        <v>-70.40289816174888</v>
+        <v>-84.48347779409866</v>
       </c>
       <c r="S56">
         <v>5.186440677966102</v>
       </c>
       <c r="T56">
-        <v>-0.03797628596756679</v>
+        <v>-639.6921167376527</v>
       </c>
       <c r="U56">
-        <v>0.3038102877405343</v>
+        <v>-159.9230291844132</v>
       </c>
       <c r="V56">
-        <v>-677.321064781044</v>
+        <v>-1705.84564463374</v>
       </c>
       <c r="W56">
-        <v>-169.330266195261</v>
-      </c>
-      <c r="X56">
-        <v>-1806.189506082784</v>
-      </c>
-      <c r="Y56">
-        <v>-150.9192111753752</v>
+        <v>-171.6367584212563</v>
       </c>
     </row>
     <row r="57">
@@ -4946,16 +4606,16 @@
         <v>2.526490079365079</v>
       </c>
       <c r="C57">
-        <v>235.4075546539495</v>
+        <v>257.2054894904381</v>
       </c>
       <c r="D57">
-        <v>0.8813526513792739</v>
+        <v>0.9530225769130095</v>
       </c>
       <c r="E57">
-        <v>166.7400148158484</v>
+        <v>174.5415359090369</v>
       </c>
       <c r="F57">
-        <v>68.66753983810102</v>
+        <v>82.66395358140124</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -4990,31 +4650,25 @@
         <v>-39.83697885336878</v>
       </c>
       <c r="Q57">
-        <v>-89.47385450466628</v>
+        <v>-115.5272386747695</v>
       </c>
       <c r="R57">
-        <v>-159.3479154134751</v>
+        <v>-191.2174984961702</v>
       </c>
       <c r="S57">
         <v>1.983050847457627</v>
       </c>
       <c r="T57">
-        <v>-0.08996755166593402</v>
+        <v>-262.5861493309494</v>
       </c>
       <c r="U57">
-        <v>0.179935103331868</v>
+        <v>-65.64653733273735</v>
       </c>
       <c r="V57">
-        <v>-278.0323934092406</v>
+        <v>-700.2297315491984</v>
       </c>
       <c r="W57">
-        <v>-69.50809835231014</v>
-      </c>
-      <c r="X57">
-        <v>-741.4197157579748</v>
-      </c>
-      <c r="Y57">
-        <v>-132.0986932599574</v>
+        <v>-120.9078985152807</v>
       </c>
     </row>
     <row r="58">
@@ -5027,16 +4681,16 @@
         <v>5.871413174603175</v>
       </c>
       <c r="C58">
-        <v>533.0183466937839</v>
+        <v>580.9254419945478</v>
       </c>
       <c r="D58">
-        <v>0.6225720766571092</v>
+        <v>0.4838736792954186</v>
       </c>
       <c r="E58">
-        <v>437.9094689542681</v>
+        <v>512.0390253260225</v>
       </c>
       <c r="F58">
-        <v>95.10887773951578</v>
+        <v>68.88641666852527</v>
       </c>
       <c r="G58">
         <v>16</v>
@@ -5071,31 +4725,25 @@
         <v>-8.5251765194656</v>
       </c>
       <c r="Q58">
-        <v>-19.14754646271974</v>
+        <v>-24.72301190645024</v>
       </c>
       <c r="R58">
-        <v>-34.1007060778624</v>
+        <v>-40.92084729343487</v>
       </c>
       <c r="S58">
         <v>12.3</v>
       </c>
       <c r="T58">
-        <v>0.03134540163025619</v>
+        <v>-30.98620230848367</v>
       </c>
       <c r="U58">
-        <v>-0.501526426084099</v>
+        <v>-7.746550577120918</v>
       </c>
       <c r="V58">
-        <v>-32.80892009133566</v>
+        <v>-82.62987282262313</v>
       </c>
       <c r="W58">
-        <v>-8.202230022833914</v>
-      </c>
-      <c r="X58">
-        <v>-87.49045357689509</v>
-      </c>
-      <c r="Y58">
-        <v>481.0618801397285</v>
+        <v>525.2162277796139</v>
       </c>
     </row>
     <row r="59">
@@ -5108,16 +4756,16 @@
         <v>3.700146031746032</v>
       </c>
       <c r="C59">
-        <v>321.7125004316547</v>
+        <v>399.4953343656799</v>
       </c>
       <c r="D59">
-        <v>0.5839628446926173</v>
+        <v>0.6306904904028244</v>
       </c>
       <c r="E59">
-        <v>269.7790495529365</v>
+        <v>326.7760285968058</v>
       </c>
       <c r="F59">
-        <v>51.93345087871819</v>
+        <v>72.71930576887411</v>
       </c>
       <c r="G59">
         <v>4</v>
@@ -5152,31 +4800,25 @@
         <v>-5.948729477843169</v>
       </c>
       <c r="Q59">
-        <v>-13.36084640723576</v>
+        <v>-17.25131548574519</v>
       </c>
       <c r="R59">
-        <v>-23.79491791137267</v>
+        <v>-28.55390149364721</v>
       </c>
       <c r="S59">
         <v>3.416666666666667</v>
       </c>
       <c r="T59">
-        <v>-0.07263712976647828</v>
+        <v>198.2104816727272</v>
       </c>
       <c r="U59">
-        <v>0.2905485190659131</v>
+        <v>49.55262041818181</v>
       </c>
       <c r="V59">
-        <v>209.869921771123</v>
+        <v>528.561284460606</v>
       </c>
       <c r="W59">
-        <v>52.46748044278074</v>
-      </c>
-      <c r="X59">
-        <v>559.6531247229946</v>
-      </c>
-      <c r="Y59">
-        <v>518.2215757955419</v>
+        <v>580.4545005526619</v>
       </c>
     </row>
     <row r="60">
@@ -5189,16 +4831,16 @@
         <v>5.847208333333334</v>
       </c>
       <c r="C60">
-        <v>613.6993391377227</v>
+        <v>615.0835647355232</v>
       </c>
       <c r="D60">
-        <v>0.3249917787566381</v>
+        <v>0.2997586926792622</v>
       </c>
       <c r="E60">
-        <v>577.8195143108509</v>
+        <v>584.1344561822083</v>
       </c>
       <c r="F60">
-        <v>35.87982482687187</v>
+        <v>30.94910855331489</v>
       </c>
       <c r="G60">
         <v>16</v>
@@ -5233,31 +4875,25 @@
         <v>-9.693948763882558</v>
       </c>
       <c r="Q60">
-        <v>-21.77260892368022</v>
+        <v>-28.11245141525941</v>
       </c>
       <c r="R60">
-        <v>-38.77579505553023</v>
+        <v>-46.53095406663628</v>
       </c>
       <c r="S60">
         <v>11.28813559322034</v>
       </c>
       <c r="T60">
-        <v>0.03134540163025619</v>
+        <v>150.8143772717958</v>
       </c>
       <c r="U60">
-        <v>-0.501526426084099</v>
+        <v>37.70359431794895</v>
       </c>
       <c r="V60">
-        <v>159.6858112289603</v>
+        <v>402.1716727247888</v>
       </c>
       <c r="W60">
-        <v>39.92145280724007</v>
-      </c>
-      <c r="X60">
-        <v>425.8288299438941</v>
-      </c>
-      <c r="Y60">
-        <v>751.6125414430028</v>
+        <v>737.7854905920595</v>
       </c>
     </row>
     <row r="61">
@@ -5270,16 +4906,16 @@
         <v>3.230436212698413</v>
       </c>
       <c r="C61">
-        <v>353.5780796588469</v>
+        <v>350.2490443669753</v>
       </c>
       <c r="D61">
-        <v>0.2637204468582484</v>
+        <v>0.3247363896757173</v>
       </c>
       <c r="E61">
-        <v>339.5979416705142</v>
+        <v>329.8014943043372</v>
       </c>
       <c r="F61">
-        <v>13.98013798833267</v>
+        <v>20.44755006263813</v>
       </c>
       <c r="G61">
         <v>16</v>
@@ -5314,31 +4950,25 @@
         <v>-3.609975225762181</v>
       </c>
       <c r="Q61">
-        <v>-8.10800435706186</v>
+        <v>-10.46892815471033</v>
       </c>
       <c r="R61">
-        <v>-14.43990090304873</v>
+        <v>-17.32788108365847</v>
       </c>
       <c r="S61">
         <v>13</v>
       </c>
       <c r="T61">
-        <v>0.03134540163025619</v>
+        <v>841.474237757583</v>
       </c>
       <c r="U61">
-        <v>-0.501526426084099</v>
+        <v>210.3685594393957</v>
       </c>
       <c r="V61">
-        <v>890.9727223315584</v>
+        <v>2243.931300686888</v>
       </c>
       <c r="W61">
-        <v>222.7431805828896</v>
-      </c>
-      <c r="X61">
-        <v>2375.927259550822</v>
-      </c>
-      <c r="Y61">
-        <v>1236.442797633343</v>
+        <v>1181.254353969848</v>
       </c>
     </row>
     <row r="62">
@@ -5351,16 +4981,16 @@
         <v>0.05161785714285715</v>
       </c>
       <c r="C62">
-        <v>4.094234458631806</v>
+        <v>4.124421623540979</v>
       </c>
       <c r="D62">
-        <v>0.882514098852932</v>
+        <v>0.8718211300659418</v>
       </c>
       <c r="E62">
-        <v>2.897956590969642</v>
+        <v>2.937952584325763</v>
       </c>
       <c r="F62">
-        <v>1.196277867662163</v>
+        <v>1.186469039215216</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5395,31 +5025,25 @@
         <v>-6.461993530328306</v>
       </c>
       <c r="Q62">
-        <v>-14.51363746911738</v>
+        <v>-18.73978123795209</v>
       </c>
       <c r="R62">
-        <v>-25.84797412131323</v>
+        <v>-31.01756894557587</v>
       </c>
       <c r="S62">
         <v>0.8571428571428571</v>
       </c>
       <c r="T62">
-        <v>-0.0986327626156619</v>
+        <v>-587.0267300596598</v>
       </c>
       <c r="U62">
-        <v>0.0986327626156619</v>
+        <v>-146.756682514915</v>
       </c>
       <c r="V62">
-        <v>-621.5577141808162</v>
+        <v>-1565.404613492426</v>
       </c>
       <c r="W62">
-        <v>-155.3894285452041</v>
-      </c>
-      <c r="X62">
-        <v>-1657.48723781551</v>
-      </c>
-      <c r="Y62">
-        <v>-631.9771171913018</v>
+        <v>-601.6420896740709</v>
       </c>
     </row>
     <row r="63">
@@ -5432,16 +5056,16 @@
         <v>3.127399603174603</v>
       </c>
       <c r="C63">
-        <v>331.2155702051887</v>
+        <v>337.9065417724732</v>
       </c>
       <c r="D63">
-        <v>0.4076793871889568</v>
+        <v>0.4021484694905896</v>
       </c>
       <c r="E63">
-        <v>302.0274162879984</v>
+        <v>308.8410065798885</v>
       </c>
       <c r="F63">
-        <v>29.18815391719033</v>
+        <v>29.06553519258472</v>
       </c>
       <c r="G63">
         <v>4</v>
@@ -5476,31 +5100,25 @@
         <v>-22.71769917888244</v>
       </c>
       <c r="Q63">
-        <v>-51.02395235576996</v>
+        <v>-65.88132761875907</v>
       </c>
       <c r="R63">
-        <v>-90.87079671552976</v>
+        <v>-109.0449560586357</v>
       </c>
       <c r="S63">
         <v>2.95</v>
       </c>
       <c r="T63">
-        <v>-0.07263712976647828</v>
+        <v>-1087.409657566273</v>
       </c>
       <c r="U63">
-        <v>0.2905485190659131</v>
+        <v>-271.8524143915683</v>
       </c>
       <c r="V63">
-        <v>-1151.37493154076</v>
+        <v>-2899.759086843396</v>
       </c>
       <c r="W63">
-        <v>-287.84373288519</v>
-      </c>
-      <c r="X63">
-        <v>-3070.333150775361</v>
-      </c>
-      <c r="Y63">
-        <v>-871.1833136913415</v>
+        <v>-815.3844434125592</v>
       </c>
     </row>
     <row r="64">
@@ -5513,16 +5131,16 @@
         <v>1.622862301587302</v>
       </c>
       <c r="C64">
-        <v>166.4771215457227</v>
+        <v>170.4240910174726</v>
       </c>
       <c r="D64">
-        <v>0.3957112148469318</v>
+        <v>0.363350988452983</v>
       </c>
       <c r="E64">
-        <v>152.562392893685</v>
+        <v>158.2040580512468</v>
       </c>
       <c r="F64">
-        <v>13.91472865203772</v>
+        <v>12.2200329662258</v>
       </c>
       <c r="G64">
         <v>8</v>
@@ -5557,31 +5175,25 @@
         <v>-8.597738119987069</v>
       </c>
       <c r="Q64">
-        <v>-19.31051981749096</v>
+        <v>-24.9334405479625</v>
       </c>
       <c r="R64">
-        <v>-34.39095247994828</v>
+        <v>-41.26914297593793</v>
       </c>
       <c r="S64">
         <v>7.689655172413793</v>
       </c>
       <c r="T64">
-        <v>-0.03797628596756679</v>
+        <v>858.0909074004417</v>
       </c>
       <c r="U64">
-        <v>0.3038102877405343</v>
+        <v>214.5227268501104</v>
       </c>
       <c r="V64">
-        <v>908.5668431298793</v>
+        <v>2288.242419734511</v>
       </c>
       <c r="W64">
-        <v>227.1417107824698</v>
-      </c>
-      <c r="X64">
-        <v>2422.844915013011</v>
-      </c>
-      <c r="Y64">
-        <v>1055.733444858111</v>
+        <v>1003.581557869952</v>
       </c>
     </row>
     <row r="65">
@@ -5594,16 +5206,16 @@
         <v>2.060706746031746</v>
       </c>
       <c r="C65">
-        <v>144.0626619340843</v>
+        <v>186.3354500932518</v>
       </c>
       <c r="D65">
-        <v>0.9779911964428544</v>
+        <v>0.8235544356909044</v>
       </c>
       <c r="E65">
-        <v>96.3092383487875</v>
+        <v>136.5786292195064</v>
       </c>
       <c r="F65">
-        <v>47.7534235852968</v>
+        <v>49.75682087374545</v>
       </c>
       <c r="G65">
         <v>4</v>
@@ -5638,31 +5250,25 @@
         <v>-31.22476653477719</v>
       </c>
       <c r="Q65">
-        <v>-70.13082563710958</v>
+        <v>-90.55182295085386</v>
       </c>
       <c r="R65">
-        <v>-124.8990661391088</v>
+        <v>-149.8788793669305</v>
       </c>
       <c r="S65">
         <v>2.694915254237288</v>
       </c>
       <c r="T65">
-        <v>-0.07263712976647828</v>
+        <v>-103.0166085441775</v>
       </c>
       <c r="U65">
-        <v>0.2905485190659131</v>
+        <v>-25.75415213604437</v>
       </c>
       <c r="V65">
-        <v>-109.0764090467761</v>
+        <v>-274.7109561178066</v>
       </c>
       <c r="W65">
-        <v>-27.26910226169403</v>
-      </c>
-      <c r="X65">
-        <v>-290.8704241247364</v>
-      </c>
-      <c r="Y65">
-        <v>-35.1445727498014</v>
+        <v>-7.23298140177954</v>
       </c>
     </row>
     <row r="66">
@@ -5675,16 +5281,16 @@
         <v>1.768886904761905</v>
       </c>
       <c r="C66">
-        <v>187.9109281360244</v>
+        <v>186.8540138193211</v>
       </c>
       <c r="D66">
-        <v>0.4355757245587996</v>
+        <v>0.4007894481461658</v>
       </c>
       <c r="E66">
-        <v>169.3104716938524</v>
+        <v>170.87780879856</v>
       </c>
       <c r="F66">
-        <v>18.600456442172</v>
+        <v>15.97620502076103</v>
       </c>
       <c r="G66">
         <v>8</v>
@@ -5719,31 +5325,25 @@
         <v>-7.827326320892669</v>
       </c>
       <c r="Q66">
-        <v>-17.58017491672494</v>
+        <v>-22.69924633058874</v>
       </c>
       <c r="R66">
-        <v>-31.30930528357068</v>
+        <v>-37.57116634028481</v>
       </c>
       <c r="S66">
         <v>6.677966101694915</v>
       </c>
       <c r="T66">
-        <v>-0.03797628596756679</v>
+        <v>-350.5494967596808</v>
       </c>
       <c r="U66">
-        <v>0.3038102877405343</v>
+        <v>-87.63737418992019</v>
       </c>
       <c r="V66">
-        <v>-371.1700553926032</v>
+        <v>-934.7986580258154</v>
       </c>
       <c r="W66">
-        <v>-92.79251384815079</v>
-      </c>
-      <c r="X66">
-        <v>-989.7868143802751</v>
-      </c>
-      <c r="Y66">
-        <v>-200.8393021733037</v>
+        <v>-186.3947292709484</v>
       </c>
     </row>
     <row r="67">
@@ -5756,16 +5356,16 @@
         <v>1.316310317460317</v>
       </c>
       <c r="C67">
-        <v>44.33276054038921</v>
+        <v>122.9430589560079</v>
       </c>
       <c r="D67">
-        <v>1.250189480279705</v>
+        <v>1.248113397842487</v>
       </c>
       <c r="E67">
-        <v>25.20451132201104</v>
+        <v>69.98184430407868</v>
       </c>
       <c r="F67">
-        <v>19.12824921837817</v>
+        <v>52.96121465192923</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -5800,31 +5400,25 @@
         <v>-33.46244492132946</v>
       </c>
       <c r="Q67">
-        <v>-75.15665129330596</v>
+        <v>-97.04109027185542</v>
       </c>
       <c r="R67">
-        <v>-133.8497796853178</v>
+        <v>-160.6197356223814</v>
       </c>
       <c r="S67">
         <v>1</v>
       </c>
       <c r="T67">
-        <v>-0.0986327626156619</v>
+        <v>-391.0487455847381</v>
       </c>
       <c r="U67">
-        <v>0.0986327626156619</v>
+        <v>-97.76218639618452</v>
       </c>
       <c r="V67">
-        <v>-414.0516129720756</v>
+        <v>-1042.796654892635</v>
       </c>
       <c r="W67">
-        <v>-103.5129032430189</v>
-      </c>
-      <c r="X67">
-        <v>-1104.137634592201</v>
-      </c>
-      <c r="Y67">
-        <v>-444.8755037249924</v>
+        <v>-365.1467769005856</v>
       </c>
     </row>
     <row r="68">
@@ -5837,16 +5431,16 @@
         <v>3.48915873015873</v>
       </c>
       <c r="C68">
-        <v>371.58448747479</v>
+        <v>381.9025138510944</v>
       </c>
       <c r="D68">
-        <v>0.6103918929011415</v>
+        <v>0.5522882703459885</v>
       </c>
       <c r="E68">
-        <v>307.2807153004699</v>
+        <v>325.5230534962093</v>
       </c>
       <c r="F68">
-        <v>64.3037721743201</v>
+        <v>56.37946035488511</v>
       </c>
       <c r="G68">
         <v>8</v>
@@ -5881,31 +5475,25 @@
         <v>-4.556956387379461</v>
       </c>
       <c r="Q68">
-        <v>-10.23492404605427</v>
+        <v>-13.21517352340044</v>
       </c>
       <c r="R68">
-        <v>-18.22782554951785</v>
+        <v>-21.87339065942142</v>
       </c>
       <c r="S68">
         <v>6.610169491525424</v>
       </c>
       <c r="T68">
-        <v>-0.03797628596756679</v>
+        <v>305.0015765069846</v>
       </c>
       <c r="U68">
-        <v>0.3038102877405343</v>
+        <v>76.25039412674616</v>
       </c>
       <c r="V68">
-        <v>322.9428457132778</v>
+        <v>813.337537351959</v>
       </c>
       <c r="W68">
-        <v>80.73571142831946</v>
-      </c>
-      <c r="X68">
-        <v>861.1809219020743</v>
-      </c>
-      <c r="Y68">
-        <v>684.2924091420135</v>
+        <v>673.6889168346786</v>
       </c>
     </row>
     <row r="69">
@@ -5918,16 +5506,16 @@
         <v>4.497427380952381</v>
       </c>
       <c r="C69">
-        <v>385.0906973135464</v>
+        <v>467.7098255700591</v>
       </c>
       <c r="D69">
-        <v>0.5742810646470282</v>
+        <v>0.5389454749052142</v>
       </c>
       <c r="E69">
-        <v>324.557371091376</v>
+        <v>401.3555897833736</v>
       </c>
       <c r="F69">
-        <v>60.53332622217044</v>
+        <v>66.35423578668548</v>
       </c>
       <c r="G69">
         <v>4</v>
@@ -5962,31 +5550,25 @@
         <v>-22.05313022921123</v>
       </c>
       <c r="Q69">
-        <v>-49.53133049480842</v>
+        <v>-63.95407766471256</v>
       </c>
       <c r="R69">
-        <v>-88.21252091684491</v>
+        <v>-105.8550251002139</v>
       </c>
       <c r="S69">
         <v>3.779661016949153</v>
       </c>
       <c r="T69">
-        <v>-0.07263712976647828</v>
+        <v>-567.0975784374136</v>
       </c>
       <c r="U69">
-        <v>0.2905485190659131</v>
+        <v>-141.7743946093534</v>
       </c>
       <c r="V69">
-        <v>-600.4562595219674</v>
+        <v>-1512.260209166436</v>
       </c>
       <c r="W69">
-        <v>-150.1140648804918</v>
-      </c>
-      <c r="X69">
-        <v>-1601.21669205858</v>
-      </c>
-      <c r="Y69">
-        <v>-264.8968927032294</v>
+        <v>-163.3418305320671</v>
       </c>
     </row>
     <row r="70">
@@ -5999,16 +5581,16 @@
         <v>0.6535412698412698</v>
       </c>
       <c r="C70">
-        <v>17.78324900024618</v>
+        <v>60.43639494840134</v>
       </c>
       <c r="D70">
-        <v>1.332901876395605</v>
+        <v>1.329019018293494</v>
       </c>
       <c r="E70">
-        <v>9.636083293893348</v>
+        <v>32.82160242321872</v>
       </c>
       <c r="F70">
-        <v>8.147165706352835</v>
+        <v>27.61479252518262</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6043,31 +5625,25 @@
         <v>-7.788998243257691</v>
       </c>
       <c r="Q70">
-        <v>-17.49409005435677</v>
+        <v>-22.5880949054473</v>
       </c>
       <c r="R70">
-        <v>-31.15599297303076</v>
+        <v>-37.38719156763692</v>
       </c>
       <c r="S70">
         <v>0.9833333333333333</v>
       </c>
       <c r="T70">
-        <v>-0.0986327626156619</v>
+        <v>-505.8342403352136</v>
       </c>
       <c r="U70">
-        <v>0.0986327626156619</v>
+        <v>-126.4585600838034</v>
       </c>
       <c r="V70">
-        <v>-535.5891956490497</v>
+        <v>-1348.89130756057</v>
       </c>
       <c r="W70">
-        <v>-133.8972989122624</v>
-      </c>
-      <c r="X70">
-        <v>-1428.237855064132</v>
-      </c>
-      <c r="Y70">
-        <v>-535.3000367031602</v>
+        <v>-467.9859402922596</v>
       </c>
     </row>
     <row r="71">
@@ -6080,16 +5656,16 @@
         <v>1.502526984126984</v>
       </c>
       <c r="C71">
-        <v>77.76855008126934</v>
+        <v>147.0930956404707</v>
       </c>
       <c r="D71">
-        <v>1.194327471132991</v>
+        <v>1.157735147111956</v>
       </c>
       <c r="E71">
-        <v>45.6903641070214</v>
+        <v>88.31281466406686</v>
       </c>
       <c r="F71">
-        <v>32.07818597424794</v>
+        <v>58.7802809764038</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6124,31 +5700,25 @@
         <v>-20.28168215454048</v>
       </c>
       <c r="Q71">
-        <v>-45.55265811909793</v>
+        <v>-58.8168782481674</v>
       </c>
       <c r="R71">
-        <v>-81.12672861816193</v>
+        <v>-97.35207434179432</v>
       </c>
       <c r="S71">
         <v>0.9833333333333333</v>
       </c>
       <c r="T71">
-        <v>-0.0986327626156619</v>
+        <v>-286.9955872458959</v>
       </c>
       <c r="U71">
-        <v>0.0986327626156619</v>
+        <v>-71.74889681147397</v>
       </c>
       <c r="V71">
-        <v>-303.8776806133015</v>
+        <v>-765.3215659890557</v>
       </c>
       <c r="W71">
-        <v>-75.96942015332537</v>
-      </c>
-      <c r="X71">
-        <v>-810.3404816354706</v>
-      </c>
-      <c r="Y71">
-        <v>-271.6617886511301</v>
+        <v>-198.7193698535926</v>
       </c>
     </row>
     <row r="72">
@@ -6161,16 +5731,16 @@
         <v>1.01298373015873</v>
       </c>
       <c r="C72">
-        <v>81.68811888275019</v>
+        <v>103.3169247755815</v>
       </c>
       <c r="D72">
-        <v>0.7032450931338317</v>
+        <v>0.7609121363849716</v>
       </c>
       <c r="E72">
-        <v>64.18772563440406</v>
+        <v>78.54965686035638</v>
       </c>
       <c r="F72">
-        <v>17.50039324834613</v>
+        <v>24.76726791522508</v>
       </c>
       <c r="G72">
         <v>2</v>
@@ -6205,31 +5775,25 @@
         <v>-5.176173271291563</v>
       </c>
       <c r="Q72">
-        <v>-11.62568516732085</v>
+        <v>-15.01090248674553</v>
       </c>
       <c r="R72">
-        <v>-20.70469308516625</v>
+        <v>-24.8456317021995</v>
       </c>
       <c r="S72">
         <v>2</v>
       </c>
       <c r="T72">
-        <v>-0.08996755166593402</v>
+        <v>-290.4258767432515</v>
       </c>
       <c r="U72">
-        <v>0.179935103331868</v>
+        <v>-72.60646918581288</v>
       </c>
       <c r="V72">
-        <v>-307.5097518457957</v>
+        <v>-774.4690046486708</v>
       </c>
       <c r="W72">
-        <v>-76.87743796144893</v>
-      </c>
-      <c r="X72">
-        <v>-820.026004922122</v>
-      </c>
-      <c r="Y72">
-        <v>-237.4473181303664</v>
+        <v>-202.1198544544156</v>
       </c>
     </row>
     <row r="73">
@@ -6242,16 +5806,16 @@
         <v>0.9821642857142857</v>
       </c>
       <c r="C73">
-        <v>64.6201229447921</v>
+        <v>96.05466418308332</v>
       </c>
       <c r="D73">
-        <v>1.185176245585462</v>
+        <v>1.18531503324793</v>
       </c>
       <c r="E73">
-        <v>38.17134329235822</v>
+        <v>56.73518466949175</v>
       </c>
       <c r="F73">
-        <v>26.44877965243388</v>
+        <v>39.31947951359157</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -6286,31 +5850,25 @@
         <v>-8.237109632034196</v>
       </c>
       <c r="Q73">
-        <v>-18.50054823354881</v>
+        <v>-23.88761793289917</v>
       </c>
       <c r="R73">
-        <v>-32.94843852813678</v>
+        <v>-39.53812623376415</v>
       </c>
       <c r="S73">
         <v>1.9</v>
       </c>
       <c r="T73">
-        <v>-0.08996755166593402</v>
+        <v>-753.4259683304886</v>
       </c>
       <c r="U73">
-        <v>0.179935103331868</v>
+        <v>-188.3564920826221</v>
       </c>
       <c r="V73">
-        <v>-797.7451429381643</v>
+        <v>-2009.135915547969</v>
       </c>
       <c r="W73">
-        <v>-199.4362857345411</v>
-      </c>
-      <c r="X73">
-        <v>-2127.320381168438</v>
-      </c>
-      <c r="Y73">
-        <v>-751.625568226921</v>
+        <v>-681.2589220803044</v>
       </c>
     </row>
     <row r="74">
@@ -6323,16 +5881,16 @@
         <v>2.737940079365079</v>
       </c>
       <c r="C74">
-        <v>307.6104377377655</v>
+        <v>293.5696797878302</v>
       </c>
       <c r="D74">
-        <v>0.4027317375563226</v>
+        <v>0.4240949039837977</v>
       </c>
       <c r="E74">
-        <v>281.0827200786817</v>
+        <v>265.8359355101423</v>
       </c>
       <c r="F74">
-        <v>26.52771765908375</v>
+        <v>27.73374427768789</v>
       </c>
       <c r="G74">
         <v>8</v>
@@ -6367,31 +5925,25 @@
         <v>-13.34143588675399</v>
       </c>
       <c r="Q74">
-        <v>-29.96486500164946</v>
+        <v>-38.69016407158657</v>
       </c>
       <c r="R74">
-        <v>-53.36574354701596</v>
+        <v>-64.03889225641915</v>
       </c>
       <c r="S74">
         <v>6.35593220338983</v>
       </c>
       <c r="T74">
-        <v>-0.03797628596756679</v>
+        <v>16.70456314787427</v>
       </c>
       <c r="U74">
-        <v>0.3038102877405343</v>
+        <v>4.176140786968568</v>
       </c>
       <c r="V74">
-        <v>17.68718450951393</v>
+        <v>44.54550172766472</v>
       </c>
       <c r="W74">
-        <v>4.421796127378483</v>
-      </c>
-      <c r="X74">
-        <v>47.16582535870382</v>
-      </c>
-      <c r="Y74">
-        <v>295.33275724563</v>
+        <v>271.5840788641179</v>
       </c>
     </row>
     <row r="75">
@@ -6404,16 +5956,16 @@
         <v>1.472504365079365</v>
       </c>
       <c r="C75">
-        <v>105.9109591344339</v>
+        <v>147.628362666278</v>
       </c>
       <c r="D75">
-        <v>0.7829418608779152</v>
+        <v>0.7268298288501506</v>
       </c>
       <c r="E75">
-        <v>79.49880683757536</v>
+        <v>114.4584268146812</v>
       </c>
       <c r="F75">
-        <v>26.41215229685858</v>
+        <v>33.16993585159676</v>
       </c>
       <c r="G75">
         <v>2</v>
@@ -6448,31 +6000,25 @@
         <v>-15.47696030365173</v>
       </c>
       <c r="Q75">
-        <v>-34.76125284200179</v>
+        <v>-44.88318488059002</v>
       </c>
       <c r="R75">
-        <v>-61.90784121460692</v>
+        <v>-74.28940945752831</v>
       </c>
       <c r="S75">
         <v>2</v>
       </c>
       <c r="T75">
-        <v>-0.08996755166593402</v>
+        <v>-420.5163597635979</v>
       </c>
       <c r="U75">
-        <v>0.179935103331868</v>
+        <v>-105.1290899408995</v>
       </c>
       <c r="V75">
-        <v>-445.2526162202801</v>
+        <v>-1121.376959369594</v>
       </c>
       <c r="W75">
-        <v>-111.31315405507</v>
-      </c>
-      <c r="X75">
-        <v>-1187.340309920747</v>
-      </c>
-      <c r="Y75">
-        <v>-374.102909927848</v>
+        <v>-317.7711819779099</v>
       </c>
     </row>
     <row r="76">
@@ -6485,16 +6031,16 @@
         <v>7.033963888888889</v>
       </c>
       <c r="C76">
-        <v>666.8555581309215</v>
+        <v>783.8712697083254</v>
       </c>
       <c r="D76">
-        <v>0.5044618014653459</v>
+        <v>0.7429673733188065</v>
       </c>
       <c r="E76">
-        <v>582.0404598907838</v>
+        <v>602.156848362108</v>
       </c>
       <c r="F76">
-        <v>84.81509824013767</v>
+        <v>181.7144213462174</v>
       </c>
       <c r="G76">
         <v>16</v>
@@ -6529,31 +6075,25 @@
         <v>-14.66702963587115</v>
       </c>
       <c r="Q76">
-        <v>-32.94214856216661</v>
+        <v>-42.53438594402634</v>
       </c>
       <c r="R76">
-        <v>-58.66811854348461</v>
+        <v>-70.40174225218152</v>
       </c>
       <c r="S76">
         <v>10.48333333333333</v>
       </c>
       <c r="T76">
-        <v>0.03134540163025619</v>
+        <v>255.4085737801854</v>
       </c>
       <c r="U76">
-        <v>-0.501526426084099</v>
+        <v>63.85214344504634</v>
       </c>
       <c r="V76">
-        <v>270.432607531961</v>
+        <v>681.0895300804943</v>
       </c>
       <c r="W76">
-        <v>67.60815188299024</v>
-      </c>
-      <c r="X76">
-        <v>721.1536200852292</v>
-      </c>
-      <c r="Y76">
-        <v>904.3460171007159</v>
+        <v>996.7454575444845</v>
       </c>
     </row>
     <row r="77">
@@ -6566,16 +6106,16 @@
         <v>6.088669206349206</v>
       </c>
       <c r="C77">
-        <v>607.0241944873949</v>
+        <v>649.6938451617767</v>
       </c>
       <c r="D77">
-        <v>0.2999675809611602</v>
+        <v>0.354893257991813</v>
       </c>
       <c r="E77">
-        <v>576.4408533597567</v>
+        <v>605.0586427189581</v>
       </c>
       <c r="F77">
-        <v>30.58334112763816</v>
+        <v>44.63520244281858</v>
       </c>
       <c r="G77">
         <v>16</v>
@@ -6610,31 +6150,25 @@
         <v>-15.72490034953211</v>
       </c>
       <c r="Q77">
-        <v>-35.31812618504912</v>
+        <v>-45.60221101364311</v>
       </c>
       <c r="R77">
-        <v>-62.89960139812842</v>
+        <v>-75.47952167775412</v>
       </c>
       <c r="S77">
         <v>9.85</v>
       </c>
       <c r="T77">
-        <v>0.03134540163025619</v>
+        <v>-128.2650949350807</v>
       </c>
       <c r="U77">
-        <v>-0.501526426084099</v>
+        <v>-32.06627373377018</v>
       </c>
       <c r="V77">
-        <v>-135.8101005194972</v>
+        <v>-342.0402531602153</v>
       </c>
       <c r="W77">
-        <v>-33.95252512987431</v>
-      </c>
-      <c r="X77">
-        <v>-362.1602680519927</v>
-      </c>
-      <c r="Y77">
-        <v>435.8959677828485</v>
+        <v>475.8265392130529</v>
       </c>
     </row>
     <row r="78">
@@ -6647,16 +6181,16 @@
         <v>5.614575396825397</v>
       </c>
       <c r="C78">
-        <v>536.5527574468085</v>
+        <v>609.2887051185389</v>
       </c>
       <c r="D78">
-        <v>0.3675601566907281</v>
+        <v>0.4018018256644398</v>
       </c>
       <c r="E78">
-        <v>497.2695305637183</v>
+        <v>556.9599972865784</v>
       </c>
       <c r="F78">
-        <v>39.28322688309026</v>
+        <v>52.32870783196051</v>
       </c>
       <c r="G78">
         <v>2</v>
@@ -6691,31 +6225,25 @@
         <v>-14.90195094773535</v>
       </c>
       <c r="Q78">
-        <v>-33.4697818286136</v>
+        <v>-43.21565774843251</v>
       </c>
       <c r="R78">
-        <v>-59.6078037909414</v>
+        <v>-71.52936454912968</v>
       </c>
       <c r="S78">
         <v>1.9</v>
       </c>
       <c r="T78">
-        <v>-0.08996755166593402</v>
+        <v>-541.6394727238318</v>
       </c>
       <c r="U78">
-        <v>0.179935103331868</v>
+        <v>-135.4098681809579</v>
       </c>
       <c r="V78">
-        <v>-573.5006181781748</v>
+        <v>-1444.371927263551</v>
       </c>
       <c r="W78">
-        <v>-143.3751545445437</v>
-      </c>
-      <c r="X78">
-        <v>-1529.334981808466</v>
-      </c>
-      <c r="Y78">
-        <v>-70.41764255997987</v>
+        <v>24.43357464627468</v>
       </c>
     </row>
     <row r="79">
@@ -6728,16 +6256,16 @@
         <v>4.541767460317461</v>
       </c>
       <c r="C79">
-        <v>447.1431610757122</v>
+        <v>484.5123489970151</v>
       </c>
       <c r="D79">
-        <v>0.4751615929678069</v>
+        <v>0.4275491918933289</v>
       </c>
       <c r="E79">
-        <v>395.7303731580254</v>
+        <v>438.0850502886863</v>
       </c>
       <c r="F79">
-        <v>51.41278791768684</v>
+        <v>46.42729870832886</v>
       </c>
       <c r="G79">
         <v>4</v>
@@ -6772,31 +6300,25 @@
         <v>-4.992953175167221</v>
       </c>
       <c r="Q79">
-        <v>-11.21417283142558</v>
+        <v>-14.47956420798494</v>
       </c>
       <c r="R79">
-        <v>-19.97181270066888</v>
+        <v>-23.96617524080266</v>
       </c>
       <c r="S79">
         <v>2.833333333333333</v>
       </c>
       <c r="T79">
-        <v>-0.07263712976647828</v>
+        <v>46.72362019437261</v>
       </c>
       <c r="U79">
-        <v>0.2905485190659131</v>
+        <v>11.68090504859315</v>
       </c>
       <c r="V79">
-        <v>49.47206844110042</v>
+        <v>124.596320518327</v>
       </c>
       <c r="W79">
-        <v>12.3680171102751</v>
-      </c>
-      <c r="X79">
-        <v>131.9255158429345</v>
-      </c>
-      <c r="Y79">
-        <v>485.4010566853871</v>
+        <v>516.7564049834028</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/economic_MF_final.xlsx
+++ b/Data Analysis/1_Data/economic_MF_final.xlsx
@@ -487,10 +487,10 @@
         <v>0.39345572806922</v>
       </c>
       <c r="E2">
-        <v>416.5968581011657</v>
+        <v>429.1958060771606</v>
       </c>
       <c r="F2">
-        <v>37.57657589385445</v>
+        <v>24.97762791785954</v>
       </c>
       <c r="G2">
         <v>16</v>
@@ -530,9 +530,6 @@
       <c r="R2">
         <v>-50.28157516499095</v>
       </c>
-      <c r="S2">
-        <v>11.83333333333333</v>
-      </c>
       <c r="T2">
         <v>776.0019362477558</v>
       </c>
@@ -562,10 +559,10 @@
         <v>0.4168268958916156</v>
       </c>
       <c r="E3">
-        <v>329.2007010263908</v>
+        <v>340.3004259862033</v>
       </c>
       <c r="F3">
-        <v>33.21326827851698</v>
+        <v>22.11354331870444</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -605,9 +602,6 @@
       <c r="R3">
         <v>-62.7502337238665</v>
       </c>
-      <c r="S3">
-        <v>5.728813559322034</v>
-      </c>
       <c r="T3">
         <v>7.583391783192281</v>
       </c>
@@ -637,10 +631,10 @@
         <v>0.6592796869815137</v>
       </c>
       <c r="E4">
-        <v>248.540370395803</v>
+        <v>267.820204333732</v>
       </c>
       <c r="F4">
-        <v>60.09412555997855</v>
+        <v>40.81429162204955</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -680,9 +674,6 @@
       <c r="R4">
         <v>-188.9905626286803</v>
       </c>
-      <c r="S4">
-        <v>6.186440677966102</v>
-      </c>
       <c r="T4">
         <v>74.56707340401853</v>
       </c>
@@ -712,10 +703,10 @@
         <v>0.6277465946716212</v>
       </c>
       <c r="E5">
-        <v>356.5929114777018</v>
+        <v>381.9788725211258</v>
       </c>
       <c r="F5">
-        <v>78.66098449524912</v>
+        <v>53.27502345182518</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -755,9 +746,6 @@
       <c r="R5">
         <v>-162.3022324266065</v>
       </c>
-      <c r="S5">
-        <v>3.35</v>
-      </c>
       <c r="T5">
         <v>-381.4278283481973</v>
       </c>
@@ -787,10 +775,10 @@
         <v>1.023510985183034</v>
       </c>
       <c r="E6">
-        <v>256.5043236285</v>
+        <v>297.5235318449186</v>
       </c>
       <c r="F6">
-        <v>137.8063629827535</v>
+        <v>96.78715476633494</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -830,9 +818,6 @@
       <c r="R6">
         <v>-130.8609161569784</v>
       </c>
-      <c r="S6">
-        <v>1.864406779661017</v>
-      </c>
       <c r="T6">
         <v>-405.2626142571454</v>
       </c>
@@ -862,10 +847,10 @@
         <v>0.4815114334563739</v>
       </c>
       <c r="E7">
-        <v>286.7338295428325</v>
+        <v>299.3812817315102</v>
       </c>
       <c r="F7">
-        <v>38.21450954216374</v>
+        <v>25.56705735348601</v>
       </c>
       <c r="G7">
         <v>16</v>
@@ -905,9 +890,6 @@
       <c r="R7">
         <v>-30.39190942733287</v>
       </c>
-      <c r="S7">
-        <v>12.89830508474576</v>
-      </c>
       <c r="T7">
         <v>212.5784837509758</v>
       </c>
@@ -937,10 +919,10 @@
         <v>0.7615213407886234</v>
       </c>
       <c r="E8">
-        <v>144.1596234494615</v>
+        <v>158.4750165107871</v>
       </c>
       <c r="F8">
-        <v>45.52137710382149</v>
+        <v>31.20598404249591</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -980,9 +962,6 @@
       <c r="R8">
         <v>-140.0203770131957</v>
       </c>
-      <c r="S8">
-        <v>2</v>
-      </c>
       <c r="T8">
         <v>-373.4422893248743</v>
       </c>
@@ -1012,10 +991,10 @@
         <v>0.6679587706777543</v>
       </c>
       <c r="E9">
-        <v>306.7709091073825</v>
+        <v>331.1155000353219</v>
       </c>
       <c r="F9">
-        <v>76.00587331946997</v>
+        <v>51.66128239153056</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1055,9 +1034,6 @@
       <c r="R9">
         <v>-229.3370740969741</v>
       </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
       <c r="T9">
         <v>-356.7084314993093</v>
       </c>
@@ -1087,10 +1063,10 @@
         <v>1.087336851145372</v>
       </c>
       <c r="E10">
-        <v>47.96640542908309</v>
+        <v>56.37577490563337</v>
       </c>
       <c r="F10">
-        <v>28.64369224305305</v>
+        <v>20.23432276650276</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1130,9 +1106,6 @@
       <c r="R10">
         <v>-106.6752976432115</v>
       </c>
-      <c r="S10">
-        <v>0.9523809523809523</v>
-      </c>
       <c r="T10">
         <v>-453.0081391389492</v>
       </c>
@@ -1162,10 +1135,10 @@
         <v>0.4566204374199388</v>
       </c>
       <c r="E11">
-        <v>313.4942306184083</v>
+        <v>326.0279067961011</v>
       </c>
       <c r="F11">
-        <v>37.72478801621145</v>
+        <v>25.19111183851862</v>
       </c>
       <c r="G11">
         <v>16</v>
@@ -1205,9 +1178,6 @@
       <c r="R11">
         <v>-55.81306805400369</v>
       </c>
-      <c r="S11">
-        <v>11.03333333333333</v>
-      </c>
       <c r="T11">
         <v>1022.72996477033</v>
       </c>
@@ -1237,10 +1207,10 @@
         <v>0.5448753392177107</v>
       </c>
       <c r="E12">
-        <v>422.2794362261802</v>
+        <v>445.6263095259632</v>
       </c>
       <c r="F12">
-        <v>71.28248290912234</v>
+        <v>47.93560960933928</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -1280,9 +1250,6 @@
       <c r="R12">
         <v>-162.4702296753888</v>
       </c>
-      <c r="S12">
-        <v>5.3</v>
-      </c>
       <c r="T12">
         <v>-370.1816630423123</v>
       </c>
@@ -1312,10 +1279,10 @@
         <v>0.6498474301972058</v>
       </c>
       <c r="E13">
-        <v>383.8417064536477</v>
+        <v>412.8777203856216</v>
       </c>
       <c r="F13">
-        <v>90.34262089240082</v>
+        <v>61.30660696042696</v>
       </c>
       <c r="G13">
         <v>4</v>
@@ -1355,9 +1322,6 @@
       <c r="R13">
         <v>-148.852252336754</v>
       </c>
-      <c r="S13">
-        <v>3.2</v>
-      </c>
       <c r="T13">
         <v>-168.5018317652187</v>
       </c>
@@ -1387,10 +1351,10 @@
         <v>0.5280969391028871</v>
       </c>
       <c r="E14">
-        <v>221.6580450526751</v>
+        <v>233.2371438577435</v>
       </c>
       <c r="F14">
-        <v>35.25294059226744</v>
+        <v>23.67384178719908</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -1430,9 +1394,6 @@
       <c r="R14">
         <v>-40.78101627379836</v>
       </c>
-      <c r="S14">
-        <v>6.559322033898305</v>
-      </c>
       <c r="T14">
         <v>433.4735654111012</v>
       </c>
@@ -1462,10 +1423,10 @@
         <v>2.059899075105867</v>
       </c>
       <c r="E15">
-        <v>35.52390877429637</v>
+        <v>50.0583966227656</v>
       </c>
       <c r="F15">
-        <v>60.47754623177874</v>
+        <v>45.94305838330951</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1505,9 +1466,6 @@
       <c r="R15">
         <v>-92.49525164652148</v>
       </c>
-      <c r="S15">
-        <v>0.95</v>
-      </c>
       <c r="T15">
         <v>-607.3755880406841</v>
       </c>
@@ -1537,10 +1495,10 @@
         <v>0.7187828851276133</v>
       </c>
       <c r="E16">
-        <v>136.8525914046039</v>
+        <v>149.1750623328464</v>
       </c>
       <c r="F16">
-        <v>38.85237901415098</v>
+        <v>26.52990808590846</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1580,9 +1538,6 @@
       <c r="R16">
         <v>-27.27674853955119</v>
       </c>
-      <c r="S16">
-        <v>1.983050847457627</v>
-      </c>
       <c r="T16">
         <v>-637.9332337409667</v>
       </c>
@@ -1612,10 +1567,10 @@
         <v>0.6582366787324752</v>
       </c>
       <c r="E17">
-        <v>165.1947746486002</v>
+        <v>177.973995574335</v>
       </c>
       <c r="F17">
-        <v>39.82422812923664</v>
+        <v>27.04500720350185</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1655,9 +1610,6 @@
       <c r="R17">
         <v>-69.41329029307803</v>
       </c>
-      <c r="S17">
-        <v>2</v>
-      </c>
       <c r="T17">
         <v>-998.2419574417249</v>
       </c>
@@ -1687,10 +1639,10 @@
         <v>0.9174449964737151</v>
       </c>
       <c r="E18">
-        <v>47.59588718965632</v>
+        <v>54.00948001977324</v>
       </c>
       <c r="F18">
-        <v>21.06375127884599</v>
+        <v>14.65015844872907</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1730,9 +1682,6 @@
       <c r="R18">
         <v>-52.17060611591119</v>
       </c>
-      <c r="S18">
-        <v>1</v>
-      </c>
       <c r="T18">
         <v>-757.7101452362072</v>
       </c>
@@ -1762,10 +1711,10 @@
         <v>0.6161318233197487</v>
       </c>
       <c r="E19">
-        <v>227.1861985099758</v>
+        <v>242.8354319103713</v>
       </c>
       <c r="F19">
-        <v>48.3872276808813</v>
+        <v>32.73799428048579</v>
       </c>
       <c r="G19">
         <v>4</v>
@@ -1805,9 +1754,6 @@
       <c r="R19">
         <v>-52.46373763961006</v>
       </c>
-      <c r="S19">
-        <v>3.559322033898305</v>
-      </c>
       <c r="T19">
         <v>-744.369023474728</v>
       </c>
@@ -1837,10 +1783,10 @@
         <v>0.3206156334207687</v>
       </c>
       <c r="E20">
-        <v>588.8201959106296</v>
+        <v>600.8679899281124</v>
       </c>
       <c r="F20">
-        <v>35.60357115193676</v>
+        <v>23.55577713445405</v>
       </c>
       <c r="G20">
         <v>16</v>
@@ -1880,9 +1826,6 @@
       <c r="R20">
         <v>-80.56385715887156</v>
       </c>
-      <c r="S20">
-        <v>12.15254237288136</v>
-      </c>
       <c r="T20">
         <v>-156.5795148059204</v>
       </c>
@@ -1912,10 +1855,10 @@
         <v>1.012011213505238</v>
       </c>
       <c r="E21">
-        <v>107.1722850759626</v>
+        <v>124.0153575066032</v>
       </c>
       <c r="F21">
-        <v>56.44540447769138</v>
+        <v>39.60233204705081</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -1955,9 +1898,6 @@
       <c r="R21">
         <v>-23.97763894200598</v>
       </c>
-      <c r="S21">
-        <v>3.694915254237288</v>
-      </c>
       <c r="T21">
         <v>72.5154982273032</v>
       </c>
@@ -1987,10 +1927,10 @@
         <v>0.3551811417396349</v>
       </c>
       <c r="E22">
-        <v>456.8148258797681</v>
+        <v>468.1886737817301</v>
       </c>
       <c r="F22">
-        <v>33.75268010341836</v>
+        <v>22.37883220145631</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -2030,9 +1970,6 @@
       <c r="R22">
         <v>-45.07948438017191</v>
       </c>
-      <c r="S22">
-        <v>3.6</v>
-      </c>
       <c r="T22">
         <v>822.0031998972684</v>
       </c>
@@ -2062,10 +1999,10 @@
         <v>0.7130422182029099</v>
       </c>
       <c r="E23">
-        <v>159.8986152219455</v>
+        <v>174.1002375138188</v>
       </c>
       <c r="F23">
-        <v>44.72684160091154</v>
+        <v>30.52521930903828</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2105,9 +2042,6 @@
       <c r="R23">
         <v>-17.7815422654048</v>
       </c>
-      <c r="S23">
-        <v>1.983050847457627</v>
-      </c>
       <c r="T23">
         <v>-50.02277013860132</v>
       </c>
@@ -2137,10 +2071,10 @@
         <v>0.8559765251674778</v>
       </c>
       <c r="E24">
-        <v>109.44133844812</v>
+        <v>122.6300533357862</v>
       </c>
       <c r="F24">
-        <v>42.75871015165337</v>
+        <v>29.56999526398715</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2180,9 +2114,6 @@
       <c r="R24">
         <v>-120.8238153226634</v>
       </c>
-      <c r="S24">
-        <v>1</v>
-      </c>
       <c r="T24">
         <v>-216.7298338907898</v>
       </c>
@@ -2212,10 +2143,10 @@
         <v>1.339552482385653</v>
       </c>
       <c r="E25">
-        <v>91.5820982705574</v>
+        <v>113.2902021053998</v>
       </c>
       <c r="F25">
-        <v>78.07960111115742</v>
+        <v>56.37149727631501</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2255,9 +2186,6 @@
       <c r="R25">
         <v>-45.6945025391969</v>
       </c>
-      <c r="S25">
-        <v>0.9833333333333333</v>
-      </c>
       <c r="T25">
         <v>-70.16476144728868</v>
       </c>
@@ -2287,10 +2215,10 @@
         <v>0.3709690988846847</v>
       </c>
       <c r="E26">
-        <v>296.1312695228585</v>
+        <v>304.1413997610836</v>
       </c>
       <c r="F26">
-        <v>23.81876257823694</v>
+        <v>15.8086323400118</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -2330,9 +2258,6 @@
       <c r="R26">
         <v>-59.87185375948937</v>
       </c>
-      <c r="S26">
-        <v>3.677966101694915</v>
-      </c>
       <c r="T26">
         <v>458.1313522679775</v>
       </c>
@@ -2362,10 +2287,10 @@
         <v>0.7943447411242142</v>
       </c>
       <c r="E27">
-        <v>114.1598476401484</v>
+        <v>126.3253309517738</v>
       </c>
       <c r="F27">
-        <v>38.94295182941181</v>
+        <v>26.77746851778643</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -2405,9 +2330,6 @@
       <c r="R27">
         <v>-48.31947164076955</v>
       </c>
-      <c r="S27">
-        <v>1.627118644067797</v>
-      </c>
       <c r="T27">
         <v>-417.5614356405866</v>
       </c>
@@ -2437,10 +2359,10 @@
         <v>0.6482604441170002</v>
       </c>
       <c r="E28">
-        <v>167.9833922714159</v>
+        <v>180.6364247484773</v>
       </c>
       <c r="F28">
-        <v>39.35688998595751</v>
+        <v>26.70385750889611</v>
       </c>
       <c r="G28">
         <v>4</v>
@@ -2480,9 +2402,6 @@
       <c r="R28">
         <v>-23.98385578133442</v>
       </c>
-      <c r="S28">
-        <v>3.933333333333333</v>
-      </c>
       <c r="T28">
         <v>-152.817217983223</v>
       </c>
@@ -2512,10 +2431,10 @@
         <v>0.4230253462140602</v>
       </c>
       <c r="E29">
-        <v>356.5276811339573</v>
+        <v>368.8865608132653</v>
       </c>
       <c r="F29">
-        <v>37.01386236293655</v>
+        <v>24.65498268362853</v>
       </c>
       <c r="G29">
         <v>16</v>
@@ -2555,9 +2474,6 @@
       <c r="R29">
         <v>-26.07845498112912</v>
       </c>
-      <c r="S29">
-        <v>12.86440677966102</v>
-      </c>
       <c r="T29">
         <v>446.5867656201178</v>
       </c>
@@ -2587,10 +2503,10 @@
         <v>0.4629939334493692</v>
       </c>
       <c r="E30">
-        <v>341.6509932303018</v>
+        <v>355.6664178576838</v>
       </c>
       <c r="F30">
-        <v>42.22582413324727</v>
+        <v>28.21039950586527</v>
       </c>
       <c r="G30">
         <v>8</v>
@@ -2630,9 +2546,6 @@
       <c r="R30">
         <v>-22.93640367452804</v>
       </c>
-      <c r="S30">
-        <v>6.135593220338983</v>
-      </c>
       <c r="T30">
         <v>686.5262758335965</v>
       </c>
@@ -2662,10 +2575,10 @@
         <v>0.561157748949866</v>
       </c>
       <c r="E31">
-        <v>94.04543703289646</v>
+        <v>99.5287128692364</v>
       </c>
       <c r="F31">
-        <v>16.78855389412787</v>
+        <v>11.30527805778793</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2705,9 +2618,6 @@
       <c r="R31">
         <v>-132.4114092948746</v>
       </c>
-      <c r="S31">
-        <v>1</v>
-      </c>
       <c r="T31">
         <v>-348.1786362533473</v>
       </c>
@@ -2737,10 +2647,10 @@
         <v>0.4999571520091635</v>
       </c>
       <c r="E32">
-        <v>315.4396844215909</v>
+        <v>330.3494748533894</v>
       </c>
       <c r="F32">
-        <v>45.18330190791801</v>
+        <v>30.27351147611944</v>
       </c>
       <c r="G32">
         <v>8</v>
@@ -2780,9 +2690,6 @@
       <c r="R32">
         <v>-32.7771120167408</v>
       </c>
-      <c r="S32">
-        <v>6</v>
-      </c>
       <c r="T32">
         <v>285.0303606961218</v>
       </c>
@@ -2812,10 +2719,10 @@
         <v>0.9771527159386635</v>
       </c>
       <c r="E33">
-        <v>304.1519598482253</v>
+        <v>349.4218535155175</v>
       </c>
       <c r="F33">
-        <v>150.5802043807483</v>
+        <v>105.3103107134561</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2855,9 +2762,6 @@
       <c r="R33">
         <v>-99.32213809590436</v>
       </c>
-      <c r="S33">
-        <v>0.7333333333333333</v>
-      </c>
       <c r="T33">
         <v>-245.2723622574324</v>
       </c>
@@ -2887,10 +2791,10 @@
         <v>0.4227347236872109</v>
       </c>
       <c r="E34">
-        <v>490.6054258011374</v>
+        <v>507.5901443672414</v>
       </c>
       <c r="F34">
-        <v>50.86575193808375</v>
+        <v>33.88103337197975</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -2930,9 +2834,6 @@
       <c r="R34">
         <v>-33.75375027892549</v>
       </c>
-      <c r="S34">
-        <v>3.610169491525424</v>
-      </c>
       <c r="T34">
         <v>-71.83156791000187</v>
       </c>
@@ -2962,10 +2863,10 @@
         <v>0.5533812224418524</v>
       </c>
       <c r="E35">
-        <v>282.2455123677459</v>
+        <v>298.2930723843074</v>
       </c>
       <c r="F35">
-        <v>49.06788121398392</v>
+        <v>33.02032119742239</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -3005,9 +2906,6 @@
       <c r="R35">
         <v>-69.76600477359052</v>
       </c>
-      <c r="S35">
-        <v>6.220338983050848</v>
-      </c>
       <c r="T35">
         <v>715.1119955715096</v>
       </c>
@@ -3037,10 +2935,10 @@
         <v>0.4351810597028645</v>
       </c>
       <c r="E36">
-        <v>363.1890360414601</v>
+        <v>376.4647289769989</v>
       </c>
       <c r="F36">
-        <v>39.83010036387219</v>
+        <v>26.55440742833343</v>
       </c>
       <c r="G36">
         <v>16</v>
@@ -3080,9 +2978,6 @@
       <c r="R36">
         <v>-27.22953876710327</v>
       </c>
-      <c r="S36">
-        <v>11.2</v>
-      </c>
       <c r="T36">
         <v>799.9688724580296</v>
       </c>
@@ -3112,10 +3007,10 @@
         <v>0.4713941864434524</v>
       </c>
       <c r="E37">
-        <v>158.7618523761666</v>
+        <v>165.4952476719619</v>
       </c>
       <c r="F37">
-        <v>20.31282839619072</v>
+        <v>13.57943310039542</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -3155,9 +3050,6 @@
       <c r="R37">
         <v>-18.58141926439271</v>
       </c>
-      <c r="S37">
-        <v>2</v>
-      </c>
       <c r="T37">
         <v>115.1339448338881</v>
       </c>
@@ -3187,10 +3079,10 @@
         <v>0.5705049226071159</v>
       </c>
       <c r="E38">
-        <v>148.5736822371986</v>
+        <v>157.4972063389352</v>
       </c>
       <c r="F38">
-        <v>27.3664774878178</v>
+        <v>18.4429533860812</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -3230,9 +3122,6 @@
       <c r="R38">
         <v>-57.70377317826512</v>
       </c>
-      <c r="S38">
-        <v>1.88135593220339</v>
-      </c>
       <c r="T38">
         <v>-391.0246525627841</v>
       </c>
@@ -3262,10 +3151,10 @@
         <v>0.4661272433346796</v>
       </c>
       <c r="E39">
-        <v>504.9312466879447</v>
+        <v>525.9054596467809</v>
       </c>
       <c r="F39">
-        <v>63.22185833373715</v>
+        <v>42.24764537490103</v>
       </c>
       <c r="G39">
         <v>8</v>
@@ -3305,9 +3194,6 @@
       <c r="R39">
         <v>-37.82831323651127</v>
       </c>
-      <c r="S39">
-        <v>6.915254237288136</v>
-      </c>
       <c r="T39">
         <v>-273.0250565140611</v>
       </c>
@@ -3337,10 +3223,10 @@
         <v>0.4968011189958311</v>
       </c>
       <c r="E40">
-        <v>504.2340106443602</v>
+        <v>527.7921059781677</v>
       </c>
       <c r="F40">
-        <v>71.35512001371598</v>
+        <v>47.79702467990853</v>
       </c>
       <c r="G40">
         <v>16</v>
@@ -3380,9 +3266,6 @@
       <c r="R40">
         <v>-88.29875926621034</v>
       </c>
-      <c r="S40">
-        <v>11.22033898305085</v>
-      </c>
       <c r="T40">
         <v>204.5507074525101</v>
       </c>
@@ -3412,10 +3295,10 @@
         <v>0.5561755448508273</v>
       </c>
       <c r="E41">
-        <v>225.3238302146827</v>
+        <v>238.2519026613122</v>
       </c>
       <c r="F41">
-        <v>39.54865258518996</v>
+        <v>26.62058013856043</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -3455,9 +3338,6 @@
       <c r="R41">
         <v>-31.9976583991754</v>
       </c>
-      <c r="S41">
-        <v>1</v>
-      </c>
       <c r="T41">
         <v>-966.0429212020487</v>
       </c>
@@ -3487,10 +3367,10 @@
         <v>1.200818368266199</v>
       </c>
       <c r="E42">
-        <v>103.4919112060029</v>
+        <v>124.4997447968828</v>
       </c>
       <c r="F42">
-        <v>73.33568450207086</v>
+        <v>52.32785091119098</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -3530,9 +3410,6 @@
       <c r="R42">
         <v>-66.6095139583979</v>
       </c>
-      <c r="S42">
-        <v>1.932203389830508</v>
-      </c>
       <c r="T42">
         <v>-1141.569156945336</v>
       </c>
@@ -3562,10 +3439,10 @@
         <v>0.8501191074525598</v>
       </c>
       <c r="E43">
-        <v>210.7045849345145</v>
+        <v>235.8139617223286</v>
       </c>
       <c r="F43">
-        <v>81.30705000932684</v>
+        <v>56.19767322151276</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -3605,9 +3482,6 @@
       <c r="R43">
         <v>-43.57228032095942</v>
       </c>
-      <c r="S43">
-        <v>3.491525423728814</v>
-      </c>
       <c r="T43">
         <v>-1624.929458919247</v>
       </c>
@@ -3637,10 +3511,10 @@
         <v>0.4695421996711477</v>
       </c>
       <c r="E44">
-        <v>366.6743099508213</v>
+        <v>382.1127998988063</v>
       </c>
       <c r="F44">
-        <v>46.5603325019726</v>
+        <v>31.12184255398762</v>
       </c>
       <c r="G44">
         <v>8</v>
@@ -3680,9 +3554,6 @@
       <c r="R44">
         <v>-23.5983827663694</v>
       </c>
-      <c r="S44">
-        <v>6.35593220338983</v>
-      </c>
       <c r="T44">
         <v>-931.5429266587793</v>
       </c>
@@ -3712,10 +3583,10 @@
         <v>0.4831526210202264</v>
       </c>
       <c r="E45">
-        <v>506.7326196642649</v>
+        <v>529.2246146120453</v>
       </c>
       <c r="F45">
-        <v>67.97761322648159</v>
+        <v>45.48561827870117</v>
       </c>
       <c r="G45">
         <v>8</v>
@@ -3755,9 +3626,6 @@
       <c r="R45">
         <v>-35.26445651144341</v>
       </c>
-      <c r="S45">
-        <v>5.491525423728813</v>
-      </c>
       <c r="T45">
         <v>-28.55696837950058</v>
       </c>
@@ -3787,10 +3655,10 @@
         <v>0.670426792632747</v>
       </c>
       <c r="E46">
-        <v>223.6617586294217</v>
+        <v>241.5250471126923</v>
       </c>
       <c r="F46">
-        <v>55.79695056885603</v>
+        <v>37.93366208558538</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -3830,9 +3698,6 @@
       <c r="R46">
         <v>-17.35655505192626</v>
       </c>
-      <c r="S46">
-        <v>1</v>
-      </c>
       <c r="T46">
         <v>-794.2045027091767</v>
       </c>
@@ -3862,10 +3727,10 @@
         <v>0.5410559028991293</v>
       </c>
       <c r="E47">
-        <v>519.736224828245</v>
+        <v>548.1077045944247</v>
       </c>
       <c r="F47">
-        <v>86.56717017323899</v>
+        <v>58.19569040705926</v>
       </c>
       <c r="G47">
         <v>8</v>
@@ -3905,9 +3770,6 @@
       <c r="R47">
         <v>-29.66221983874401</v>
       </c>
-      <c r="S47">
-        <v>6.203389830508475</v>
-      </c>
       <c r="T47">
         <v>-13.28549215938822</v>
       </c>
@@ -3937,10 +3799,10 @@
         <v>0.6955641178841452</v>
       </c>
       <c r="E48">
-        <v>207.8962680971215</v>
+        <v>225.5911023639913</v>
       </c>
       <c r="F48">
-        <v>55.53879062782633</v>
+        <v>37.84395636095658</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -3980,9 +3842,6 @@
       <c r="R48">
         <v>-25.9084799374745</v>
       </c>
-      <c r="S48">
-        <v>1.864406779661017</v>
-      </c>
       <c r="T48">
         <v>-907.9343167996072</v>
       </c>
@@ -4012,10 +3871,10 @@
         <v>0.3150807368421378</v>
       </c>
       <c r="E49">
-        <v>447.353439584931</v>
+        <v>456.2048171775218</v>
       </c>
       <c r="F49">
-        <v>26.1409070265363</v>
+        <v>17.28952943394557</v>
       </c>
       <c r="G49">
         <v>16</v>
@@ -4055,9 +3914,6 @@
       <c r="R49">
         <v>-19.43462453174192</v>
       </c>
-      <c r="S49">
-        <v>11.5</v>
-      </c>
       <c r="T49">
         <v>-13.44608419750229</v>
       </c>
@@ -4087,10 +3943,10 @@
         <v>0.3420029303696343</v>
       </c>
       <c r="E50">
-        <v>333.6125329626454</v>
+        <v>341.3395631497756</v>
       </c>
       <c r="F50">
-        <v>22.89304619201909</v>
+        <v>15.16601600488889</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -4130,9 +3986,6 @@
       <c r="R50">
         <v>-28.01301462364787</v>
       </c>
-      <c r="S50">
-        <v>3.254237288135593</v>
-      </c>
       <c r="T50">
         <v>38.77324499785593</v>
       </c>
@@ -4162,10 +4015,10 @@
         <v>0.8889942869013838</v>
       </c>
       <c r="E51">
-        <v>96.88147330183328</v>
+        <v>109.2941513142395</v>
       </c>
       <c r="F51">
-        <v>40.52202805147998</v>
+        <v>28.10935003907379</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -4205,9 +4058,6 @@
       <c r="R51">
         <v>-192.9124417585077</v>
       </c>
-      <c r="S51">
-        <v>1</v>
-      </c>
       <c r="T51">
         <v>-459.991635634027</v>
       </c>
@@ -4237,10 +4087,10 @@
         <v>0.392666266310928</v>
       </c>
       <c r="E52">
-        <v>366.5804652467775</v>
+        <v>377.6247677354891</v>
       </c>
       <c r="F52">
-        <v>32.93627288227702</v>
+        <v>21.89197039356543</v>
       </c>
       <c r="G52">
         <v>4</v>
@@ -4280,9 +4130,6 @@
       <c r="R52">
         <v>-27.48984268260899</v>
       </c>
-      <c r="S52">
-        <v>3.033898305084746</v>
-      </c>
       <c r="T52">
         <v>-531.4328454065576</v>
       </c>
@@ -4312,10 +4159,10 @@
         <v>0.5184715306626632</v>
       </c>
       <c r="E53">
-        <v>519.4490710126141</v>
+        <v>545.6903351017299</v>
       </c>
       <c r="F53">
-        <v>79.76429188447707</v>
+        <v>53.52302779536126</v>
       </c>
       <c r="G53">
         <v>16</v>
@@ -4355,9 +4202,6 @@
       <c r="R53">
         <v>-39.04530378209561</v>
       </c>
-      <c r="S53">
-        <v>10.33898305084746</v>
-      </c>
       <c r="T53">
         <v>-203.5334048808638</v>
       </c>
@@ -4387,10 +4231,10 @@
         <v>1.57066084700116</v>
       </c>
       <c r="E54">
-        <v>35.451641983204</v>
+        <v>45.85705545834136</v>
       </c>
       <c r="F54">
-        <v>39.29760433948937</v>
+        <v>28.892190864352</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -4430,9 +4274,6 @@
       <c r="R54">
         <v>-81.71405011370113</v>
       </c>
-      <c r="S54">
-        <v>1</v>
-      </c>
       <c r="T54">
         <v>-513.3567931933326</v>
       </c>
@@ -4462,10 +4303,10 @@
         <v>0.550547410568094</v>
       </c>
       <c r="E55">
-        <v>128.2740563103069</v>
+        <v>135.5000297590243</v>
       </c>
       <c r="F55">
-        <v>22.08374464642444</v>
+        <v>14.85777119770705</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -4505,9 +4346,6 @@
       <c r="R55">
         <v>-40.86534077375143</v>
       </c>
-      <c r="S55">
-        <v>1.983050847457627</v>
-      </c>
       <c r="T55">
         <v>-847.4048581032467</v>
       </c>
@@ -4537,10 +4375,10 @@
         <v>0.4377367241241371</v>
       </c>
       <c r="E56">
-        <v>467.2697511388687</v>
+        <v>484.537834519546</v>
       </c>
       <c r="F56">
-        <v>51.8277083447955</v>
+        <v>34.55962496411826</v>
       </c>
       <c r="G56">
         <v>8</v>
@@ -4580,9 +4418,6 @@
       <c r="R56">
         <v>-84.48347779409866</v>
       </c>
-      <c r="S56">
-        <v>5.186440677966102</v>
-      </c>
       <c r="T56">
         <v>-639.6921167376527</v>
       </c>
@@ -4612,10 +4447,10 @@
         <v>0.9530225769130095</v>
       </c>
       <c r="E57">
-        <v>174.5415359090369</v>
+        <v>199.5218165251513</v>
       </c>
       <c r="F57">
-        <v>82.66395358140124</v>
+        <v>57.6836729652868</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -4655,9 +4490,6 @@
       <c r="R57">
         <v>-191.2174984961702</v>
       </c>
-      <c r="S57">
-        <v>1.983050847457627</v>
-      </c>
       <c r="T57">
         <v>-262.5861493309494</v>
       </c>
@@ -4687,10 +4519,10 @@
         <v>0.4838736792954186</v>
       </c>
       <c r="E58">
-        <v>512.0390253260225</v>
+        <v>534.8291167459547</v>
       </c>
       <c r="F58">
-        <v>68.88641666852527</v>
+        <v>46.09632524859308</v>
       </c>
       <c r="G58">
         <v>16</v>
@@ -4730,9 +4562,6 @@
       <c r="R58">
         <v>-40.92084729343487</v>
       </c>
-      <c r="S58">
-        <v>12.3</v>
-      </c>
       <c r="T58">
         <v>-30.98620230848367</v>
       </c>
@@ -4762,10 +4591,10 @@
         <v>0.6306904904028244</v>
       </c>
       <c r="E59">
-        <v>326.7760285968058</v>
+        <v>350.2316701823168</v>
       </c>
       <c r="F59">
-        <v>72.71930576887411</v>
+        <v>49.26366418336306</v>
       </c>
       <c r="G59">
         <v>4</v>
@@ -4805,9 +4634,6 @@
       <c r="R59">
         <v>-28.55390149364721</v>
       </c>
-      <c r="S59">
-        <v>3.416666666666667</v>
-      </c>
       <c r="T59">
         <v>198.2104816727272</v>
       </c>
@@ -4837,10 +4663,10 @@
         <v>0.2997586926792622</v>
       </c>
       <c r="E60">
-        <v>584.1344561822083</v>
+        <v>594.6318568795867</v>
       </c>
       <c r="F60">
-        <v>30.94910855331489</v>
+        <v>20.45170785593643</v>
       </c>
       <c r="G60">
         <v>16</v>
@@ -4880,9 +4706,6 @@
       <c r="R60">
         <v>-46.53095406663628</v>
       </c>
-      <c r="S60">
-        <v>11.28813559322034</v>
-      </c>
       <c r="T60">
         <v>150.8143772717958</v>
       </c>
@@ -4912,10 +4735,10 @@
         <v>0.3247363896757173</v>
       </c>
       <c r="E61">
-        <v>329.8014943043372</v>
+        <v>336.7173666980587</v>
       </c>
       <c r="F61">
-        <v>20.44755006263813</v>
+        <v>13.53167766891659</v>
       </c>
       <c r="G61">
         <v>16</v>
@@ -4955,9 +4778,6 @@
       <c r="R61">
         <v>-17.32788108365847</v>
       </c>
-      <c r="S61">
-        <v>13</v>
-      </c>
       <c r="T61">
         <v>841.474237757583</v>
       </c>
@@ -4987,10 +4807,10 @@
         <v>0.8718211300659418</v>
       </c>
       <c r="E62">
-        <v>2.937952584325763</v>
+        <v>3.302703498629482</v>
       </c>
       <c r="F62">
-        <v>1.186469039215216</v>
+        <v>0.8217181249114969</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5030,9 +4850,6 @@
       <c r="R62">
         <v>-31.01756894557587</v>
       </c>
-      <c r="S62">
-        <v>0.8571428571428571</v>
-      </c>
       <c r="T62">
         <v>-587.0267300596598</v>
       </c>
@@ -5062,10 +4879,10 @@
         <v>0.4021484694905896</v>
       </c>
       <c r="E63">
-        <v>308.8410065798885</v>
+        <v>318.5746577371695</v>
       </c>
       <c r="F63">
-        <v>29.06553519258472</v>
+        <v>19.33188403530369</v>
       </c>
       <c r="G63">
         <v>4</v>
@@ -5105,9 +4922,6 @@
       <c r="R63">
         <v>-109.0449560586357</v>
       </c>
-      <c r="S63">
-        <v>2.95</v>
-      </c>
       <c r="T63">
         <v>-1087.409657566273</v>
       </c>
@@ -5137,10 +4951,10 @@
         <v>0.363350988452983</v>
       </c>
       <c r="E64">
-        <v>158.2040580512468</v>
+        <v>162.3176441894802</v>
       </c>
       <c r="F64">
-        <v>12.2200329662258</v>
+        <v>8.106446827992443</v>
       </c>
       <c r="G64">
         <v>8</v>
@@ -5180,9 +4994,6 @@
       <c r="R64">
         <v>-41.26914297593793</v>
       </c>
-      <c r="S64">
-        <v>7.689655172413793</v>
-      </c>
       <c r="T64">
         <v>858.0909074004417</v>
       </c>
@@ -5212,10 +5023,10 @@
         <v>0.8235544356909044</v>
       </c>
       <c r="E65">
-        <v>136.5786292195064</v>
+        <v>152.0294218391515</v>
       </c>
       <c r="F65">
-        <v>49.75682087374545</v>
+        <v>34.30602825410028</v>
       </c>
       <c r="G65">
         <v>4</v>
@@ -5255,9 +5066,6 @@
       <c r="R65">
         <v>-149.8788793669305</v>
       </c>
-      <c r="S65">
-        <v>2.694915254237288</v>
-      </c>
       <c r="T65">
         <v>-103.0166085441775</v>
       </c>
@@ -5287,10 +5095,10 @@
         <v>0.4007894481461658</v>
       </c>
       <c r="E66">
-        <v>170.87780879856</v>
+        <v>176.2290297937859</v>
       </c>
       <c r="F66">
-        <v>15.97620502076103</v>
+        <v>10.62498402553516</v>
       </c>
       <c r="G66">
         <v>8</v>
@@ -5330,9 +5138,6 @@
       <c r="R66">
         <v>-37.57116634028481</v>
       </c>
-      <c r="S66">
-        <v>6.677966101694915</v>
-      </c>
       <c r="T66">
         <v>-350.5494967596808</v>
       </c>
@@ -5362,10 +5167,10 @@
         <v>1.248113397842487</v>
       </c>
       <c r="E67">
-        <v>69.98184430407868</v>
+        <v>84.99890117094834</v>
       </c>
       <c r="F67">
-        <v>52.96121465192923</v>
+        <v>37.94415778505956</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -5405,9 +5210,6 @@
       <c r="R67">
         <v>-160.6197356223814</v>
       </c>
-      <c r="S67">
-        <v>1</v>
-      </c>
       <c r="T67">
         <v>-391.0487455847381</v>
       </c>
@@ -5437,10 +5239,10 @@
         <v>0.5522882703459885</v>
       </c>
       <c r="E68">
-        <v>325.5230534962093</v>
+        <v>343.9653260713237</v>
       </c>
       <c r="F68">
-        <v>56.37946035488511</v>
+        <v>37.93718777977068</v>
       </c>
       <c r="G68">
         <v>8</v>
@@ -5480,9 +5282,6 @@
       <c r="R68">
         <v>-21.87339065942142</v>
       </c>
-      <c r="S68">
-        <v>6.610169491525424</v>
-      </c>
       <c r="T68">
         <v>305.0015765069846</v>
       </c>
@@ -5512,10 +5311,10 @@
         <v>0.5389454749052142</v>
       </c>
       <c r="E69">
-        <v>401.3555897833736</v>
+        <v>423.1102946144026</v>
       </c>
       <c r="F69">
-        <v>66.35423578668548</v>
+        <v>44.59953095565652</v>
       </c>
       <c r="G69">
         <v>4</v>
@@ -5555,9 +5354,6 @@
       <c r="R69">
         <v>-105.8550251002139</v>
       </c>
-      <c r="S69">
-        <v>3.779661016949153</v>
-      </c>
       <c r="T69">
         <v>-567.0975784374136</v>
       </c>
@@ -5587,10 +5383,10 @@
         <v>1.329019018293494</v>
       </c>
       <c r="E70">
-        <v>32.82160242321872</v>
+        <v>40.51656849467178</v>
       </c>
       <c r="F70">
-        <v>27.61479252518262</v>
+        <v>19.91982645372956</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -5630,9 +5426,6 @@
       <c r="R70">
         <v>-37.38719156763692</v>
       </c>
-      <c r="S70">
-        <v>0.9833333333333333</v>
-      </c>
       <c r="T70">
         <v>-505.8342403352136</v>
       </c>
@@ -5662,10 +5455,10 @@
         <v>1.157735147111956</v>
       </c>
       <c r="E71">
-        <v>88.31281466406686</v>
+        <v>105.3088524494946</v>
       </c>
       <c r="F71">
-        <v>58.7802809764038</v>
+        <v>41.78424319097607</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -5705,9 +5498,6 @@
       <c r="R71">
         <v>-97.35207434179432</v>
       </c>
-      <c r="S71">
-        <v>0.9833333333333333</v>
-      </c>
       <c r="T71">
         <v>-286.9955872458959</v>
       </c>
@@ -5737,10 +5527,10 @@
         <v>0.7609121363849716</v>
       </c>
       <c r="E72">
-        <v>78.54965686035638</v>
+        <v>86.33932894291543</v>
       </c>
       <c r="F72">
-        <v>24.76726791522508</v>
+        <v>16.97759583266603</v>
       </c>
       <c r="G72">
         <v>2</v>
@@ -5780,9 +5570,6 @@
       <c r="R72">
         <v>-24.8456317021995</v>
       </c>
-      <c r="S72">
-        <v>2</v>
-      </c>
       <c r="T72">
         <v>-290.4258767432515</v>
       </c>
@@ -5812,10 +5599,10 @@
         <v>1.18531503324793</v>
       </c>
       <c r="E73">
-        <v>56.73518466949175</v>
+        <v>68.03654285933914</v>
       </c>
       <c r="F73">
-        <v>39.31947951359157</v>
+        <v>28.01812132374418</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -5855,9 +5642,6 @@
       <c r="R73">
         <v>-39.53812623376415</v>
       </c>
-      <c r="S73">
-        <v>1.9</v>
-      </c>
       <c r="T73">
         <v>-753.4259683304886</v>
       </c>
@@ -5887,10 +5671,10 @@
         <v>0.4240949039837977</v>
       </c>
       <c r="E74">
-        <v>265.8359355101423</v>
+        <v>275.0947672395676</v>
       </c>
       <c r="F74">
-        <v>27.73374427768789</v>
+        <v>18.47491254826258</v>
       </c>
       <c r="G74">
         <v>8</v>
@@ -5930,9 +5714,6 @@
       <c r="R74">
         <v>-64.03889225641915</v>
       </c>
-      <c r="S74">
-        <v>6.35593220338983</v>
-      </c>
       <c r="T74">
         <v>16.70456314787427</v>
       </c>
@@ -5962,10 +5743,10 @@
         <v>0.7268298288501506</v>
       </c>
       <c r="E75">
-        <v>114.4584268146812</v>
+        <v>124.9619728288896</v>
       </c>
       <c r="F75">
-        <v>33.16993585159676</v>
+        <v>22.66638983738835</v>
       </c>
       <c r="G75">
         <v>2</v>
@@ -6005,9 +5786,6 @@
       <c r="R75">
         <v>-74.28940945752831</v>
       </c>
-      <c r="S75">
-        <v>2</v>
-      </c>
       <c r="T75">
         <v>-420.5163597635979</v>
       </c>
@@ -6037,10 +5815,10 @@
         <v>0.7429673733188065</v>
       </c>
       <c r="E76">
-        <v>602.156848362108</v>
+        <v>659.5143436454306</v>
       </c>
       <c r="F76">
-        <v>181.7144213462174</v>
+        <v>124.3569260628948</v>
       </c>
       <c r="G76">
         <v>16</v>
@@ -6080,9 +5858,6 @@
       <c r="R76">
         <v>-70.40174225218152</v>
       </c>
-      <c r="S76">
-        <v>10.48333333333333</v>
-      </c>
       <c r="T76">
         <v>255.4085737801854</v>
       </c>
@@ -6112,10 +5887,10 @@
         <v>0.354893257991813</v>
       </c>
       <c r="E77">
-        <v>605.0586427189581</v>
+        <v>620.1001861232746</v>
       </c>
       <c r="F77">
-        <v>44.63520244281858</v>
+        <v>29.5936590385021</v>
       </c>
       <c r="G77">
         <v>16</v>
@@ -6155,9 +5930,6 @@
       <c r="R77">
         <v>-75.47952167775412</v>
       </c>
-      <c r="S77">
-        <v>9.85</v>
-      </c>
       <c r="T77">
         <v>-128.2650949350807</v>
       </c>
@@ -6187,10 +5959,10 @@
         <v>0.4018018256644398</v>
       </c>
       <c r="E78">
-        <v>556.9599972865784</v>
+        <v>574.4850103687164</v>
       </c>
       <c r="F78">
-        <v>52.32870783196051</v>
+        <v>34.80369474982251</v>
       </c>
       <c r="G78">
         <v>2</v>
@@ -6230,9 +6002,6 @@
       <c r="R78">
         <v>-71.52936454912968</v>
       </c>
-      <c r="S78">
-        <v>1.9</v>
-      </c>
       <c r="T78">
         <v>-541.6394727238318</v>
       </c>
@@ -6262,10 +6031,10 @@
         <v>0.4275491918933289</v>
       </c>
       <c r="E79">
-        <v>438.0850502886863</v>
+        <v>453.5769194742682</v>
       </c>
       <c r="F79">
-        <v>46.42729870832886</v>
+        <v>30.93542952274692</v>
       </c>
       <c r="G79">
         <v>4</v>
@@ -6304,9 +6073,6 @@
       </c>
       <c r="R79">
         <v>-23.96617524080266</v>
-      </c>
-      <c r="S79">
-        <v>2.833333333333333</v>
       </c>
       <c r="T79">
         <v>46.72362019437261</v>

--- a/Data Analysis/1_Data/economic_MF_final.xlsx
+++ b/Data Analysis/1_Data/economic_MF_final.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:AB79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,27 +447,52 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>SOC_costs_mid</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>SOC_costs_lo</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>SOC_costs_hi</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>costs_total_mid</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>costs_total_lo</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>costs_total_hi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>costs_total_mid_adj</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>costs_total_lo_adj</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>costs_total_hi_adj</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>meanSR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>SOC_costs_mid</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>SOC_costs_lo</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>SOC_costs_hi</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>costs_total_mid</t>
         </is>
       </c>
     </row>
@@ -530,17 +555,35 @@
       <c r="R2">
         <v>-50.28157516499095</v>
       </c>
+      <c r="S2">
+        <v>776.0019362477558</v>
+      </c>
       <c r="T2">
-        <v>776.0019362477558</v>
+        <v>194.0004840619389</v>
       </c>
       <c r="U2">
-        <v>194.0004840619389</v>
+        <v>2069.338496660682</v>
       </c>
       <c r="V2">
-        <v>2069.338496660682</v>
+        <v>1199.796918580594</v>
       </c>
       <c r="W2">
-        <v>1199.796918580594</v>
+        <v>637.6985898975859</v>
+      </c>
+      <c r="X2">
+        <v>2473.230355490711</v>
+      </c>
+      <c r="Y2">
+        <v>1174.819290662734</v>
+      </c>
+      <c r="Z2">
+        <v>612.7209619797263</v>
+      </c>
+      <c r="AA2">
+        <v>2448.252727572852</v>
+      </c>
+      <c r="AB2">
+        <v>11.83333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -602,17 +645,35 @@
       <c r="R3">
         <v>-62.7502337238665</v>
       </c>
+      <c r="S3">
+        <v>7.583391783192281</v>
+      </c>
       <c r="T3">
-        <v>7.583391783192281</v>
+        <v>1.89584794579807</v>
       </c>
       <c r="U3">
-        <v>1.89584794579807</v>
+        <v>20.22237808851275</v>
       </c>
       <c r="V3">
-        <v>20.22237808851275</v>
+        <v>332.0857615465974</v>
       </c>
       <c r="W3">
-        <v>332.0857615465974</v>
+        <v>351.236851891567</v>
+      </c>
+      <c r="X3">
+        <v>319.8861136695541</v>
+      </c>
+      <c r="Y3">
+        <v>309.9722182278929</v>
+      </c>
+      <c r="Z3">
+        <v>329.1233085728625</v>
+      </c>
+      <c r="AA3">
+        <v>297.7725703508496</v>
+      </c>
+      <c r="AB3">
+        <v>5.728813559322034</v>
       </c>
     </row>
     <row r="4">
@@ -674,17 +735,35 @@
       <c r="R4">
         <v>-188.9905626286803</v>
       </c>
+      <c r="S4">
+        <v>74.56707340401853</v>
+      </c>
       <c r="T4">
-        <v>74.56707340401853</v>
+        <v>18.64176835100463</v>
       </c>
       <c r="U4">
-        <v>18.64176835100463</v>
+        <v>198.8455290773827</v>
       </c>
       <c r="V4">
-        <v>198.8455290773827</v>
+        <v>269.0197711049724</v>
       </c>
       <c r="W4">
-        <v>269.0197711049724</v>
+        <v>287.9032304258111</v>
+      </c>
+      <c r="X4">
+        <v>318.4894624044839</v>
+      </c>
+      <c r="Y4">
+        <v>228.2054794829228</v>
+      </c>
+      <c r="Z4">
+        <v>247.0889388037616</v>
+      </c>
+      <c r="AA4">
+        <v>277.6751707824344</v>
+      </c>
+      <c r="AB4">
+        <v>6.186440677966102</v>
       </c>
     </row>
     <row r="5">
@@ -746,17 +825,35 @@
       <c r="R5">
         <v>-162.3022324266065</v>
       </c>
+      <c r="S5">
+        <v>-381.4278283481973</v>
+      </c>
       <c r="T5">
-        <v>-381.4278283481973</v>
+        <v>-95.35695708704932</v>
       </c>
       <c r="U5">
-        <v>-95.35695708704932</v>
+        <v>-1017.140875595193</v>
       </c>
       <c r="V5">
-        <v>-1017.140875595193</v>
+        <v>-44.23153113298775</v>
       </c>
       <c r="W5">
-        <v>-44.23153113298775</v>
+        <v>306.0839737970252</v>
+      </c>
+      <c r="X5">
+        <v>-744.1892120488487</v>
+      </c>
+      <c r="Y5">
+        <v>-97.50655458481287</v>
+      </c>
+      <c r="Z5">
+        <v>252.8089503452001</v>
+      </c>
+      <c r="AA5">
+        <v>-797.4642355006738</v>
+      </c>
+      <c r="AB5">
+        <v>3.35</v>
       </c>
     </row>
     <row r="6">
@@ -818,17 +915,35 @@
       <c r="R6">
         <v>-130.8609161569784</v>
       </c>
+      <c r="S6">
+        <v>-405.2626142571454</v>
+      </c>
       <c r="T6">
-        <v>-405.2626142571454</v>
+        <v>-101.3156535642864</v>
       </c>
       <c r="U6">
-        <v>-101.3156535642864</v>
+        <v>-1080.700304685721</v>
       </c>
       <c r="V6">
-        <v>-1080.700304685721</v>
+        <v>-90.0137311573996</v>
       </c>
       <c r="W6">
-        <v>-90.0137311573996</v>
+        <v>265.73234218093</v>
+      </c>
+      <c r="X6">
+        <v>-817.250534231446</v>
+      </c>
+      <c r="Y6">
+        <v>-186.8008859237345</v>
+      </c>
+      <c r="Z6">
+        <v>168.945187414595</v>
+      </c>
+      <c r="AA6">
+        <v>-914.0376889977808</v>
+      </c>
+      <c r="AB6">
+        <v>1.864406779661017</v>
       </c>
     </row>
     <row r="7">
@@ -890,17 +1005,35 @@
       <c r="R7">
         <v>-30.39190942733287</v>
       </c>
+      <c r="S7">
+        <v>212.5784837509758</v>
+      </c>
       <c r="T7">
-        <v>212.5784837509758</v>
+        <v>53.14462093774394</v>
       </c>
       <c r="U7">
-        <v>53.14462093774394</v>
+        <v>566.8759566692687</v>
       </c>
       <c r="V7">
-        <v>566.8759566692687</v>
+        <v>519.165044223625</v>
       </c>
       <c r="W7">
-        <v>519.165044223625</v>
+        <v>371.7613122253791</v>
+      </c>
+      <c r="X7">
+        <v>861.432386326932</v>
+      </c>
+      <c r="Y7">
+        <v>493.5979868701391</v>
+      </c>
+      <c r="Z7">
+        <v>346.1942548718931</v>
+      </c>
+      <c r="AA7">
+        <v>835.8653289734461</v>
+      </c>
+      <c r="AB7">
+        <v>12.89830508474576</v>
       </c>
     </row>
     <row r="8">
@@ -962,17 +1095,35 @@
       <c r="R8">
         <v>-140.0203770131957</v>
       </c>
+      <c r="S8">
+        <v>-373.4422893248743</v>
+      </c>
       <c r="T8">
-        <v>-373.4422893248743</v>
+        <v>-93.36057233121856</v>
       </c>
       <c r="U8">
-        <v>-93.36057233121856</v>
+        <v>-995.8461048663313</v>
       </c>
       <c r="V8">
-        <v>-995.8461048663313</v>
+        <v>-268.3569332170637</v>
       </c>
       <c r="W8">
-        <v>-268.3569332170637</v>
+        <v>67.14951634431534</v>
+      </c>
+      <c r="X8">
+        <v>-946.1854813262441</v>
+      </c>
+      <c r="Y8">
+        <v>-299.5629172595596</v>
+      </c>
+      <c r="Z8">
+        <v>35.94353230181943</v>
+      </c>
+      <c r="AA8">
+        <v>-977.39146536874</v>
+      </c>
+      <c r="AB8">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1034,17 +1185,35 @@
       <c r="R9">
         <v>-229.3370740969741</v>
       </c>
+      <c r="S9">
+        <v>-356.7084314993093</v>
+      </c>
       <c r="T9">
-        <v>-356.7084314993093</v>
+        <v>-89.17710787482731</v>
       </c>
       <c r="U9">
-        <v>-89.17710787482731</v>
+        <v>-951.2224839981581</v>
       </c>
       <c r="V9">
-        <v>-951.2224839981581</v>
+        <v>-112.489464672712</v>
       </c>
       <c r="W9">
-        <v>-112.489464672712</v>
+        <v>245.8211174484889</v>
+      </c>
+      <c r="X9">
+        <v>-797.7827756682797</v>
+      </c>
+      <c r="Y9">
+        <v>-164.1507470642426</v>
+      </c>
+      <c r="Z9">
+        <v>194.1598350569583</v>
+      </c>
+      <c r="AA9">
+        <v>-849.4440580598102</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1106,17 +1275,35 @@
       <c r="R10">
         <v>-106.6752976432115</v>
       </c>
+      <c r="S10">
+        <v>-453.0081391389492</v>
+      </c>
       <c r="T10">
-        <v>-453.0081391389492</v>
+        <v>-113.2520347847373</v>
       </c>
       <c r="U10">
-        <v>-113.2520347847373</v>
+        <v>-1208.021704370531</v>
       </c>
       <c r="V10">
-        <v>-1208.021704370531</v>
+        <v>-440.8477004595866</v>
       </c>
       <c r="W10">
-        <v>-440.8477004595866</v>
+        <v>-58.8659574549369</v>
+      </c>
+      <c r="X10">
+        <v>-1238.086904341606</v>
+      </c>
+      <c r="Y10">
+        <v>-461.0820232260895</v>
+      </c>
+      <c r="Z10">
+        <v>-79.10028022143968</v>
+      </c>
+      <c r="AA10">
+        <v>-1258.321227108109</v>
+      </c>
+      <c r="AB10">
+        <v>0.9523809523809523</v>
       </c>
     </row>
     <row r="11">
@@ -1178,17 +1365,35 @@
       <c r="R11">
         <v>-55.81306805400369</v>
       </c>
+      <c r="S11">
+        <v>1022.72996477033</v>
+      </c>
       <c r="T11">
-        <v>1022.72996477033</v>
+        <v>255.6824911925825</v>
       </c>
       <c r="U11">
-        <v>255.6824911925825</v>
+        <v>2727.279906054213</v>
       </c>
       <c r="V11">
-        <v>2727.279906054213</v>
+        <v>1340.228588122322</v>
       </c>
       <c r="W11">
-        <v>1340.228588122322</v>
+        <v>595.2737873159515</v>
+      </c>
+      <c r="X11">
+        <v>3022.685856634829</v>
+      </c>
+      <c r="Y11">
+        <v>1315.037476283804</v>
+      </c>
+      <c r="Z11">
+        <v>570.0826754774328</v>
+      </c>
+      <c r="AA11">
+        <v>2997.49474479631</v>
+      </c>
+      <c r="AB11">
+        <v>11.03333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1250,17 +1455,35 @@
       <c r="R12">
         <v>-162.4702296753888</v>
       </c>
+      <c r="S12">
+        <v>-370.1816630423123</v>
+      </c>
       <c r="T12">
-        <v>-370.1816630423123</v>
+        <v>-92.54541576057808</v>
       </c>
       <c r="U12">
-        <v>-92.54541576057808</v>
+        <v>-987.1511014461662</v>
       </c>
       <c r="V12">
-        <v>-987.1511014461662</v>
+        <v>25.22115899744279</v>
       </c>
       <c r="W12">
-        <v>25.22115899744279</v>
+        <v>367.1685388590184</v>
+      </c>
+      <c r="X12">
+        <v>-656.0594119862524</v>
+      </c>
+      <c r="Y12">
+        <v>-22.7144506118965</v>
+      </c>
+      <c r="Z12">
+        <v>319.2329292496792</v>
+      </c>
+      <c r="AA12">
+        <v>-703.9950215955917</v>
+      </c>
+      <c r="AB12">
+        <v>5.3</v>
       </c>
     </row>
     <row r="13">
@@ -1322,17 +1545,35 @@
       <c r="R13">
         <v>-148.852252336754</v>
       </c>
+      <c r="S13">
+        <v>-168.5018317652187</v>
+      </c>
       <c r="T13">
-        <v>-168.5018317652187</v>
+        <v>-42.12545794130468</v>
       </c>
       <c r="U13">
-        <v>-42.12545794130468</v>
+        <v>-449.3382180405833</v>
       </c>
       <c r="V13">
-        <v>-449.3382180405833</v>
+        <v>215.7509264607076</v>
       </c>
       <c r="W13">
-        <v>215.7509264607076</v>
+        <v>401.0479835012534</v>
+      </c>
+      <c r="X13">
+        <v>-124.0061430312888</v>
+      </c>
+      <c r="Y13">
+        <v>154.4443195002807</v>
+      </c>
+      <c r="Z13">
+        <v>339.7413765408265</v>
+      </c>
+      <c r="AA13">
+        <v>-185.3127499917157</v>
+      </c>
+      <c r="AB13">
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -1394,17 +1635,35 @@
       <c r="R14">
         <v>-40.78101627379836</v>
       </c>
+      <c r="S14">
+        <v>433.4735654111012</v>
+      </c>
       <c r="T14">
-        <v>433.4735654111012</v>
+        <v>108.3683913527753</v>
       </c>
       <c r="U14">
-        <v>108.3683913527753</v>
+        <v>1155.929507762937</v>
       </c>
       <c r="V14">
-        <v>1155.929507762937</v>
+        <v>665.7460203906239</v>
       </c>
       <c r="W14">
-        <v>665.7460203906239</v>
+        <v>356.7833319406766</v>
+      </c>
+      <c r="X14">
+        <v>1372.059477134081</v>
+      </c>
+      <c r="Y14">
+        <v>642.0721786034248</v>
+      </c>
+      <c r="Z14">
+        <v>333.1094901534775</v>
+      </c>
+      <c r="AA14">
+        <v>1348.385635346882</v>
+      </c>
+      <c r="AB14">
+        <v>6.559322033898305</v>
       </c>
     </row>
     <row r="15">
@@ -1466,17 +1725,35 @@
       <c r="R15">
         <v>-92.49525164652148</v>
       </c>
+      <c r="S15">
+        <v>-607.3755880406841</v>
+      </c>
       <c r="T15">
-        <v>-607.3755880406841</v>
+        <v>-151.843897010171</v>
       </c>
       <c r="U15">
-        <v>-151.843897010171</v>
+        <v>-1619.668234775158</v>
       </c>
       <c r="V15">
-        <v>-1619.668234775158</v>
+        <v>-567.2566809043824</v>
       </c>
       <c r="W15">
-        <v>-567.2566809043824</v>
+        <v>-75.1122860971212</v>
+      </c>
+      <c r="X15">
+        <v>-1616.162031415604</v>
+      </c>
+      <c r="Y15">
+        <v>-613.1997392876918</v>
+      </c>
+      <c r="Z15">
+        <v>-121.0553444804307</v>
+      </c>
+      <c r="AA15">
+        <v>-1662.105089798914</v>
+      </c>
+      <c r="AB15">
+        <v>0.95</v>
       </c>
     </row>
     <row r="16">
@@ -1538,17 +1815,35 @@
       <c r="R16">
         <v>-27.27674853955119</v>
       </c>
+      <c r="S16">
+        <v>-637.9332337409667</v>
+      </c>
       <c r="T16">
-        <v>-637.9332337409667</v>
+        <v>-159.4833084352417</v>
       </c>
       <c r="U16">
-        <v>-159.4833084352417</v>
+        <v>-1701.155289975911</v>
       </c>
       <c r="V16">
-        <v>-1701.155289975911</v>
+        <v>-478.7079655648573</v>
       </c>
       <c r="W16">
-        <v>-478.7079655648573</v>
+        <v>10.53900603777336</v>
+      </c>
+      <c r="X16">
+        <v>-1552.727068096707</v>
+      </c>
+      <c r="Y16">
+        <v>-505.2378736507658</v>
+      </c>
+      <c r="Z16">
+        <v>-15.99090204813513</v>
+      </c>
+      <c r="AA16">
+        <v>-1579.256976182616</v>
+      </c>
+      <c r="AB16">
+        <v>1.983050847457627</v>
       </c>
     </row>
     <row r="17">
@@ -1610,17 +1905,35 @@
       <c r="R17">
         <v>-69.41329029307803</v>
       </c>
+      <c r="S17">
+        <v>-998.2419574417249</v>
+      </c>
       <c r="T17">
-        <v>-998.2419574417249</v>
+        <v>-249.5604893604312</v>
       </c>
       <c r="U17">
-        <v>-249.5604893604312</v>
+        <v>-2661.978553177933</v>
       </c>
       <c r="V17">
-        <v>-2661.978553177933</v>
+        <v>-835.1601508826228</v>
       </c>
       <c r="W17">
-        <v>-835.1601508826228</v>
+        <v>-59.00258872698569</v>
+      </c>
+      <c r="X17">
+        <v>-2526.372840693175</v>
+      </c>
+      <c r="Y17">
+        <v>-862.2051580861246</v>
+      </c>
+      <c r="Z17">
+        <v>-86.04759593048749</v>
+      </c>
+      <c r="AA17">
+        <v>-2553.417847896676</v>
+      </c>
+      <c r="AB17">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1682,17 +1995,35 @@
       <c r="R18">
         <v>-52.17060611591119</v>
       </c>
+      <c r="S18">
+        <v>-757.7101452362072</v>
+      </c>
       <c r="T18">
-        <v>-757.7101452362072</v>
+        <v>-189.4275363090518</v>
       </c>
       <c r="U18">
-        <v>-189.4275363090518</v>
+        <v>-2020.560387296552</v>
       </c>
       <c r="V18">
-        <v>-2020.560387296552</v>
+        <v>-720.5702479627346</v>
       </c>
       <c r="W18">
-        <v>-720.5702479627346</v>
+        <v>-131.6367741146976</v>
+      </c>
+      <c r="X18">
+        <v>-2004.071354943961</v>
+      </c>
+      <c r="Y18">
+        <v>-735.2204064114636</v>
+      </c>
+      <c r="Z18">
+        <v>-146.2869325634267</v>
+      </c>
+      <c r="AA18">
+        <v>-2018.72151339269</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1754,17 +2085,35 @@
       <c r="R19">
         <v>-52.46373763961006</v>
       </c>
+      <c r="S19">
+        <v>-744.369023474728</v>
+      </c>
       <c r="T19">
-        <v>-744.369023474728</v>
+        <v>-186.092255868682</v>
       </c>
       <c r="U19">
-        <v>-186.092255868682</v>
+        <v>-1984.984062599275</v>
       </c>
       <c r="V19">
-        <v>-1984.984062599275</v>
+        <v>-500.4924387744687</v>
       </c>
       <c r="W19">
-        <v>-500.4924387744687</v>
+        <v>78.55122498058967</v>
+      </c>
+      <c r="X19">
+        <v>-1761.874374048028</v>
+      </c>
+      <c r="Y19">
+        <v>-533.2304330549545</v>
+      </c>
+      <c r="Z19">
+        <v>45.81323070010387</v>
+      </c>
+      <c r="AA19">
+        <v>-1794.612368328514</v>
+      </c>
+      <c r="AB19">
+        <v>3.559322033898305</v>
       </c>
     </row>
     <row r="20">
@@ -1826,17 +2175,35 @@
       <c r="R20">
         <v>-80.56385715887156</v>
       </c>
+      <c r="S20">
+        <v>-156.5795148059204</v>
+      </c>
       <c r="T20">
-        <v>-156.5795148059204</v>
+        <v>-39.14487870148009</v>
       </c>
       <c r="U20">
-        <v>-39.14487870148009</v>
+        <v>-417.5453728157876</v>
       </c>
       <c r="V20">
-        <v>-417.5453728157876</v>
+        <v>419.1702552231611</v>
       </c>
       <c r="W20">
-        <v>419.1702552231611</v>
+        <v>568.4947514529881</v>
+      </c>
+      <c r="X20">
+        <v>126.3145370879073</v>
+      </c>
+      <c r="Y20">
+        <v>395.6144780887071</v>
+      </c>
+      <c r="Z20">
+        <v>544.9389743185341</v>
+      </c>
+      <c r="AA20">
+        <v>102.7587599534533</v>
+      </c>
+      <c r="AB20">
+        <v>12.15254237288136</v>
       </c>
     </row>
     <row r="21">
@@ -1898,17 +2265,35 @@
       <c r="R21">
         <v>-23.97763894200598</v>
       </c>
+      <c r="S21">
+        <v>72.5154982273032</v>
+      </c>
       <c r="T21">
-        <v>72.5154982273032</v>
+        <v>18.1288745568258</v>
       </c>
       <c r="U21">
-        <v>18.1288745568258</v>
+        <v>193.3746619394752</v>
       </c>
       <c r="V21">
-        <v>193.3746619394752</v>
+        <v>221.6466975868286</v>
       </c>
       <c r="W21">
-        <v>221.6466975868286</v>
+        <v>176.7512226642285</v>
+      </c>
+      <c r="X21">
+        <v>333.0147125511232</v>
+      </c>
+      <c r="Y21">
+        <v>182.0443655397778</v>
+      </c>
+      <c r="Z21">
+        <v>137.1488906171778</v>
+      </c>
+      <c r="AA21">
+        <v>293.4123805040724</v>
+      </c>
+      <c r="AB21">
+        <v>3.694915254237288</v>
       </c>
     </row>
     <row r="22">
@@ -1970,17 +2355,35 @@
       <c r="R22">
         <v>-45.07948438017191</v>
       </c>
+      <c r="S22">
+        <v>822.0031998972684</v>
+      </c>
       <c r="T22">
-        <v>822.0031998972684</v>
+        <v>205.5007999743171</v>
       </c>
       <c r="U22">
-        <v>205.5007999743171</v>
+        <v>2192.008533059382</v>
       </c>
       <c r="V22">
-        <v>2192.008533059382</v>
+        <v>1285.335184067434</v>
       </c>
       <c r="W22">
-        <v>1285.335184067434</v>
+        <v>686.6767467116343</v>
+      </c>
+      <c r="X22">
+        <v>2637.496554662397</v>
+      </c>
+      <c r="Y22">
+        <v>1262.956351865978</v>
+      </c>
+      <c r="Z22">
+        <v>664.297914510178</v>
+      </c>
+      <c r="AA22">
+        <v>2615.11772246094</v>
+      </c>
+      <c r="AB22">
+        <v>3.6</v>
       </c>
     </row>
     <row r="23">
@@ -2042,17 +2445,35 @@
       <c r="R23">
         <v>-17.7815422654048</v>
       </c>
+      <c r="S23">
+        <v>-50.02277013860132</v>
+      </c>
       <c r="T23">
-        <v>-50.02277013860132</v>
+        <v>-12.50569253465033</v>
       </c>
       <c r="U23">
-        <v>-12.50569253465033</v>
+        <v>-133.3940537029368</v>
       </c>
       <c r="V23">
-        <v>-133.3940537029368</v>
+        <v>143.8596715655736</v>
       </c>
       <c r="W23">
-        <v>143.8596715655736</v>
+        <v>188.4152763162473</v>
+      </c>
+      <c r="X23">
+        <v>53.44986085451541</v>
+      </c>
+      <c r="Y23">
+        <v>113.3344522565354</v>
+      </c>
+      <c r="Z23">
+        <v>157.8900570072091</v>
+      </c>
+      <c r="AA23">
+        <v>22.92464154547721</v>
+      </c>
+      <c r="AB23">
+        <v>1.983050847457627</v>
       </c>
     </row>
     <row r="24">
@@ -2114,17 +2535,35 @@
       <c r="R24">
         <v>-120.8238153226634</v>
       </c>
+      <c r="S24">
+        <v>-216.7298338907898</v>
+      </c>
       <c r="T24">
-        <v>-216.7298338907898</v>
+        <v>-54.18245847269746</v>
       </c>
       <c r="U24">
-        <v>-54.18245847269746</v>
+        <v>-577.9462237087729</v>
       </c>
       <c r="V24">
-        <v>-577.9462237087729</v>
+        <v>-137.527507048459</v>
       </c>
       <c r="W24">
-        <v>-137.527507048459</v>
+        <v>72.84596193485439</v>
+      </c>
+      <c r="X24">
+        <v>-546.569990431663</v>
+      </c>
+      <c r="Y24">
+        <v>-167.0975023124461</v>
+      </c>
+      <c r="Z24">
+        <v>43.27596667086719</v>
+      </c>
+      <c r="AA24">
+        <v>-576.1399856956501</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2186,17 +2625,35 @@
       <c r="R25">
         <v>-45.6945025391969</v>
       </c>
+      <c r="S25">
+        <v>-70.16476144728868</v>
+      </c>
       <c r="T25">
-        <v>-70.16476144728868</v>
+        <v>-17.54119036182217</v>
       </c>
       <c r="U25">
-        <v>-17.54119036182217</v>
+        <v>-187.1060305261032</v>
       </c>
       <c r="V25">
-        <v>-187.1060305261032</v>
+        <v>71.88984265032799</v>
       </c>
       <c r="W25">
-        <v>71.88984265032799</v>
+        <v>142.6008209908933</v>
+      </c>
+      <c r="X25">
+        <v>-63.13883368358529</v>
+      </c>
+      <c r="Y25">
+        <v>15.51834537401299</v>
+      </c>
+      <c r="Z25">
+        <v>86.22932371457827</v>
+      </c>
+      <c r="AA25">
+        <v>-119.5103309599003</v>
+      </c>
+      <c r="AB25">
+        <v>0.9833333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -2258,17 +2715,35 @@
       <c r="R26">
         <v>-59.87185375948937</v>
       </c>
+      <c r="S26">
+        <v>458.1313522679775</v>
+      </c>
       <c r="T26">
-        <v>458.1313522679775</v>
+        <v>114.5328380669944</v>
       </c>
       <c r="U26">
-        <v>114.5328380669944</v>
+        <v>1221.68360604794</v>
       </c>
       <c r="V26">
-        <v>1221.68360604794</v>
+        <v>741.9088060560481</v>
       </c>
       <c r="W26">
-        <v>741.9088060560481</v>
+        <v>422.0095673015295</v>
+      </c>
+      <c r="X26">
+        <v>1481.761784389546</v>
+      </c>
+      <c r="Y26">
+        <v>726.1001737160364</v>
+      </c>
+      <c r="Z26">
+        <v>406.2009349615178</v>
+      </c>
+      <c r="AA26">
+        <v>1465.953152049534</v>
+      </c>
+      <c r="AB26">
+        <v>3.677966101694915</v>
       </c>
     </row>
     <row r="27">
@@ -2330,17 +2805,35 @@
       <c r="R27">
         <v>-48.31947164076955</v>
       </c>
+      <c r="S27">
+        <v>-417.5614356405866</v>
+      </c>
       <c r="T27">
-        <v>-417.5614356405866</v>
+        <v>-104.3903589101467</v>
       </c>
       <c r="U27">
-        <v>-104.3903589101467</v>
+        <v>-1113.497161708231</v>
       </c>
       <c r="V27">
-        <v>-1113.497161708231</v>
+        <v>-293.6516502873247</v>
       </c>
       <c r="W27">
-        <v>-293.6516502873247</v>
+        <v>38.64588396758651</v>
+      </c>
+      <c r="X27">
+        <v>-1008.71383387944</v>
+      </c>
+      <c r="Y27">
+        <v>-320.4291188051111</v>
+      </c>
+      <c r="Z27">
+        <v>11.8684154498001</v>
+      </c>
+      <c r="AA27">
+        <v>-1035.491302397227</v>
+      </c>
+      <c r="AB27">
+        <v>1.627118644067797</v>
       </c>
     </row>
     <row r="28">
@@ -2402,17 +2895,35 @@
       <c r="R28">
         <v>-23.98385578133442</v>
       </c>
+      <c r="S28">
+        <v>-152.817217983223</v>
+      </c>
       <c r="T28">
-        <v>-152.817217983223</v>
+        <v>-38.20430449580575</v>
       </c>
       <c r="U28">
-        <v>-38.20430449580575</v>
+        <v>-407.5125812885947</v>
       </c>
       <c r="V28">
-        <v>-407.5125812885947</v>
+        <v>40.03281807292754</v>
       </c>
       <c r="W28">
-        <v>40.03281807292754</v>
+        <v>164.1393411404563</v>
+      </c>
+      <c r="X28">
+        <v>-224.1561548125557</v>
+      </c>
+      <c r="Y28">
+        <v>13.32896056403143</v>
+      </c>
+      <c r="Z28">
+        <v>137.4354836315602</v>
+      </c>
+      <c r="AA28">
+        <v>-250.8600123214518</v>
+      </c>
+      <c r="AB28">
+        <v>3.933333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -2474,17 +2985,35 @@
       <c r="R29">
         <v>-26.07845498112912</v>
       </c>
+      <c r="S29">
+        <v>446.5867656201178</v>
+      </c>
       <c r="T29">
-        <v>446.5867656201178</v>
+        <v>111.6466914050294</v>
       </c>
       <c r="U29">
-        <v>111.6466914050294</v>
+        <v>1190.898041653647</v>
       </c>
       <c r="V29">
-        <v>1190.898041653647</v>
+        <v>824.3725758992462</v>
       </c>
       <c r="W29">
-        <v>824.3725758992462</v>
+        <v>499.7552234475213</v>
+      </c>
+      <c r="X29">
+        <v>1558.361130169412</v>
+      </c>
+      <c r="Y29">
+        <v>799.7175932156176</v>
+      </c>
+      <c r="Z29">
+        <v>475.1002407638928</v>
+      </c>
+      <c r="AA29">
+        <v>1533.706147485783</v>
+      </c>
+      <c r="AB29">
+        <v>12.86440677966102</v>
       </c>
     </row>
     <row r="30">
@@ -2546,17 +3075,35 @@
       <c r="R30">
         <v>-22.93640367452804</v>
       </c>
+      <c r="S30">
+        <v>686.5262758335965</v>
+      </c>
       <c r="T30">
-        <v>686.5262758335965</v>
+        <v>171.6315689583991</v>
       </c>
       <c r="U30">
-        <v>171.6315689583991</v>
+        <v>1830.736735556257</v>
       </c>
       <c r="V30">
-        <v>1830.736735556257</v>
+        <v>1056.545682643785</v>
       </c>
       <c r="W30">
-        <v>1056.545682643785</v>
+        <v>550.7299688897549</v>
+      </c>
+      <c r="X30">
+        <v>2191.677149245278</v>
+      </c>
+      <c r="Y30">
+        <v>1028.33528313792</v>
+      </c>
+      <c r="Z30">
+        <v>522.5195693838896</v>
+      </c>
+      <c r="AA30">
+        <v>2163.466749739413</v>
+      </c>
+      <c r="AB30">
+        <v>6.135593220338983</v>
       </c>
     </row>
     <row r="31">
@@ -2618,17 +3165,35 @@
       <c r="R31">
         <v>-132.4114092948746</v>
       </c>
+      <c r="S31">
+        <v>-348.1786362533473</v>
+      </c>
       <c r="T31">
-        <v>-348.1786362533473</v>
+        <v>-87.04465906333684</v>
       </c>
       <c r="U31">
-        <v>-87.04465906333684</v>
+        <v>-928.4763633422596</v>
       </c>
       <c r="V31">
-        <v>-928.4763633422596</v>
+        <v>-317.3432051086431</v>
       </c>
       <c r="W31">
-        <v>-317.3432051086431</v>
+        <v>-3.796378406078077</v>
+      </c>
+      <c r="X31">
+        <v>-950.05378171011</v>
+      </c>
+      <c r="Y31">
+        <v>-328.6484831664309</v>
+      </c>
+      <c r="Z31">
+        <v>-15.10165646386598</v>
+      </c>
+      <c r="AA31">
+        <v>-961.3590597678979</v>
+      </c>
+      <c r="AB31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2690,17 +3255,35 @@
       <c r="R32">
         <v>-32.7771120167408</v>
       </c>
+      <c r="S32">
+        <v>285.0303606961218</v>
+      </c>
       <c r="T32">
-        <v>285.0303606961218</v>
+        <v>71.25759017403045</v>
       </c>
       <c r="U32">
-        <v>71.25759017403045</v>
+        <v>760.0809618563248</v>
       </c>
       <c r="V32">
-        <v>760.0809618563248</v>
+        <v>625.8505085155165</v>
       </c>
       <c r="W32">
-        <v>625.8505085155165</v>
+        <v>425.0520115000517</v>
+      </c>
+      <c r="X32">
+        <v>1087.926836169093</v>
+      </c>
+      <c r="Y32">
+        <v>595.5769970393969</v>
+      </c>
+      <c r="Z32">
+        <v>394.7785000239322</v>
+      </c>
+      <c r="AA32">
+        <v>1057.653324692973</v>
+      </c>
+      <c r="AB32">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2762,17 +3345,35 @@
       <c r="R33">
         <v>-99.32213809590436</v>
       </c>
+      <c r="S33">
+        <v>-245.2723622574324</v>
+      </c>
       <c r="T33">
-        <v>-245.2723622574324</v>
+        <v>-61.31809056435809</v>
       </c>
       <c r="U33">
-        <v>-61.31809056435809</v>
+        <v>-654.0596326864863</v>
       </c>
       <c r="V33">
-        <v>-654.0596326864863</v>
+        <v>149.4526768719323</v>
       </c>
       <c r="W33">
-        <v>149.4526768719323</v>
+        <v>372.7219615613021</v>
+      </c>
+      <c r="X33">
+        <v>-298.6496065534171</v>
+      </c>
+      <c r="Y33">
+        <v>44.14236615847625</v>
+      </c>
+      <c r="Z33">
+        <v>267.411650847846</v>
+      </c>
+      <c r="AA33">
+        <v>-403.9599172668732</v>
+      </c>
+      <c r="AB33">
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -2834,17 +3435,35 @@
       <c r="R34">
         <v>-33.75375027892549</v>
       </c>
+      <c r="S34">
+        <v>-71.83156791000187</v>
+      </c>
       <c r="T34">
-        <v>-71.83156791000187</v>
+        <v>-17.95789197750047</v>
       </c>
       <c r="U34">
-        <v>-17.95789197750047</v>
+        <v>-191.550847760005</v>
       </c>
       <c r="V34">
-        <v>-191.550847760005</v>
+        <v>449.2467190357018</v>
       </c>
       <c r="W34">
-        <v>449.2467190357018</v>
+        <v>516.4812544536112</v>
+      </c>
+      <c r="X34">
+        <v>316.1665797002906</v>
+      </c>
+      <c r="Y34">
+        <v>415.365685663722</v>
+      </c>
+      <c r="Z34">
+        <v>482.6002210816314</v>
+      </c>
+      <c r="AA34">
+        <v>282.2855463283109</v>
+      </c>
+      <c r="AB34">
+        <v>3.610169491525424</v>
       </c>
     </row>
     <row r="35">
@@ -2906,17 +3525,35 @@
       <c r="R35">
         <v>-69.76600477359052</v>
       </c>
+      <c r="S35">
+        <v>715.1119955715096</v>
+      </c>
       <c r="T35">
-        <v>715.1119955715096</v>
+        <v>178.7779988928774</v>
       </c>
       <c r="U35">
-        <v>178.7779988928774</v>
+        <v>1906.965321524026</v>
       </c>
       <c r="V35">
-        <v>1906.965321524026</v>
+        <v>1004.275094602528</v>
       </c>
       <c r="W35">
-        <v>1004.275094602528</v>
+        <v>495.5568081467759</v>
+      </c>
+      <c r="X35">
+        <v>2168.512710332165</v>
+      </c>
+      <c r="Y35">
+        <v>971.2547734051061</v>
+      </c>
+      <c r="Z35">
+        <v>462.5364869493534</v>
+      </c>
+      <c r="AA35">
+        <v>2135.492389134743</v>
+      </c>
+      <c r="AB35">
+        <v>6.220338983050848</v>
       </c>
     </row>
     <row r="36">
@@ -2978,17 +3615,35 @@
       <c r="R36">
         <v>-27.22953876710327</v>
       </c>
+      <c r="S36">
+        <v>799.9688724580296</v>
+      </c>
       <c r="T36">
-        <v>799.9688724580296</v>
+        <v>199.9922181145074</v>
       </c>
       <c r="U36">
-        <v>199.9922181145074</v>
+        <v>2133.250326554746</v>
       </c>
       <c r="V36">
-        <v>2133.250326554746</v>
+        <v>1186.53682919157</v>
       </c>
       <c r="W36">
-        <v>1186.53682919157</v>
+        <v>597.3385339433598</v>
+      </c>
+      <c r="X36">
+        <v>2509.039924192975</v>
+      </c>
+      <c r="Y36">
+        <v>1159.982421763237</v>
+      </c>
+      <c r="Z36">
+        <v>570.7841265150265</v>
+      </c>
+      <c r="AA36">
+        <v>2482.485516764642</v>
+      </c>
+      <c r="AB36">
+        <v>11.2</v>
       </c>
     </row>
     <row r="37">
@@ -3050,17 +3705,35 @@
       <c r="R37">
         <v>-18.58141926439271</v>
       </c>
+      <c r="S37">
+        <v>115.1339448338881</v>
+      </c>
       <c r="T37">
-        <v>115.1339448338881</v>
+        <v>28.78348620847201</v>
       </c>
       <c r="U37">
-        <v>28.78348620847201</v>
+        <v>307.0238528903681</v>
       </c>
       <c r="V37">
-        <v>307.0238528903681</v>
+        <v>282.9823514673414</v>
       </c>
       <c r="W37">
-        <v>282.9823514673414</v>
+        <v>203.9870379674142</v>
+      </c>
+      <c r="X37">
+        <v>467.5171143983328</v>
+      </c>
+      <c r="Y37">
+        <v>269.402918366946</v>
+      </c>
+      <c r="Z37">
+        <v>190.4076048670188</v>
+      </c>
+      <c r="AA37">
+        <v>453.9376812979373</v>
+      </c>
+      <c r="AB37">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -3122,17 +3795,35 @@
       <c r="R38">
         <v>-57.70377317826512</v>
       </c>
+      <c r="S38">
+        <v>-391.0246525627841</v>
+      </c>
       <c r="T38">
-        <v>-391.0246525627841</v>
+        <v>-97.75616314069602</v>
       </c>
       <c r="U38">
-        <v>-97.75616314069602</v>
+        <v>-1042.732406834091</v>
       </c>
       <c r="V38">
-        <v>-1042.732406834091</v>
+        <v>-249.9471891329695</v>
       </c>
       <c r="W38">
-        <v>-249.9471891329695</v>
+        <v>66.16237717218181</v>
+      </c>
+      <c r="X38">
+        <v>-924.4960202873397</v>
+      </c>
+      <c r="Y38">
+        <v>-268.3901425190508</v>
+      </c>
+      <c r="Z38">
+        <v>47.71942378610061</v>
+      </c>
+      <c r="AA38">
+        <v>-942.9389736734208</v>
+      </c>
+      <c r="AB38">
+        <v>1.88135593220339</v>
       </c>
     </row>
     <row r="39">
@@ -3194,17 +3885,35 @@
       <c r="R39">
         <v>-37.82831323651127</v>
       </c>
+      <c r="S39">
+        <v>-273.0250565140611</v>
+      </c>
       <c r="T39">
-        <v>-273.0250565140611</v>
+        <v>-68.25626412851528</v>
       </c>
       <c r="U39">
-        <v>-68.25626412851528</v>
+        <v>-728.0668173708297</v>
       </c>
       <c r="V39">
-        <v>-728.0668173708297</v>
+        <v>272.2734425938952</v>
       </c>
       <c r="W39">
-        <v>272.2734425938952</v>
+        <v>492.0159423022267</v>
+      </c>
+      <c r="X39">
+        <v>-197.742025585659</v>
+      </c>
+      <c r="Y39">
+        <v>230.0257972189942</v>
+      </c>
+      <c r="Z39">
+        <v>449.7682969273257</v>
+      </c>
+      <c r="AA39">
+        <v>-239.98967096056</v>
+      </c>
+      <c r="AB39">
+        <v>6.915254237288136</v>
       </c>
     </row>
     <row r="40">
@@ -3266,17 +3975,35 @@
       <c r="R40">
         <v>-88.29875926621034</v>
       </c>
+      <c r="S40">
+        <v>204.5507074525101</v>
+      </c>
       <c r="T40">
-        <v>204.5507074525101</v>
+        <v>51.13767686312753</v>
       </c>
       <c r="U40">
-        <v>51.13767686312753</v>
+        <v>545.4685532066936</v>
       </c>
       <c r="V40">
-        <v>545.4685532066936</v>
+        <v>726.7926710539176</v>
       </c>
       <c r="W40">
-        <v>726.7926710539176</v>
+        <v>608.3312326740765</v>
+      </c>
+      <c r="X40">
+        <v>1032.75892459856</v>
+      </c>
+      <c r="Y40">
+        <v>678.9956463740091</v>
+      </c>
+      <c r="Z40">
+        <v>560.534207994168</v>
+      </c>
+      <c r="AA40">
+        <v>984.9618999186509</v>
+      </c>
+      <c r="AB40">
+        <v>11.22033898305085</v>
       </c>
     </row>
     <row r="41">
@@ -3338,17 +4065,35 @@
       <c r="R41">
         <v>-31.9976583991754</v>
       </c>
+      <c r="S41">
+        <v>-966.0429212020487</v>
+      </c>
       <c r="T41">
-        <v>-966.0429212020487</v>
+        <v>-241.5107303005122</v>
       </c>
       <c r="U41">
-        <v>-241.5107303005122</v>
+        <v>-2576.114456538796</v>
       </c>
       <c r="V41">
-        <v>-2576.114456538796</v>
+        <v>-720.5023570183444</v>
       </c>
       <c r="W41">
-        <v>-720.5023570183444</v>
+        <v>16.69557366619898</v>
+      </c>
+      <c r="X41">
+        <v>-2343.239632138098</v>
+      </c>
+      <c r="Y41">
+        <v>-747.1229371569049</v>
+      </c>
+      <c r="Z41">
+        <v>-9.925006472361559</v>
+      </c>
+      <c r="AA41">
+        <v>-2369.860212276659</v>
+      </c>
+      <c r="AB41">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3410,17 +4155,35 @@
       <c r="R42">
         <v>-66.6095139583979</v>
       </c>
+      <c r="S42">
+        <v>-1141.569156945336</v>
+      </c>
       <c r="T42">
-        <v>-1141.569156945336</v>
+        <v>-285.3922892363341</v>
       </c>
       <c r="U42">
-        <v>-285.3922892363341</v>
+        <v>-3044.184418520897</v>
       </c>
       <c r="V42">
-        <v>-3044.184418520897</v>
+        <v>-1004.984809253795</v>
       </c>
       <c r="W42">
-        <v>-1004.984809253795</v>
+        <v>-122.4416756029266</v>
+      </c>
+      <c r="X42">
+        <v>-2933.966336771221</v>
+      </c>
+      <c r="Y42">
+        <v>-1057.312660164985</v>
+      </c>
+      <c r="Z42">
+        <v>-174.7695265141175</v>
+      </c>
+      <c r="AA42">
+        <v>-2986.294187682412</v>
+      </c>
+      <c r="AB42">
+        <v>1.932203389830508</v>
       </c>
     </row>
     <row r="43">
@@ -3482,17 +4245,35 @@
       <c r="R43">
         <v>-43.57228032095942</v>
       </c>
+      <c r="S43">
+        <v>-1624.929458919247</v>
+      </c>
       <c r="T43">
-        <v>-1624.929458919247</v>
+        <v>-406.2323647298118</v>
       </c>
       <c r="U43">
-        <v>-406.2323647298118</v>
+        <v>-4333.14522378466</v>
       </c>
       <c r="V43">
-        <v>-4333.14522378466</v>
+        <v>-1359.242743335986</v>
       </c>
       <c r="W43">
-        <v>-1359.242743335986</v>
+        <v>-123.2982881861705</v>
+      </c>
+      <c r="X43">
+        <v>-4084.705869161778</v>
+      </c>
+      <c r="Y43">
+        <v>-1415.440416557498</v>
+      </c>
+      <c r="Z43">
+        <v>-179.4959614076831</v>
+      </c>
+      <c r="AA43">
+        <v>-4140.90354238329</v>
+      </c>
+      <c r="AB43">
+        <v>3.491525423728814</v>
       </c>
     </row>
     <row r="44">
@@ -3554,17 +4335,35 @@
       <c r="R44">
         <v>-23.5983827663694</v>
       </c>
+      <c r="S44">
+        <v>-931.5429266587793</v>
+      </c>
       <c r="T44">
-        <v>-931.5429266587793</v>
+        <v>-232.8857316646948</v>
       </c>
       <c r="U44">
-        <v>-232.8857316646948</v>
+        <v>-2484.114471090078</v>
       </c>
       <c r="V44">
-        <v>-2484.114471090078</v>
+        <v>-532.5656404606669</v>
       </c>
       <c r="W44">
-        <v>-532.5656404606669</v>
+        <v>175.4325810451055</v>
+      </c>
+      <c r="X44">
+        <v>-2094.478211403653</v>
+      </c>
+      <c r="Y44">
+        <v>-563.6874830146545</v>
+      </c>
+      <c r="Z44">
+        <v>144.3107384911179</v>
+      </c>
+      <c r="AA44">
+        <v>-2125.600053957641</v>
+      </c>
+      <c r="AB44">
+        <v>6.35593220338983</v>
       </c>
     </row>
     <row r="45">
@@ -3626,17 +4425,35 @@
       <c r="R45">
         <v>-35.26445651144341</v>
       </c>
+      <c r="S45">
+        <v>-28.55696837950058</v>
+      </c>
       <c r="T45">
-        <v>-28.55696837950058</v>
+        <v>-7.139242094875145</v>
       </c>
       <c r="U45">
-        <v>-7.139242094875145</v>
+        <v>-76.15191567866822</v>
       </c>
       <c r="V45">
-        <v>-76.15191567866822</v>
+        <v>524.8476553689155</v>
       </c>
       <c r="W45">
-        <v>524.8476553689155</v>
+        <v>560.224229022654</v>
+      </c>
+      <c r="X45">
+        <v>463.2938607006349</v>
+      </c>
+      <c r="Y45">
+        <v>479.3620370902144</v>
+      </c>
+      <c r="Z45">
+        <v>514.7386107439528</v>
+      </c>
+      <c r="AA45">
+        <v>417.8082424219337</v>
+      </c>
+      <c r="AB45">
+        <v>5.491525423728813</v>
       </c>
     </row>
     <row r="46">
@@ -3698,17 +4515,35 @@
       <c r="R46">
         <v>-17.35655505192626</v>
       </c>
+      <c r="S46">
+        <v>-794.2045027091767</v>
+      </c>
       <c r="T46">
-        <v>-794.2045027091767</v>
+        <v>-198.5511256772942</v>
       </c>
       <c r="U46">
-        <v>-198.5511256772942</v>
+        <v>-2117.878673891138</v>
       </c>
       <c r="V46">
-        <v>-2117.878673891138</v>
+        <v>-525.2320455214378</v>
       </c>
       <c r="W46">
-        <v>-525.2320455214378</v>
+        <v>77.29163455183217</v>
+      </c>
+      <c r="X46">
+        <v>-1855.776519744787</v>
+      </c>
+      <c r="Y46">
+        <v>-563.1657076070233</v>
+      </c>
+      <c r="Z46">
+        <v>39.35797246624679</v>
+      </c>
+      <c r="AA46">
+        <v>-1893.710181830372</v>
+      </c>
+      <c r="AB46">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3770,17 +4605,35 @@
       <c r="R47">
         <v>-29.66221983874401</v>
       </c>
+      <c r="S47">
+        <v>-13.28549215938822</v>
+      </c>
       <c r="T47">
-        <v>-13.28549215938822</v>
+        <v>-3.321373039847054</v>
       </c>
       <c r="U47">
-        <v>-3.321373039847054</v>
+        <v>-35.42797909170191</v>
       </c>
       <c r="V47">
-        <v>-35.42797909170191</v>
+        <v>575.0969783561879</v>
       </c>
       <c r="W47">
-        <v>575.0969783561879</v>
+        <v>596.8023928285653</v>
+      </c>
+      <c r="X47">
+        <v>541.2131960710381</v>
+      </c>
+      <c r="Y47">
+        <v>516.9012879491287</v>
+      </c>
+      <c r="Z47">
+        <v>538.606702421506</v>
+      </c>
+      <c r="AA47">
+        <v>483.0175056639788</v>
+      </c>
+      <c r="AB47">
+        <v>6.203389830508475</v>
       </c>
     </row>
     <row r="48">
@@ -3842,17 +4695,35 @@
       <c r="R48">
         <v>-25.9084799374745</v>
       </c>
+      <c r="S48">
+        <v>-907.9343167996072</v>
+      </c>
       <c r="T48">
-        <v>-907.9343167996072</v>
+        <v>-226.9835791999018</v>
       </c>
       <c r="U48">
-        <v>-226.9835791999018</v>
+        <v>-2421.158178132286</v>
       </c>
       <c r="V48">
-        <v>-2421.158178132286</v>
+        <v>-660.1522980368836</v>
       </c>
       <c r="W48">
-        <v>-660.1522980368836</v>
+        <v>31.05387953807224</v>
+      </c>
+      <c r="X48">
+        <v>-2183.631599344813</v>
+      </c>
+      <c r="Y48">
+        <v>-697.9962543978402</v>
+      </c>
+      <c r="Z48">
+        <v>-6.790076822884373</v>
+      </c>
+      <c r="AA48">
+        <v>-2221.475555705769</v>
+      </c>
+      <c r="AB48">
+        <v>1.864406779661017</v>
       </c>
     </row>
     <row r="49">
@@ -3914,17 +4785,35 @@
       <c r="R49">
         <v>-19.43462453174192</v>
       </c>
+      <c r="S49">
+        <v>-13.44608419750229</v>
+      </c>
       <c r="T49">
-        <v>-13.44608419750229</v>
+        <v>-3.361521049375571</v>
       </c>
       <c r="U49">
-        <v>-3.361521049375571</v>
+        <v>-35.85622452667276</v>
       </c>
       <c r="V49">
-        <v>-35.85622452667276</v>
+        <v>448.3065100927043</v>
       </c>
       <c r="W49">
-        <v>448.3065100927043</v>
+        <v>466.0839454513122</v>
+      </c>
+      <c r="X49">
+        <v>418.2034975530526</v>
+      </c>
+      <c r="Y49">
+        <v>431.0169806587588</v>
+      </c>
+      <c r="Z49">
+        <v>448.7944160173667</v>
+      </c>
+      <c r="AA49">
+        <v>400.9139681191072</v>
+      </c>
+      <c r="AB49">
+        <v>11.5</v>
       </c>
     </row>
     <row r="50">
@@ -3986,17 +4875,35 @@
       <c r="R50">
         <v>-28.01301462364787</v>
       </c>
+      <c r="S50">
+        <v>38.77324499785593</v>
+      </c>
       <c r="T50">
-        <v>38.77324499785593</v>
+        <v>9.693311249463981</v>
       </c>
       <c r="U50">
-        <v>9.693311249463981</v>
+        <v>103.3953199942825</v>
       </c>
       <c r="V50">
-        <v>103.3953199942825</v>
+        <v>378.3542944840665</v>
       </c>
       <c r="W50">
-        <v>378.3542944840665</v>
+        <v>360.3628456908685</v>
+      </c>
+      <c r="X50">
+        <v>431.8878845252991</v>
+      </c>
+      <c r="Y50">
+        <v>363.1882784791776</v>
+      </c>
+      <c r="Z50">
+        <v>345.1968296859796</v>
+      </c>
+      <c r="AA50">
+        <v>416.7218685204102</v>
+      </c>
+      <c r="AB50">
+        <v>3.254237288135593</v>
       </c>
     </row>
     <row r="51">
@@ -4058,17 +4965,35 @@
       <c r="R51">
         <v>-192.9124417585077</v>
       </c>
+      <c r="S51">
+        <v>-459.991635634027</v>
+      </c>
       <c r="T51">
-        <v>-459.991635634027</v>
+        <v>-114.9979089085068</v>
       </c>
       <c r="U51">
-        <v>-114.9979089085068</v>
+        <v>-1226.644361690739</v>
       </c>
       <c r="V51">
-        <v>-1226.644361690739</v>
+        <v>-439.1394011764789</v>
       </c>
       <c r="W51">
-        <v>-439.1394011764789</v>
+        <v>-17.78449958821597</v>
+      </c>
+      <c r="X51">
+        <v>-1282.153302095933</v>
+      </c>
+      <c r="Y51">
+        <v>-467.2487512155525</v>
+      </c>
+      <c r="Z51">
+        <v>-45.89384962728975</v>
+      </c>
+      <c r="AA51">
+        <v>-1310.262652135007</v>
+      </c>
+      <c r="AB51">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4130,17 +5055,35 @@
       <c r="R52">
         <v>-27.48984268260899</v>
       </c>
+      <c r="S52">
+        <v>-531.4328454065576</v>
+      </c>
       <c r="T52">
-        <v>-531.4328454065576</v>
+        <v>-132.8582113516394</v>
       </c>
       <c r="U52">
-        <v>-132.8582113516394</v>
+        <v>-1417.154254417487</v>
       </c>
       <c r="V52">
-        <v>-1417.154254417487</v>
+        <v>-148.524553898246</v>
       </c>
       <c r="W52">
-        <v>-148.524553898246</v>
+        <v>260.9314762185383</v>
+      </c>
+      <c r="X52">
+        <v>-1045.127358971041</v>
+      </c>
+      <c r="Y52">
+        <v>-170.4165242918114</v>
+      </c>
+      <c r="Z52">
+        <v>239.0395058249728</v>
+      </c>
+      <c r="AA52">
+        <v>-1067.019329364607</v>
+      </c>
+      <c r="AB52">
+        <v>3.033898305084746</v>
       </c>
     </row>
     <row r="53">
@@ -4202,17 +5145,35 @@
       <c r="R53">
         <v>-39.04530378209561</v>
       </c>
+      <c r="S53">
+        <v>-203.5334048808638</v>
+      </c>
       <c r="T53">
-        <v>-203.5334048808638</v>
+        <v>-50.88335122021595</v>
       </c>
       <c r="U53">
-        <v>-50.88335122021595</v>
+        <v>-542.7557463489701</v>
       </c>
       <c r="V53">
-        <v>-542.7557463489701</v>
+        <v>372.0900869812113</v>
       </c>
       <c r="W53">
-        <v>372.0900869812113</v>
+        <v>540.1955733889387</v>
+      </c>
+      <c r="X53">
+        <v>17.41231276602548</v>
+      </c>
+      <c r="Y53">
+        <v>318.56705918585</v>
+      </c>
+      <c r="Z53">
+        <v>486.6725455935774</v>
+      </c>
+      <c r="AA53">
+        <v>-36.11071502933578</v>
+      </c>
+      <c r="AB53">
+        <v>10.33898305084746</v>
       </c>
     </row>
     <row r="54">
@@ -4274,17 +5235,35 @@
       <c r="R54">
         <v>-81.71405011370113</v>
       </c>
+      <c r="S54">
+        <v>-513.3567931933326</v>
+      </c>
       <c r="T54">
-        <v>-513.3567931933326</v>
+        <v>-128.3391982983331</v>
       </c>
       <c r="U54">
-        <v>-128.3391982983331</v>
+        <v>-1368.951448515553</v>
       </c>
       <c r="V54">
-        <v>-1368.951448515553</v>
+        <v>-487.976452147667</v>
       </c>
       <c r="W54">
-        <v>-487.976452147667</v>
+        <v>-70.61371241599413</v>
+      </c>
+      <c r="X54">
+        <v>-1375.916252306561</v>
+      </c>
+      <c r="Y54">
+        <v>-516.868643012019</v>
+      </c>
+      <c r="Z54">
+        <v>-99.50590328034613</v>
+      </c>
+      <c r="AA54">
+        <v>-1404.808443170913</v>
+      </c>
+      <c r="AB54">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -4346,17 +5325,35 @@
       <c r="R55">
         <v>-40.86534077375143</v>
       </c>
+      <c r="S55">
+        <v>-847.4048581032467</v>
+      </c>
       <c r="T55">
-        <v>-847.4048581032467</v>
+        <v>-211.8512145258117</v>
       </c>
       <c r="U55">
-        <v>-211.8512145258117</v>
+        <v>-2259.746288275325</v>
       </c>
       <c r="V55">
-        <v>-2259.746288275325</v>
+        <v>-721.7365338639902</v>
       </c>
       <c r="W55">
-        <v>-721.7365338639902</v>
+        <v>-70.00702623027863</v>
+      </c>
+      <c r="X55">
+        <v>-2150.253828092345</v>
+      </c>
+      <c r="Y55">
+        <v>-736.5943050616972</v>
+      </c>
+      <c r="Z55">
+        <v>-84.86479742798562</v>
+      </c>
+      <c r="AA55">
+        <v>-2165.111599290052</v>
+      </c>
+      <c r="AB55">
+        <v>1.983050847457627</v>
       </c>
     </row>
     <row r="56">
@@ -4418,17 +5415,35 @@
       <c r="R56">
         <v>-84.48347779409866</v>
       </c>
+      <c r="S56">
+        <v>-639.6921167376527</v>
+      </c>
       <c r="T56">
-        <v>-639.6921167376527</v>
+        <v>-159.9230291844132</v>
       </c>
       <c r="U56">
-        <v>-159.9230291844132</v>
+        <v>-1705.84564463374</v>
       </c>
       <c r="V56">
-        <v>-1705.84564463374</v>
+        <v>-171.6367584212563</v>
       </c>
       <c r="W56">
-        <v>-171.6367584212563</v>
+        <v>341.5737057588138</v>
+      </c>
+      <c r="X56">
+        <v>-1271.231662944174</v>
+      </c>
+      <c r="Y56">
+        <v>-206.1963833853746</v>
+      </c>
+      <c r="Z56">
+        <v>307.0140807946956</v>
+      </c>
+      <c r="AA56">
+        <v>-1305.791287908293</v>
+      </c>
+      <c r="AB56">
+        <v>5.186440677966102</v>
       </c>
     </row>
     <row r="57">
@@ -4490,17 +5505,35 @@
       <c r="R57">
         <v>-191.2174984961702</v>
       </c>
+      <c r="S57">
+        <v>-262.5861493309494</v>
+      </c>
       <c r="T57">
-        <v>-262.5861493309494</v>
+        <v>-65.64653733273735</v>
       </c>
       <c r="U57">
-        <v>-65.64653733273735</v>
+        <v>-700.2297315491984</v>
       </c>
       <c r="V57">
-        <v>-700.2297315491984</v>
+        <v>-120.9078985152807</v>
       </c>
       <c r="W57">
-        <v>-120.9078985152807</v>
+        <v>151.721973304332</v>
+      </c>
+      <c r="X57">
+        <v>-634.2417405549304</v>
+      </c>
+      <c r="Y57">
+        <v>-178.5915714805676</v>
+      </c>
+      <c r="Z57">
+        <v>94.03830033904518</v>
+      </c>
+      <c r="AA57">
+        <v>-691.9254135202173</v>
+      </c>
+      <c r="AB57">
+        <v>1.983050847457627</v>
       </c>
     </row>
     <row r="58">
@@ -4562,17 +5595,35 @@
       <c r="R58">
         <v>-40.92084729343487</v>
       </c>
+      <c r="S58">
+        <v>-30.98620230848367</v>
+      </c>
       <c r="T58">
-        <v>-30.98620230848367</v>
+        <v>-7.746550577120918</v>
       </c>
       <c r="U58">
-        <v>-7.746550577120918</v>
+        <v>-82.62987282262313</v>
       </c>
       <c r="V58">
-        <v>-82.62987282262313</v>
+        <v>525.2162277796139</v>
       </c>
       <c r="W58">
-        <v>525.2162277796139</v>
+        <v>564.6537148979612</v>
+      </c>
+      <c r="X58">
+        <v>457.3747218784898</v>
+      </c>
+      <c r="Y58">
+        <v>479.1199025310208</v>
+      </c>
+      <c r="Z58">
+        <v>518.5573896493681</v>
+      </c>
+      <c r="AA58">
+        <v>411.2783966298967</v>
+      </c>
+      <c r="AB58">
+        <v>12.3</v>
       </c>
     </row>
     <row r="59">
@@ -4634,17 +5685,35 @@
       <c r="R59">
         <v>-28.55390149364721</v>
       </c>
+      <c r="S59">
+        <v>198.2104816727272</v>
+      </c>
       <c r="T59">
-        <v>198.2104816727272</v>
+        <v>49.55262041818181</v>
       </c>
       <c r="U59">
-        <v>49.55262041818181</v>
+        <v>528.561284460606</v>
       </c>
       <c r="V59">
-        <v>528.561284460606</v>
+        <v>580.4545005526619</v>
       </c>
       <c r="W59">
-        <v>580.4545005526619</v>
+        <v>443.0992253060186</v>
+      </c>
+      <c r="X59">
+        <v>899.5027173326387</v>
+      </c>
+      <c r="Y59">
+        <v>531.1908363692988</v>
+      </c>
+      <c r="Z59">
+        <v>393.8355611226555</v>
+      </c>
+      <c r="AA59">
+        <v>850.2390531492756</v>
+      </c>
+      <c r="AB59">
+        <v>3.416666666666667</v>
       </c>
     </row>
     <row r="60">
@@ -4706,17 +5775,35 @@
       <c r="R60">
         <v>-46.53095406663628</v>
       </c>
+      <c r="S60">
+        <v>150.8143772717958</v>
+      </c>
       <c r="T60">
-        <v>150.8143772717958</v>
+        <v>37.70359431794895</v>
       </c>
       <c r="U60">
-        <v>37.70359431794895</v>
+        <v>402.1716727247888</v>
       </c>
       <c r="V60">
-        <v>402.1716727247888</v>
+        <v>737.7854905920595</v>
       </c>
       <c r="W60">
-        <v>737.7854905920595</v>
+        <v>643.0932102895896</v>
+      </c>
+      <c r="X60">
+        <v>970.7242833936757</v>
+      </c>
+      <c r="Y60">
+        <v>717.3337827361231</v>
+      </c>
+      <c r="Z60">
+        <v>622.6415024336532</v>
+      </c>
+      <c r="AA60">
+        <v>950.2725755377392</v>
+      </c>
+      <c r="AB60">
+        <v>11.28813559322034</v>
       </c>
     </row>
     <row r="61">
@@ -4778,17 +5865,35 @@
       <c r="R61">
         <v>-17.32788108365847</v>
       </c>
+      <c r="S61">
+        <v>841.474237757583</v>
+      </c>
       <c r="T61">
-        <v>841.474237757583</v>
+        <v>210.3685594393957</v>
       </c>
       <c r="U61">
-        <v>210.3685594393957</v>
+        <v>2243.931300686888</v>
       </c>
       <c r="V61">
-        <v>2243.931300686888</v>
+        <v>1181.254353969848</v>
       </c>
       <c r="W61">
-        <v>1181.254353969848</v>
+        <v>557.0076285806088</v>
+      </c>
+      <c r="X61">
+        <v>2576.852463970205</v>
+      </c>
+      <c r="Y61">
+        <v>1167.722676300931</v>
+      </c>
+      <c r="Z61">
+        <v>543.4759509116923</v>
+      </c>
+      <c r="AA61">
+        <v>2563.320786301288</v>
+      </c>
+      <c r="AB61">
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -4850,17 +5955,35 @@
       <c r="R62">
         <v>-31.01756894557587</v>
       </c>
+      <c r="S62">
+        <v>-587.0267300596598</v>
+      </c>
       <c r="T62">
-        <v>-587.0267300596598</v>
+        <v>-146.756682514915</v>
       </c>
       <c r="U62">
-        <v>-146.756682514915</v>
+        <v>-1565.404613492426</v>
       </c>
       <c r="V62">
-        <v>-1565.404613492426</v>
+        <v>-601.6420896740709</v>
       </c>
       <c r="W62">
-        <v>-601.6420896740709</v>
+        <v>-149.0942544217023</v>
+      </c>
+      <c r="X62">
+        <v>-1592.297760814461</v>
+      </c>
+      <c r="Y62">
+        <v>-602.4638077989824</v>
+      </c>
+      <c r="Z62">
+        <v>-149.9159725466138</v>
+      </c>
+      <c r="AA62">
+        <v>-1593.119478939373</v>
+      </c>
+      <c r="AB62">
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="63">
@@ -4922,17 +6045,35 @@
       <c r="R63">
         <v>-109.0449560586357</v>
       </c>
+      <c r="S63">
+        <v>-1087.409657566273</v>
+      </c>
       <c r="T63">
-        <v>-1087.409657566273</v>
+        <v>-271.8524143915683</v>
       </c>
       <c r="U63">
-        <v>-271.8524143915683</v>
+        <v>-2899.759086843396</v>
       </c>
       <c r="V63">
-        <v>-2899.759086843396</v>
+        <v>-815.3844434125592</v>
       </c>
       <c r="W63">
-        <v>-815.3844434125592</v>
+        <v>43.33642820202243</v>
+      </c>
+      <c r="X63">
+        <v>-2670.897501129558</v>
+      </c>
+      <c r="Y63">
+        <v>-834.7163274478626</v>
+      </c>
+      <c r="Z63">
+        <v>24.00454416671874</v>
+      </c>
+      <c r="AA63">
+        <v>-2690.229385164862</v>
+      </c>
+      <c r="AB63">
+        <v>2.95</v>
       </c>
     </row>
     <row r="64">
@@ -4994,17 +6135,35 @@
       <c r="R64">
         <v>-41.26914297593793</v>
       </c>
+      <c r="S64">
+        <v>858.0909074004417</v>
+      </c>
       <c r="T64">
-        <v>858.0909074004417</v>
+        <v>214.5227268501104</v>
       </c>
       <c r="U64">
-        <v>214.5227268501104</v>
+        <v>2288.242419734511</v>
       </c>
       <c r="V64">
-        <v>2288.242419734511</v>
+        <v>1003.581557869952</v>
       </c>
       <c r="W64">
-        <v>1003.581557869952</v>
+        <v>376.3490797475959</v>
+      </c>
+      <c r="X64">
+        <v>2417.397367776045</v>
+      </c>
+      <c r="Y64">
+        <v>995.4751110419594</v>
+      </c>
+      <c r="Z64">
+        <v>368.2426329196035</v>
+      </c>
+      <c r="AA64">
+        <v>2409.290920948053</v>
+      </c>
+      <c r="AB64">
+        <v>7.689655172413793</v>
       </c>
     </row>
     <row r="65">
@@ -5066,17 +6225,35 @@
       <c r="R65">
         <v>-149.8788793669305</v>
       </c>
+      <c r="S65">
+        <v>-103.0166085441775</v>
+      </c>
       <c r="T65">
-        <v>-103.0166085441775</v>
+        <v>-25.75415213604437</v>
       </c>
       <c r="U65">
-        <v>-25.75415213604437</v>
+        <v>-274.7109561178066</v>
       </c>
       <c r="V65">
-        <v>-274.7109561178066</v>
+        <v>-7.23298140177954</v>
       </c>
       <c r="W65">
-        <v>-7.23298140177954</v>
+        <v>129.3565314224302</v>
+      </c>
+      <c r="X65">
+        <v>-238.2543853914853</v>
+      </c>
+      <c r="Y65">
+        <v>-41.53900965587985</v>
+      </c>
+      <c r="Z65">
+        <v>95.05050316832994</v>
+      </c>
+      <c r="AA65">
+        <v>-272.5604136455856</v>
+      </c>
+      <c r="AB65">
+        <v>2.694915254237288</v>
       </c>
     </row>
     <row r="66">
@@ -5138,17 +6315,35 @@
       <c r="R66">
         <v>-37.57116634028481</v>
       </c>
+      <c r="S66">
+        <v>-350.5494967596808</v>
+      </c>
       <c r="T66">
-        <v>-350.5494967596808</v>
+        <v>-87.63737418992019</v>
       </c>
       <c r="U66">
-        <v>-87.63737418992019</v>
+        <v>-934.7986580258154</v>
       </c>
       <c r="V66">
-        <v>-934.7986580258154</v>
+        <v>-186.3947292709484</v>
       </c>
       <c r="W66">
-        <v>-186.3947292709484</v>
+        <v>91.38931330850824</v>
+      </c>
+      <c r="X66">
+        <v>-785.515810546779</v>
+      </c>
+      <c r="Y66">
+        <v>-197.0197132964836</v>
+      </c>
+      <c r="Z66">
+        <v>80.76432928297305</v>
+      </c>
+      <c r="AA66">
+        <v>-796.1407945723142</v>
+      </c>
+      <c r="AB66">
+        <v>6.677966101694915</v>
       </c>
     </row>
     <row r="67">
@@ -5210,17 +6405,35 @@
       <c r="R67">
         <v>-160.6197356223814</v>
       </c>
+      <c r="S67">
+        <v>-391.0487455847381</v>
+      </c>
       <c r="T67">
-        <v>-391.0487455847381</v>
+        <v>-97.76218639618452</v>
       </c>
       <c r="U67">
-        <v>-97.76218639618452</v>
+        <v>-1042.796654892635</v>
       </c>
       <c r="V67">
-        <v>-1042.796654892635</v>
+        <v>-365.1467769005856</v>
       </c>
       <c r="W67">
-        <v>-365.1467769005856</v>
+        <v>-8.281572361506065</v>
+      </c>
+      <c r="X67">
+        <v>-1080.473331559008</v>
+      </c>
+      <c r="Y67">
+        <v>-403.0909346856452</v>
+      </c>
+      <c r="Z67">
+        <v>-46.22573014656562</v>
+      </c>
+      <c r="AA67">
+        <v>-1118.417489344068</v>
+      </c>
+      <c r="AB67">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -5282,17 +6495,35 @@
       <c r="R68">
         <v>-21.87339065942142</v>
       </c>
+      <c r="S68">
+        <v>305.0015765069846</v>
+      </c>
       <c r="T68">
-        <v>305.0015765069846</v>
+        <v>76.25039412674616</v>
       </c>
       <c r="U68">
-        <v>76.25039412674616</v>
+        <v>813.337537351959</v>
       </c>
       <c r="V68">
-        <v>813.337537351959</v>
+        <v>673.6889168346786</v>
       </c>
       <c r="W68">
-        <v>673.6889168346786</v>
+        <v>453.5959515904611</v>
+      </c>
+      <c r="X68">
+        <v>1173.366660543632</v>
+      </c>
+      <c r="Y68">
+        <v>635.7517290549079</v>
+      </c>
+      <c r="Z68">
+        <v>415.6587638106904</v>
+      </c>
+      <c r="AA68">
+        <v>1135.429472763861</v>
+      </c>
+      <c r="AB68">
+        <v>6.610169491525424</v>
       </c>
     </row>
     <row r="69">
@@ -5354,17 +6585,35 @@
       <c r="R69">
         <v>-105.8550251002139</v>
       </c>
+      <c r="S69">
+        <v>-567.0975784374136</v>
+      </c>
       <c r="T69">
-        <v>-567.0975784374136</v>
+        <v>-141.7743946093534</v>
       </c>
       <c r="U69">
-        <v>-141.7743946093534</v>
+        <v>-1512.260209166436</v>
       </c>
       <c r="V69">
-        <v>-1512.260209166436</v>
+        <v>-163.3418305320671</v>
       </c>
       <c r="W69">
-        <v>-163.3418305320671</v>
+        <v>303.8823007314944</v>
+      </c>
+      <c r="X69">
+        <v>-1150.405408696591</v>
+      </c>
+      <c r="Y69">
+        <v>-207.9413614877236</v>
+      </c>
+      <c r="Z69">
+        <v>259.282769775838</v>
+      </c>
+      <c r="AA69">
+        <v>-1195.004939652247</v>
+      </c>
+      <c r="AB69">
+        <v>3.779661016949153</v>
       </c>
     </row>
     <row r="70">
@@ -5426,17 +6675,35 @@
       <c r="R70">
         <v>-37.38719156763692</v>
       </c>
+      <c r="S70">
+        <v>-505.8342403352136</v>
+      </c>
       <c r="T70">
-        <v>-505.8342403352136</v>
+        <v>-126.4585600838034</v>
       </c>
       <c r="U70">
-        <v>-126.4585600838034</v>
+        <v>-1348.89130756057</v>
       </c>
       <c r="V70">
-        <v>-1348.89130756057</v>
+        <v>-467.9859402922596</v>
       </c>
       <c r="W70">
-        <v>-467.9859402922596</v>
+        <v>-73.81116337865974</v>
+      </c>
+      <c r="X70">
+        <v>-1325.842104179806</v>
+      </c>
+      <c r="Y70">
+        <v>-487.9057667459891</v>
+      </c>
+      <c r="Z70">
+        <v>-93.7309898323893</v>
+      </c>
+      <c r="AA70">
+        <v>-1345.761930633535</v>
+      </c>
+      <c r="AB70">
+        <v>0.9833333333333333</v>
       </c>
     </row>
     <row r="71">
@@ -5498,17 +6765,35 @@
       <c r="R71">
         <v>-97.35207434179432</v>
       </c>
+      <c r="S71">
+        <v>-286.9955872458959</v>
+      </c>
       <c r="T71">
-        <v>-286.9955872458959</v>
+        <v>-71.74889681147397</v>
       </c>
       <c r="U71">
-        <v>-71.74889681147397</v>
+        <v>-765.3215659890557</v>
       </c>
       <c r="V71">
-        <v>-765.3215659890557</v>
+        <v>-198.7193698535926</v>
       </c>
       <c r="W71">
-        <v>-198.7193698535926</v>
+        <v>55.06251667445625</v>
+      </c>
+      <c r="X71">
+        <v>-715.5805446903794</v>
+      </c>
+      <c r="Y71">
+        <v>-240.5036130445687</v>
+      </c>
+      <c r="Z71">
+        <v>13.27827348348015</v>
+      </c>
+      <c r="AA71">
+        <v>-757.3647878813555</v>
+      </c>
+      <c r="AB71">
+        <v>0.9833333333333333</v>
       </c>
     </row>
     <row r="72">
@@ -5570,17 +6855,35 @@
       <c r="R72">
         <v>-24.8456317021995</v>
       </c>
+      <c r="S72">
+        <v>-290.4258767432515</v>
+      </c>
       <c r="T72">
-        <v>-290.4258767432515</v>
+        <v>-72.60646918581288</v>
       </c>
       <c r="U72">
-        <v>-72.60646918581288</v>
+        <v>-774.4690046486708</v>
       </c>
       <c r="V72">
-        <v>-774.4690046486708</v>
+        <v>-202.1198544544156</v>
       </c>
       <c r="W72">
-        <v>-202.1198544544156</v>
+        <v>25.53428231847705</v>
+      </c>
+      <c r="X72">
+        <v>-695.9977115752888</v>
+      </c>
+      <c r="Y72">
+        <v>-219.0974502870816</v>
+      </c>
+      <c r="Z72">
+        <v>8.556686485810985</v>
+      </c>
+      <c r="AA72">
+        <v>-712.9753074079548</v>
+      </c>
+      <c r="AB72">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -5642,17 +6945,35 @@
       <c r="R73">
         <v>-39.53812623376415</v>
       </c>
+      <c r="S73">
+        <v>-753.4259683304886</v>
+      </c>
       <c r="T73">
-        <v>-753.4259683304886</v>
+        <v>-188.3564920826221</v>
       </c>
       <c r="U73">
-        <v>-188.3564920826221</v>
+        <v>-2009.135915547969</v>
       </c>
       <c r="V73">
-        <v>-2009.135915547969</v>
+        <v>-681.2589220803044</v>
       </c>
       <c r="W73">
-        <v>-681.2589220803044</v>
+        <v>-100.538937531573</v>
+      </c>
+      <c r="X73">
+        <v>-1952.61937759865</v>
+      </c>
+      <c r="Y73">
+        <v>-709.2770434040485</v>
+      </c>
+      <c r="Z73">
+        <v>-128.5570588553172</v>
+      </c>
+      <c r="AA73">
+        <v>-1980.637498922394</v>
+      </c>
+      <c r="AB73">
+        <v>1.9</v>
       </c>
     </row>
     <row r="74">
@@ -5714,17 +7035,35 @@
       <c r="R74">
         <v>-64.03889225641915</v>
       </c>
+      <c r="S74">
+        <v>16.70456314787427</v>
+      </c>
       <c r="T74">
-        <v>16.70456314787427</v>
+        <v>4.176140786968568</v>
       </c>
       <c r="U74">
-        <v>4.176140786968568</v>
+        <v>44.54550172766472</v>
       </c>
       <c r="V74">
-        <v>44.54550172766472</v>
+        <v>271.5840788641179</v>
       </c>
       <c r="W74">
-        <v>271.5840788641179</v>
+        <v>284.4043846880448</v>
+      </c>
+      <c r="X74">
+        <v>274.0762892590757</v>
+      </c>
+      <c r="Y74">
+        <v>253.1091663158553</v>
+      </c>
+      <c r="Z74">
+        <v>265.9294721397822</v>
+      </c>
+      <c r="AA74">
+        <v>255.6013767108132</v>
+      </c>
+      <c r="AB74">
+        <v>6.35593220338983</v>
       </c>
     </row>
     <row r="75">
@@ -5786,17 +7125,35 @@
       <c r="R75">
         <v>-74.28940945752831</v>
       </c>
+      <c r="S75">
+        <v>-420.5163597635979</v>
+      </c>
       <c r="T75">
-        <v>-420.5163597635979</v>
+        <v>-105.1290899408995</v>
       </c>
       <c r="U75">
-        <v>-105.1290899408995</v>
+        <v>-1121.376959369594</v>
       </c>
       <c r="V75">
-        <v>-1121.376959369594</v>
+        <v>-317.7711819779099</v>
       </c>
       <c r="W75">
-        <v>-317.7711819779099</v>
+        <v>27.02231242172678</v>
+      </c>
+      <c r="X75">
+        <v>-1048.038006160844</v>
+      </c>
+      <c r="Y75">
+        <v>-340.4375718152983</v>
+      </c>
+      <c r="Z75">
+        <v>4.355922584338373</v>
+      </c>
+      <c r="AA75">
+        <v>-1070.704395998233</v>
+      </c>
+      <c r="AB75">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -5858,17 +7215,35 @@
       <c r="R76">
         <v>-70.40174225218152</v>
       </c>
+      <c r="S76">
+        <v>255.4085737801854</v>
+      </c>
       <c r="T76">
-        <v>255.4085737801854</v>
+        <v>63.85214344504634</v>
       </c>
       <c r="U76">
-        <v>63.85214344504634</v>
+        <v>681.0895300804943</v>
       </c>
       <c r="V76">
-        <v>681.0895300804943</v>
+        <v>996.7454575444845</v>
       </c>
       <c r="W76">
-        <v>996.7454575444845</v>
+        <v>833.0563835175005</v>
+      </c>
+      <c r="X76">
+        <v>1394.559057536638</v>
+      </c>
+      <c r="Y76">
+        <v>872.3885314815897</v>
+      </c>
+      <c r="Z76">
+        <v>708.6994574546057</v>
+      </c>
+      <c r="AA76">
+        <v>1270.202131473744</v>
+      </c>
+      <c r="AB76">
+        <v>10.48333333333333</v>
       </c>
     </row>
     <row r="77">
@@ -5930,17 +7305,35 @@
       <c r="R77">
         <v>-75.47952167775412</v>
       </c>
+      <c r="S77">
+        <v>-128.2650949350807</v>
+      </c>
       <c r="T77">
-        <v>-128.2650949350807</v>
+        <v>-32.06627373377018</v>
       </c>
       <c r="U77">
-        <v>-32.06627373377018</v>
+        <v>-342.0402531602153</v>
       </c>
       <c r="V77">
-        <v>-342.0402531602153</v>
+        <v>475.8265392130529</v>
       </c>
       <c r="W77">
-        <v>475.8265392130529</v>
+        <v>601.9026710784744</v>
+      </c>
+      <c r="X77">
+        <v>232.1740703238073</v>
+      </c>
+      <c r="Y77">
+        <v>446.2328801745508</v>
+      </c>
+      <c r="Z77">
+        <v>572.3090120399723</v>
+      </c>
+      <c r="AA77">
+        <v>202.5804112853052</v>
+      </c>
+      <c r="AB77">
+        <v>9.85</v>
       </c>
     </row>
     <row r="78">
@@ -6002,17 +7395,35 @@
       <c r="R78">
         <v>-71.52936454912968</v>
       </c>
+      <c r="S78">
+        <v>-541.6394727238318</v>
+      </c>
       <c r="T78">
-        <v>-541.6394727238318</v>
+        <v>-135.4098681809579</v>
       </c>
       <c r="U78">
-        <v>-135.4098681809579</v>
+        <v>-1444.371927263551</v>
       </c>
       <c r="V78">
-        <v>-1444.371927263551</v>
+        <v>24.43357464627468</v>
       </c>
       <c r="W78">
-        <v>24.43357464627468</v>
+        <v>458.9768859898457</v>
+      </c>
+      <c r="X78">
+        <v>-906.6125866941418</v>
+      </c>
+      <c r="Y78">
+        <v>-10.37012010354783</v>
+      </c>
+      <c r="Z78">
+        <v>424.1731912400232</v>
+      </c>
+      <c r="AA78">
+        <v>-941.4162814439643</v>
+      </c>
+      <c r="AB78">
+        <v>1.9</v>
       </c>
     </row>
     <row r="79">
@@ -6074,17 +7485,35 @@
       <c r="R79">
         <v>-23.96617524080266</v>
       </c>
+      <c r="S79">
+        <v>46.72362019437261</v>
+      </c>
       <c r="T79">
-        <v>46.72362019437261</v>
+        <v>11.68090504859315</v>
       </c>
       <c r="U79">
-        <v>11.68090504859315</v>
+        <v>124.596320518327</v>
       </c>
       <c r="V79">
-        <v>124.596320518327</v>
+        <v>516.7564049834028</v>
       </c>
       <c r="W79">
-        <v>516.7564049834028</v>
+        <v>491.200300870441</v>
+      </c>
+      <c r="X79">
+        <v>585.1424942745394</v>
+      </c>
+      <c r="Y79">
+        <v>485.8209754606559</v>
+      </c>
+      <c r="Z79">
+        <v>460.2648713476941</v>
+      </c>
+      <c r="AA79">
+        <v>554.2070647517926</v>
+      </c>
+      <c r="AB79">
+        <v>2.833333333333333</v>
       </c>
     </row>
   </sheetData>
